--- a/examples/clustering_output_results.xlsx
+++ b/examples/clustering_output_results.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,662 +501,4556 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GO:0015979</t>
+          <t>GO:0060320</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>photosynthesis</t>
+          <t>rejection of self pollen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.862599965614952e-12</v>
+        <v>2.529352669158217e-13</v>
       </c>
       <c r="D2" t="n">
-        <v>3.324094180503678e-08</v>
+        <v>1.733037841903654e-09</v>
       </c>
       <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01877133105802042</v>
+      </c>
+      <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.2111841450054774</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
-        <v>-0.7590261697769165</v>
+        <v>-2.33518385887146</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.106618881225586</v>
+        <v>9.247836112976074</v>
       </c>
       <c r="J2" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101255525', 'LOC101253996', 'LOC101252117', 'LOC101260852', 'LOC101259692', 'LOC101267346', 'LOC101263732', 'LOC101262255', 'LOC101254806', 'LOC101266160', 'CAB9', 'LOC101251580', 'LOC101266713', 'LyesC2p053', 'LOC101245880', 'LOC101256426', 'LOC101254513', 'LOC101248456', 'LOC101254882', 'LOC101244717', 'LOC101267611', 'LOC101261166', 'LOC101262961', 'LOC101264109', 'LOC101263132', 'LOC101250586', 'PsbQ', 'LOC101261489', 'LOC101262260', 'LOC101255756', 'LOC101244176', 'LOC101255435', 'LOC101259223', 'LOC101256427', 'POR2', 'LOC101253541', 'OEE1', 'LOC101264004', 'LOC101264609', 'SPA', 'Rbcs-3B', 'CAB4', 'LOC101253805', 'LOC101245729', 'LOC101257676', 'LOC101246143', 'LOC101259494', 'LOC101255672', 'psbS', 'LOC101250650', 'LOC101248173', 'LOC101251312', 'LOC101249002', 'LOC104649438', 'LOC101252151', 'PSBP', 'LOC101257875', 'LOC101265555', 'LOC101245121', 'LOC101264255', 'rbcS1', 'LOC101261284', 'CAB7', 'PSBO', 'LOC101245421', 'SBPase'})</t>
+          <t>frozenset({'novel.896', 'novel.901', 'novel.803', 'novel.890', 'novel.702', 'novel.905', 'novel.907', 'novel.910', 'novel.898', 'novel.888', 'novel.900', 'novel.904', 'novel.802', 'novel.1149', 'sph1', 'novel.909', 'novel.906', 'novel.887', 'novel.899', 'novel.889', 'novel.703', 'novel.897'})</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>LOC101245880;CAB7;LOC101250650;SPA;LOC101262255;LOC101254882;LOC101255525;LOC101255672;CAB4;LOC101253996;LyesC2p053;LOC101245729;LOC101261166;psbS;POR2;LOC101246143;LOC101249002;LOC101253541;LOC101245421;LOC101259692;LOC101252117;LOC101251580;LOC101248173;LOC101263132;LOC101266713;LOC101267611;SBPase;LOC101256426;PSBP;LOC101259494;OEE1;LOC101260852;LOC101264109;LOC101259223;rbcS1;Rbcs-3B;LOC101257676;LOC101256427;LOC101267346;LOC101244717;LOC101251312;LOC101253805;LOC101244176;LOC104649438;LOC101255435;LOC101261489;LOC101252151;LOC101257875;LOC101266160;LOC101264004;LOC101248456;LOC101262260;LOC101255756;PSBO;LOC101263732;PsbQ;LOC101245121;LOC101264609;LOC101262961;CAB9;LOC101254806;LOC101265555;LOC101250586;LOC101254513;LOC101264255;LOC101261284</t>
+          <t>novel.888;novel.803;novel.890;novel.904;novel.897;novel.907;novel.901;novel.889;novel.802;novel.906;novel.898;novel.1149;sph1;novel.900;novel.702;novel.703;novel.910;novel.905;novel.887;novel.896;novel.909;novel.899</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GO:0006082</t>
+          <t>GO:0005576</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>organic acid metabolic process</t>
+          <t>extracellular region</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.80302686050468e-07</v>
+        <v>4.114097238751353e-13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001361658114953077</v>
+        <v>1.733037841903654e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3152156272452308</v>
+        <v>-0.07526878624699827</v>
       </c>
       <c r="G3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.64739727973938</v>
+        <v>-2.108686447143555</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.480170726776123</v>
+        <v>9.747881889343262</v>
       </c>
       <c r="J3" t="n">
-        <v>183</v>
+        <v>293</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101267346', 'LOC101262091', 'LOC100134915', 'LOC101244092', 'ACS2', 'LOC101260363', 'LOC101258131', 'LOC101254848', 'LOC101264480', 'ME1', 'LOC101250164', 'LOC101261578', 'gdh1', 'LOC101257319', 'LOC101263817', 'LOC104644402', 'LOC101248029', 'LOC101256685', 'LOC101264132', 'LOC101257857', 'PIIGLB1', 'LOC101254720', 'LOC101253805', 'LOC543658', 'LOC101251311', 'LOC101248790', 'LOC104648641', 'LOC101258079', 'AOS3', 'LOC101250891', 'LOC101254332', 'LOC544276', 'LOC101250354', 'LOC101249935', 'LOC101250791', 'LOC101266174', 'NAOD', 'GABA-TP2', 'LOC101256529', 'LOC101250561', 'LOC101256077', 'LOC101250058', 'SlALDH2B7a', 'LOC101252202', 'novel.706', '20ox-2', 'LOC543694', 'LOC101247891', 'LOC101248511', 'SlFRK3', 'SlFBA2', 'LOC101252466', 'LOC104645573', 'LOC101255340', 'LOC101260990', 'LOC101260607', 'LOC101255411', 'LOC101254281', 'LOC101256694', 'AOS2', 'LOC101256649', 'ACS6', 'LOC101245952', 'LOC101250807', 'LOC101254137', 'LOC101266950', 'LOC101244614', '3OH-1', 'LOC101267959', 'GA2ox2', 'LOC101254497', 'LOC101258461', 'LOC101267503', 'PAL5', 'novel.312', 'LysRS', 'LOC101267663', 'LOC101258830', 'LOC101246116', 'LOC101268510', 'LOC101252583', 'LOC101247770', 'LOC101264863', 'LOC104646631', 'LOC101254608', 'LOC101262198', 'LOC101256513', 'LOC101252161', 'TomloxC', 'LOC101259236', 'LOC101245370', 'novel.168', 'LOC101258355', 'LOC101258787', 'LOC101259725', 'LOC101254112', 'LOC101244469', 'LOC101247014', 'LOC101244007', 'GME1', 'LOC101247914', 'LOC101259235', 'LOC101268347', 'LOC101256592', 'LOC101245553', 'LOC101252453', 'LOC101258500', 'LOXB', 'LOC101250586', 'LeNCED1', 'LOC101267118', 'LOC101055519', 'LOC101251816', 'LOC101254597', 'NR', 'LOC101259572', 'LOC101258525', 'nii1', 'LOC101244691', 'HXK4', 'LOC101252192', 'LOC101245480', 'LOC101244882', 'LOC778326', 'novel.105', 'LOC101255874', 'LOC101251091', 'novel.113', 'LOC101247693', 'LOC101245297', 'LOC101264873', '3OH-2', 'LOC101247047', 'LOC101261642', 'LOC543920', 'LOC101263879', 'LOC101250473', 'LOC101249193', 'LOC101251350', 'LOC101267103', 'LOC109120859', 'HXK3', 'LOC101262503', 'LOC101263535', 'GS1', 'LOC101247833', 'LOC101259689', 'LOC101267184', 'LOC101252738', 'LOC101250481', 'TAO3', 'LOC101249671', 'adc1', 'LOC112940921', 'LOC101246995', 'LOC101259366', 'LOC101249057', 'LOC101246283', 'LOC101246396', 'LOC101249786', 'LOC107648852', 'ACS4', 'LOC101247828', 'MIOX', 'LOC101252977', 'HPL', 'LOC101254439', 'hdc', 'LOC101258391', 'LOC101263606', 'LOC101263085', 'LOC101254591', 'LOC101255271', 'LOC104648010', 'DXR', 'mdh', 'LOC101257261', 'LOC101248052', 'LEAS1', 'LOC101263406', 'LOC101266918', 'HDS', 'LOC101252681'})</t>
+          <t>frozenset({'TMP1', 'XTH16', 'XYL1', 'novel.805', 'novel.896', 'LOC101244564', 'LOC101267538', 'LOC101257228', 'tXET-B2', 'novel.702', 'XTH5', 'TAPG5', 'LOC101260592', 'novel.710', 'PME2.1', 'LOC101255377', 'LOC101260044', 'PGcat', 'SBT1', 'sbt4b', 'TGAS118', 'SlFBA2', 'LOC101261288', 'sbt4e', 'LOC101260852', 'novel.1171', 'LOC101267665', 'SlCYP1', 'novel.187', 'LOC104645411', 'TPX2', 'novel.77', 'Man4', 'LOC101246731', 'PE1', 'LOC101244214', 'LOC543883', 'TMP', 'sbt4c', 'LOC101259873', 'novel.438', 'PSK2', 'SlCKX2', 'SlFBA3', 'LOC101266973', 'LOC101267917', 'LOC101245673', 'LOC543511', 'exp11', 'LOC101254166', 'LIN8', 'PR1a2', 'LOC101266643', 'LOC101252117', 'Stig1', 'LOC101257783', 'LOC101252603', 'LOC101263879', 'LOC104644402', 'LOC101244241', 'PMEU1', 'novel.909', 'LOC100191110', 'LOC101251653', 'LOC101247488', 'LOC778302', 'CHI9', 'cellulase', 'P69A', 'sbt4d', 'novel.887', 'LOC101260447', 'SN2', 'LOC101244124', 'LOC101266611', 'lin5', 'LOC101260130', 'LOC101256574', 'LOC101253643', 'LOC101253648', 'SlArf_Xyl2', 'LOC101261426', 'LOC101259978', 'novel.901', 'LOC101247731', 'LOC101258822', 'novel.867', 'LOC101249518', 'EXPA10', 'PSK1', 'LOC101251798', 'CHI3', 'novel.910', 'LOC101254500', 'XTH9', 'LOC101256306', 'novel.888', 'sbt4a', 'TAPG1', 'SlCKX4', 'LOC101268808', 'LOC101258669', 'novel.1010', 'sbt3', 'LOC101250696', 'LOC104648550', 'LOC101252788', 'Wiv-1', 'PS-2', 'novel.904', 'Xegip', 'LOC101247284', 'LOC101249884', 'novel.116', 'LOC101261198', 'LOC101254950', 'LOC544217', 'novel.696', 'LOC101256106', 'LOC101251962', 'LOC101252520', 'LOC109121167', 'LOC101249763', 'novel.87', 'XTH6', 'SlArf_Xyl1', 'p69c', 'LOC101268888', 'p69F', 'LOC101254239', 'TPG6', 'LOC101245035', 'LOC101267778', 'Cel2', 'XTH7', 'TAP2', 'PG2', 'LOC101267376', 'SlArf_Xyl3', 'novel.806', 'LOC101252532', 'LOC101268065', 'LOC101253176', 'LOC101264132', 'LOC104645427', 'LOC101266976', 'LOC101263475', 'LOC101249210', 'novel.1103', 'tEG3', 'novel.703', 'LOC101246103', 'PMEI', 'LOC101258317', 'LOC101257528', 'LOC101246554', 'novel.907', 'LOC101251035', 'XSP10', 'LOC101255712', 'LOC101249056', 'novel.898', 'LOC101258355', 'LOC101248912', 'LOC101246639', 'LOC101256127', 'LOC101268518', 'SlFBA1', 'LOC101260582', 'LOC101250880', 'LOC101258638', 'TAPG2', 'PAP1', 'LOC101265627', 'LOC101261972', 'Mdip1', 'LeMAN2', 'LOC101246713', 'TAPG4', 'LOC101265285', 'LOC101253826', 'novel.972', 'LOC101249996', 'SlArf_Xyl4', 'LOC101246829', 'LOC101264531', 'LOC101249175', 'P4', 'LOC101251077', 'LOC101245521', 'LOC101263243', 'LOC101254190', 'pip1', 'LOC101257768', 'novel.906', 'LOC101256554', 'novel.973', 'LOC101254806', 'P69B', 'TPP3', 'LOC101265484', 'LOC101256015', 'CHI17', 'LOC101264400', 'LOC101055519', 'Lemir', 'LOC101250517', 'novel.889', 'EXPA4', 'novel.899', 'PR1b1', 'LOC101244240', 'LOC101245358', 'LOC101268410', 'LOC109118719', 'novel.897', 'LOC101248161', 'LOC101263181', 'TBG6', 'PR-1a1', 'LOC112941971', 'CHI14', 'LOC101263132', 'TBG7', 'PSK3', 'novel.803', 'LOC101255625', 'novel.890', 'novel.905', 'LOC101266652', 'LOC101265242', 'novel.622', 'EXPA8', 'RSI-1', 'LOC101264463', 'PR-P2', 'LOC101248898', 'LOC101265927', 'TLRP', 'LOC101255874', 'LOC101247374', 'novel.900', 'LOC101252733', 'LOC101249178', 'LOC101266584', 'SlVP2', 'LOC101250380', 'LOC101267232', 'LOC101259532', 'XET2', 'tXET-B1', 'novel.802', 'novel.670', 'LOC101245007', 'SBT2', 'LOC101261871', 'LOC101267191', 'LOC101245135', 'LOC101259262', 'ARF1', 'LOC101249981', 'novel.1149', 'LOC101248656', 'LOC101263035', 'LOC101252653', 'LOC101255834', 'MAN1', 'LOC100191111', 'LOC101262410', 'novel.688', 'LOC101249333', 'novel.1021', 'LOC101255261', 'XTH1', 'LOC101247519', 'sph1', 'LOC101260647', 'TBG2', 'XET4', 'LOC101263519', 'XTH3', 'LOC101248557', 'LOC101261405', 'LOC101244503', 'LOC101263269', 'novel.860', 'LOC101266183', 'LOC101266830', 'XOPG1', 'TBG5', 'EXLA1', 'PSK4', 'p69d'})</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>LOC101250473;LOC101248052;LOC543920;LOC101259725;LOC101254848;LOC112940921;LOC101247833;LOC101259366;LOC101248790;LOC101250164;LOC101250481;PAL5;SlFRK3;PIIGLB1;LOC101266918;hdc;LOC101261578;20ox-2;LOC101252202;LOC101267663;ACS4;LOC101266174;LOC101264873;LOC100134915;LOC101256077;3OH-1;LOC101258525;LOC101254112;LOC101264863;LOC101245480;LOC101244882;LOC101263085;LOC101244469;LOC101254497;LOC101256694;LOC101252453;LOC101252977;novel.312;DXR;LOC101266950;NAOD;LOC101267959;ACS6;LOC101251816;LOC101260990;LOC101244007;LOC101263817;LOC101264132;LysRS;LOC101255874;LOC101246116;LOC101247914;LOC101263606;LOC543658;LOC101260607;3OH-2;LOC101255411;LOC101249193;LOC101258079;LOC101258391;GA2ox2;LOC101257857;GS1;HPL;LOC104648641;LOC101254137;gdh1;SlALDH2B7a;LOC101254591;LOC101254597;LOC101252681;LOC101259235;LOC101250791;LOC101244691;LOC101258787;LeNCED1;LOC101247014;LOC778326;HDS;MIOX;LOC101268510;LOC101246396;NR;LOC101249935;LOC101267103;LOC101250354;LOC101259689;LOC101268347;LOC101263535;LOXB;LOC101254281;LOC101256529;LOC101244092;LOC101254332;LOC101267346;LOC101267118;LOC101251350;LOC101256513;TAO3;LOC104646631;LOC101256649;novel.706;LOC107648852;mdh;LOC101258500;LOC101249057;novel.113;LOC101258830;LOC101247693;LOC101247828;LOC109120859;LOC101250058;LOC101255340;novel.105;LOC101254720;HXK3;LOC101253805;GABA-TP2;LOC101249786;LOC101252192;LOC101252161;LOC104648010;LOC101249671;LOC101260363;adc1;LOC101250807;LOC101262198;SlFBA2;LOC543694;ME1;LOC101258355;LOC101256592;HXK4;LOC101245553;TomloxC;LOC101248511;LOC101263406;AOS2;LOC101248029;LOC101264480;LOC101251091;LOC101258131;LOC101258461;LOC101259572;LOC101247047;LOC101251311;LOC101257319;LOC104644402;LOC101244614;LOC101261642;LOC101254439;LOC101257261;LEAS1;LOC101250891;LOC544276;LOC101245297;LOC101245952;ACS2;LOC101252466;LOC101246283;LOC101254608;LOC104645573;LOC101247770;LOC101055519;LOC101250561;novel.168;LOC101267503;LOC101252738;LOC101247891;LOC101246995;LOC101259236;LOC101250586;AOS3;LOC101252583;nii1;LOC101267184;LOC101262503;LOC101263879;GME1;LOC101262091;LOC101256685;LOC101255271;LOC101245370</t>
+          <t>LOC101251798;LOC101248898;P4;LOC109118719;LOC101258317;LOC543511;tEG3;PR1a2;LOC101253826;LOC101260044;LOC101266973;SlArf_Xyl3;novel.888;LOC101252653;SlFBA1;LOC101266183;LOC101255834;TGAS118;p69c;XSP10;PR1b1;LOC101256015;LOC101268808;novel.77;LOC101265927;LOC101251962;LOC101266830;novel.803;SlCYP1;CHI9;XTH7;LOC104645411;Lemir;novel.890;P69B;LOC101267917;LOC112941971;LOC101261405;XTH5;tXET-B2;XYL1;LOC101257783;LOC101253176;novel.904;sbt3;Xegip;EXPA10;novel.87;MAN1;LOC778302;LOC101263269;PSK1;LOC101266652;novel.897;LOC101257528;LOC101258669;LOC101249763;TBG6;Stig1;LOC101267538;LOC101250380;LOC101245135;LOC101248656;novel.907;LOC101261426;SBT1;LOC101261288;LOC101250696;TAPG2;sbt4d;PGcat;LOC101246713;LOC101245521;LOC101244124;PAP1;TAP2;PR-1a1;LOC101254239;LOC101252532;LOC101256106;LOC101244503;LOC101263879;TPG6;CHI17;tXET-B1;LOC101250880;novel.972;LOC100191110;SlCKX4;SlFBA3;LOC101249996;TLRP;lin5;novel.901;LOC101249178;LOC101259873;LOC101260582;CHI14;novel.889;sbt4b;LOC101250517;LOC101245007;LOC544217;LOC101267191;LOC101265242;novel.710;novel.802;ARF1;novel.906;novel.116;TPP3;novel.805;LOC101257768;novel.696;LOC101251035;LOC101252603;LOC101263519;LOC101263132;TBG5;LOC101249518;Wiv-1;LOC101246554;LOC101263475;LOC101248912;LOC101249210;novel.898;LOC101259532;TBG2;SlCKX2;TMP1;LOC101251653;cellulase;LOC101244564;LOC101258355;XTH6;novel.806;LOC101265484;novel.1021;LOC101249981;LOC101255712;XTH3;P69A;SlVP2;LOC101268410;CHI3;TPX2;LOC101248161;TBG7;SN2;LOC101247731;Cel2;LOC101252788;novel.1149;LOC101259262;LOC101256554;EXLA1;LOC101264400;SlArf_Xyl4;LOC101264463;LOC101248557;novel.622;LOC101255377;TAPG1;XET2;LOC101254806;SBT2;sph1;LOC104648550;LOC100191111;PG2;LOC101252520;LOC101261871;LOC101260130;novel.900;PSK4;TMP;LOC101267665;LOC101055519;novel.187;LOC101267232;LOC101263035;novel.702;LOC101265285;LOC101266611;RSI-1;LOC101262410;novel.438;LOC101247284;exp11;EXPA8;LOC101256574;LOC101260852;LOC101247488;novel.703;novel.910;PR-P2;LOC101255625;PMEU1;LOC101260592;PS-2;LOC101256306;LOC101254166;XTH9;sbt4e;novel.905;Man4;LOC101254500;EXPA4;LOC101257228;SlFBA2;novel.887;LOC101268518;p69d;LOC101245358;LOC101263181;LOC101265627;LOC101267376;novel.1103;XTH16;LOC101268065;LOC101266976;LOC101268888;novel.688;novel.896;LOC101264132;LOC104645427;XOPG1;PSK3;LOC101263243;LOC101255261;TAPG5;LOC101246731;LOC101258638;PMEI;LOC101253648;LOC101266643;LOC101260647;LOC101245673;LOC101260447;LOC101249884;XET4;novel.1171;LOC101253643;LOC109121167;LOC101254190;Mdip1;PSK2;novel.867;LOC101267778;LOC101249333;sbt4a;SlArf_Xyl1;p69F;LOC101266584;PE1;novel.973;LOC101244214;novel.909;LOC101246829;LOC101246103;LeMAN2;LOC101261198;LOC101258822;XTH1;SlArf_Xyl2;LOC101259978;PME2.1;novel.899;LIN8;novel.1010;LOC101247374;LOC101245035;LOC101251077;LOC543883;LOC101264531;LOC101246639;LOC101252117;sbt4c;novel.670;LOC101244241;LOC101254950;novel.860;LOC101249056;LOC101244240;TAPG4;LOC104644402;pip1;LOC101249175;LOC101261972;LOC101247519;LOC101255874;LOC101252733;LOC101256127</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GO:0019253</t>
+          <t>GO:0015979</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>reductive pentose-phosphate cycle</t>
+          <t>photosynthesis</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.899548585508626e-06</v>
+        <v>5.282041578493308e-13</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002692610119958477</v>
+        <v>1.733037841903654e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2802928454524199</v>
+        <v>0.2201653946488247</v>
       </c>
       <c r="G4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.101615309715271</v>
+        <v>-2.583914041519165</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.900757312774658</v>
+        <v>6.929794311523438</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>GO:0019685</t>
-        </is>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101267611', 'LOC101253541', 'LOC101260852', 'LOC101264004', 'Rbcs-3B', 'LOC101264109', 'LOC101253805', 'LOC101266713', 'LOC101264255', 'rbcS1', 'LOC101257875', 'SBPase'})</t>
+          <t>frozenset({'LOC101245729', 'LOC101245421', 'LOC101254513', 'PsbQ', 'LyesC2p086', 'LOC101254882', 'LOC101260852', 'LyesC2p073', 'LOC101259494', 'LOC101264109', 'CAB4', 'LOC101252117', 'SPA', 'LyesC2p074', 'LOC101244176', 'LOC101251312', 'LOC101244717', 'LOC101267611', 'PSBO', 'LyesC2p076', 'LOC101262260', 'LOC101249002', 'UCP', 'LOC101264255', 'LyesC2p053', 'LyesC2p085', 'Rbcs-3B', 'LyesC2p075', 'LyesC2p069', 'LOC101252151', 'LOC101250650', 'LOC101253996', 'psbS', 'LyesC2p070', 'LOC101264004', 'LOC101253541', 'LOC101261284', 'LOC101245880', 'CAB9', 'LOC101255756', 'LOC101257676', 'LOC104649438', 'LOC101261489', 'LOC101256426', 'PSBR', 'LOC101245121', 'LOC101255672', 'LOC101255525', 'LOC101254806', 'rbcS1', 'LOC101264609', 'SBPase', 'LOC101263132', 'LOC101248173', 'LyesC2p072', 'LOC101259223', 'LOC101248456', 'OEE1', 'LOC101246143', 'LOC101256427', 'POR2', 'LOC101267346', 'LOC101266160', 'LOC101250586', 'LOC101261166', 'LyesC2p089', 'LOC101257875', 'LOC101266713', 'LOC101263732', 'LOC101265555', 'SLTAB2', 'LOC101262961', 'LOC101255435', 'ppc2', 'LOC101253805', 'ZF2', 'LOC101262255', 'LOC101251580', 'CAB7', 'PSBP', 'LOC101259692', 'VKOR'})</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>LOC101253541;LOC101266713;LOC101267611;SBPase;LOC101260852;LOC101264109;rbcS1;Rbcs-3B;LOC101253805;LOC101257875;LOC101264004;LOC101264255</t>
+          <t>LOC101262260;LOC101251580;LOC101265555;OEE1;ppc2;SPA;LOC101252151;LOC101249002;LyesC2p070;CAB9;LyesC2p086;LOC101245880;LOC101245729;LOC101266713;PSBO;LyesC2p089;LOC101244176;LOC101253541;LyesC2p073;psbS;LOC101255525;LOC101267611;SLTAB2;LOC101264109;LOC101264255;LOC101253805;LOC101264004;ZF2;LyesC2p069;LOC101263132;VKOR;LOC101246143;Rbcs-3B;PsbQ;UCP;LyesC2p085;LOC101255756;LOC101256426;LOC101261284;LOC101261489;LOC101245421;LOC101261166;LOC101257676;LOC101262961;rbcS1;LOC101244717;LyesC2p074;LOC101245121;LOC101254806;LOC101259223;LOC101256427;LOC101259692;LOC101248456;LOC101255435;LOC101254513;LOC101253996;CAB7;LOC101250586;LOC101263732;LOC104649438;LyesC2p076;LOC101260852;LyesC2p072;CAB4;LOC101257875;LOC101267346;PSBR;LOC101254882;PSBP;LOC101250650;POR2;LOC101259494;LOC101251312;SBPase;LOC101262255;LOC101248173;LyesC2p053;LOC101266160;LOC101255672;LOC101252117;LOC101264609;LyesC2p075</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GO:0043436</t>
+          <t>GO:0009579</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>oxoacid metabolic process</t>
+          <t>thylakoid</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.721144390523281e-06</v>
+        <v>1.242177310326369e-11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009889777738853401</v>
+        <v>3.056687816385612e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2622763693340895</v>
+        <v>-0.2541918857205393</v>
       </c>
       <c r="G5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.513599872589111</v>
+        <v>-2.737355709075928</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.736440181732178</v>
+        <v>7.435857772827148</v>
       </c>
       <c r="J5" t="n">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101267346', 'LOC101262091', 'LOC100134915', 'LOC101244092', 'ACS2', 'LOC101258131', 'LOC101254848', 'LOC101264480', 'ME1', 'LOC101250164', 'LOC101261578', 'gdh1', 'LOC101257319', 'LOC101263817', 'LOC104644402', 'LOC101248029', 'LOC101264132', 'LOC101257857', 'PIIGLB1', 'LOC101254720', 'LOC101253805', 'LOC543658', 'LOC101251311', 'LOC101248790', 'LOC104648641', 'LOC101258079', 'AOS3', 'LOC101250891', 'LOC101254332', 'LOC544276', 'LOC101250354', 'LOC101249935', 'LOC101250791', 'LOC101266174', 'NAOD', 'GABA-TP2', 'LOC101256529', 'LOC101250561', 'LOC101256077', 'LOC101250058', 'SlALDH2B7a', 'LOC101252202', 'novel.706', 'LOC101247891', 'LOC101248511', 'SlFRK3', 'SlFBA2', 'LOC101252466', 'LOC104645573', 'LOC101260990', 'LOC101260607', 'LOC101255411', 'LOC101254281', 'LOC101256694', 'AOS2', 'LOC101256649', 'ACS6', 'LOC101245952', 'LOC101250807', 'LOC101254137', 'LOC101266950', 'LOC101244614', 'LOC101267959', 'LOC101258461', 'LOC101267503', 'PAL5', 'novel.312', 'LysRS', 'LOC101267663', 'LOC101258830', 'LOC101246116', 'LOC101268510', 'LOC101252583', 'LOC101247770', 'LOC101264863', 'LOC104646631', 'LOC101254608', 'LOC101256513', 'LOC101252161', 'TomloxC', 'LOC101259236', 'LOC101245370', 'novel.168', 'LOC101258355', 'LOC101258787', 'LOC101259725', 'LOC101254112', 'LOC101244469', 'LOC101244007', 'GME1', 'LOC101247914', 'LOC101259235', 'LOC101268347', 'LOC101256592', 'LOC101245553', 'LOC101252453', 'LOC101258500', 'LOXB', 'LOC101250586', 'LeNCED1', 'LOC101267118', 'LOC101055519', 'LOC101251816', 'LOC101254597', 'NR', 'LOC101259572', 'LOC101258525', 'nii1', 'LOC101244691', 'HXK4', 'LOC101252192', 'LOC101245480', 'LOC101244882', 'LOC778326', 'novel.105', 'LOC101255874', 'LOC101251091', 'novel.113', 'LOC101247693', 'LOC101245297', 'LOC101264873', 'LOC101247047', 'LOC101261642', 'LOC543920', 'LOC101263879', 'LOC101249193', 'LOC101251350', 'LOC101267103', 'LOC109120859', 'HXK3', 'LOC101262503', 'LOC101263535', 'GS1', 'LOC101247833', 'LOC101267184', 'LOC101252738', 'LOC101250481', 'TAO3', 'LOC101249671', 'adc1', 'LOC112940921', 'LOC101246995', 'LOC101259366', 'LOC101249057', 'LOC101246283', 'LOC101246396', 'LOC107648852', 'ACS4', 'LOC101247828', 'MIOX', 'LOC101252977', 'HPL', 'LOC101254439', 'hdc', 'LOC101258391', 'LOC101263606', 'LOC101263085', 'LOC101254591', 'LOC101255271', 'LOC104648010', 'DXR', 'mdh', 'LOC101257261', 'LOC101248052', 'LEAS1', 'LOC101263406', 'LOC101266918', 'HDS', 'LOC101252681'})</t>
+          <t>frozenset({'PETE', 'LOC101255514', 'LOC101245729', 'LyesC2p062', 'LOC101245421', 'LOC101254513', 'PsbQ', 'SlFBA2', 'LyesC2p086', 'LOC101254882', 'SlCOR413IM1', 'LOC101255271', 'LOC101243864', 'LOC101246731', 'LyesC2p073', 'LOC101259494', 'SlFBA3', 'PIIGLB1', 'LOC101264109', 'CAB4', 'LOC101252117', 'LOC101252603', 'LyesC2p063', 'LOC101243905', 'LOC101262783', 'LOC101268227', 'LOC101245901', 'SPA', 'LOC101257833', 'LyesC2p074', 'LOC101251312', 'LOC101249164', 'LOC109120519', 'PSBO', 'LOC101248511', 'LyesC2p076', 'LOC101262260', 'LOC101259357', 'LOC101249002', 'LOC101268563', 'LOC101260274', 'LyesC2p082', 'LOC101260607', 'LOC101249904', 'LOC101262218', 'LOC101264255', 'LyesC2p053', 'LyesC2p085', 'LOC544217', 'LOC101267006', 'TomloxC', 'LyesC2p075', 'LyesC2p069', 'LOC101259028', 'LOC101262509', 'LOC101252151', 'VDE', 'MSH1', 'LOC101246554', 'LOC101257061', 'LOC101250650', 'LOC101253342', 'LOC101253996', 'psbS', 'LyesC2p070', 'HrBP1', 'SlFBA1', 'LOC101261284', 'LOC101245880', 'CAB9', 'LOC101255756', 'LOC101257676', 'LOC104649438', 'PPO-2', 'LOC101268832', 'NAGK', 'SlFBA4', 'LOC101256944', 'LOC101256426', 'PSBR', 'LOC101267919', 'LOC543932', 'LOC101245704', 'LOC101263249', 'LOC101245121', 'LOC101255672', 'LOC101255525', 'LOC101254806', 'LOC101257857', 'LOC101264609', 'LOC101244709', 'LOC101263132', 'LOC101248173', 'LyesC2p072', 'LOC101259223', 'LyesC2p083', 'LOC101248456', 'LOC101265242', 'OEE1', 'LOC101263054', 'LOC101256427', 'LOC543930', 'LOC101268560', 'LOC101250586', 'LOC101266493', 'LOC104649028', 'LyesC2p089', 'LyesC2p084', 'LOC101263732', 'LOC101265555', 'LOC101262961', 'LOC100037730', 'LOC101262255', 'LyesC2p081', 'CAB7', 'PSBP', 'LOC101263269', 'LOC101259692', 'LOC101247687', 'VKOR', 'PPO', 'LOC101257542'})</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>LOC101248052;LOC543920;LOC101259725;LOC101254848;LOC112940921;LOC101247833;LOC101259366;LOC101248790;LOC101250164;LOC101250481;PAL5;SlFRK3;PIIGLB1;LOC101266918;hdc;LOC101261578;LOC101252202;LOC101267663;ACS4;LOC101266174;LOC101264873;LOC100134915;LOC101256077;LOC101258525;LOC101254112;LOC101264863;LOC101245480;LOC101244882;LOC101263085;LOC101244469;LOC101256694;LOC101252453;LOC101252977;novel.312;DXR;LOC101266950;NAOD;LOC101267959;ACS6;LOC101251816;LOC101260990;LOC101244007;LOC101263817;LOC101264132;LysRS;LOC101255874;LOC101246116;LOC101247914;LOC101263606;LOC543658;LOC101260607;LOC101255411;LOC101249193;LOC101258079;LOC101258391;LOC101257857;GS1;HPL;LOC104648641;LOC101254137;gdh1;SlALDH2B7a;LOC101254591;LOC101254597;LOC101252681;LOC101259235;LOC101250791;LOC101244691;LOC101258787;LeNCED1;LOC778326;HDS;MIOX;LOC101268510;LOC101246396;NR;LOC101249935;LOC101267103;LOC101250354;LOC101268347;LOC101263535;LOXB;LOC101254281;LOC101256529;LOC101244092;LOC101254332;LOC101267346;LOC101267118;LOC101251350;LOC101256513;TAO3;LOC104646631;LOC101256649;novel.706;LOC107648852;mdh;LOC101258500;LOC101249057;novel.113;LOC101258830;LOC101247693;LOC101247828;LOC109120859;LOC101250058;novel.105;LOC101254720;HXK3;LOC101253805;GABA-TP2;LOC101252192;LOC101252161;LOC104648010;LOC101249671;adc1;LOC101250807;SlFBA2;ME1;LOC101258355;LOC101256592;HXK4;LOC101245553;TomloxC;LOC101248511;LOC101263406;AOS2;LOC101248029;LOC101264480;LOC101251091;LOC101258131;LOC101258461;LOC101259572;LOC101247047;LOC101251311;LOC101257319;LOC104644402;LOC101244614;LOC101261642;LOC101254439;LOC101257261;LEAS1;LOC101250891;LOC544276;LOC101245297;LOC101245952;ACS2;LOC101252466;LOC101246283;LOC101254608;LOC104645573;LOC101247770;LOC101055519;LOC101250561;novel.168;LOC101267503;LOC101252738;LOC101247891;LOC101246995;LOC101259236;LOC101250586;AOS3;LOC101252583;nii1;LOC101267184;LOC101262503;LOC101263879;GME1;LOC101262091;LOC101255271;LOC101245370</t>
+          <t>LOC101262260;LOC101265555;OEE1;SPA;LOC101252151;LOC101249002;LyesC2p070;CAB9;LyesC2p086;SlFBA1;PETE;LOC101245880;LOC101245729;LOC543932;PSBO;LyesC2p089;LyesC2p081;LOC101266493;LyesC2p073;LOC101263054;LOC101262783;LOC101268832;psbS;LOC101248511;LOC101263269;LOC101268227;LOC101255525;LOC101268560;VDE;LOC101245704;SlFBA4;LOC101255271;LOC101257542;LOC101264109;LOC101264255;LOC101267006;LOC101255514;LOC101256944;SlFBA3;LyesC2p082;LyesC2p069;LOC544217;LOC101265242;LOC101268563;LOC101252603;LOC101263132;VKOR;PsbQ;LOC101246554;LOC104649028;LyesC2p062;LOC101244709;LyesC2p085;LOC101243905;LyesC2p083;LOC101255756;LOC101257061;LOC101256426;LOC101261284;LOC101245421;LOC101253342;LOC101257676;LOC101262961;LyesC2p074;LOC101245121;LOC101254806;LOC101259223;LOC101256427;LOC101263249;LOC101259692;LOC101248456;LOC101257833;LOC101254513;LOC101245901;LOC101253996;LOC101260274;CAB7;LOC101250586;LOC101263732;LOC101249164;LOC104649438;LyesC2p076;PPO-2;LyesC2p072;LOC101247687;LOC100037730;CAB4;SlFBA2;PSBR;LOC101254882;PSBP;LOC101250650;LOC101246731;LOC101259494;LOC101262218;HrBP1;LOC101251312;LOC101257857;LOC101262509;LOC543930;LOC101262255;LOC101248173;NAGK;LyesC2p053;LOC101260607;PPO;LOC101249904;LyesC2p084;LOC109120519;LOC101259028;LOC101255672;LOC101259357;LOC101252117;LOC101264609;LyesC2p075;LyesC2p063;LOC101267919;TomloxC;PIIGLB1;LOC101243864;MSH1;SlCOR413IM1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GO:0015977</t>
+          <t>GO:0016491</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>carbon fixation</t>
+          <t>oxidoreductase activity</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.137734362571832e-05</v>
+        <v>3.7478820027793e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01075158972630381</v>
+        <v>7.37808051067133e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2547077215940191</v>
+        <v>-0.07856910113300968</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.504429459571838</v>
+        <v>-3.062249183654785</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.608329296112061</v>
+        <v>12.13705730438232</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101267611', 'LOC101261166', 'LOC101253541', 'LOC101260852', 'LOC101264004', 'Rbcs-3B', 'LOC101264109', 'LOC101253805', 'LOC101266713', 'LOC101264255', 'rbcS1', 'LOC101257875', 'SBPase'})</t>
+          <t>frozenset({'SlADH2B7d', 'LOC101244921', 'LOC101254591', 'LOC101267118', 'LOC101245370', 'TPX2', 'novel.77', 'LOC101265426', 'LOC101262071', 'LyesC2p073', 'LOC101268251', 'LOC101256104', 'LOC101249670', 'LOC101262785', 'LOC101255583', 'ZEP', 'LOC104649012', 'PDH', 'LOC101260468', 'LOC101251883', 'LOC101251653', 'MDHAR', 'LOC778302', 'LOC101264777', 'SlDMR6-1', 'LOC101251312', 'LOC101258232', 'LOC101248511', 'novel.66', 'LOC101258968', 'LOC101263535', 'LOC104648171', 'LOC101255461', 'LOC101264644', 'LOC101252202', 'LOC101260860', 'LOC101249763', 'TomloxC', 'novel.729', 'aco5', 'novel.1062', 'LyesC2p069', 'LOC778303', 'LOC101254281', 'nii1', 'LOC101244007', 'LOC101264132', 'opr3', 'LOC101244196', 'LOC101261488', 'LOC101246390', 'LOC101244962', 'LOC101255117', 'LyesC2p070', 'LOC101248253', 'LOC101260280', 'LOC101253541', 'GA2ox2', 'LOC101250561', 'SD1', 'novel.1159', 'LOC101265285', 'LOC101256685', 'novel.972', 'zds', 'LOC101257532', 'LOC101259320', 'SlADH12A1', 'LOC101260928', 'LOC101247510', 'CYP85A1', 'LOC101246681', 'NSY', 'LOC104649220', 'LOC101246642', 'LOC101250164', 'LOC101263406', 'LOC101250714', 'LOC101266713', 'SlCKX1', 'LOC101250012', 'LOC104644379', 'MSRA4', 'SEND33', 'LOC101258933', 'LOC101262255', 'RBOH1', 'LOC101268833', 'PPO', 'LOC101266862', 'MSRA3', 'LOC101254720', 'SlALD3H1', 'LOC100134915', 'LOC101243864', 'SSR2', 'SlALDH11A3a', 'LOC101258131', 'LOC101255180', 'LOC101250416', '3OH-2', 'LOC101243905', 'MIOX', 'LOC101254497', 'LOC112940024', 'LyesC2p074', 'LOC101248222', 'LOC101262295', 'gdh1', '3OH-1', 'LOC101253648', 'LOC101244717', 'novel.185', 'LyesC2p076', 'LOC101259357', 'SlADH10A9', 'LOC101256306', 'LOC101267934', 'LOC101250715', 'SO', 'LOC101253022', 'AOS2', 'HPL', 'SlALDH2B7a', 'LOC104646213', 'LOC101244831', 'LOC101245697', 'CrtR-b2', 'LOC101268013', 'LOC101262011', 'LOC101267576', 'LOC101257813', 'LOC101055609', 'LOC101259369', 'VDE', 'LOC101264170', 'LOC544002', 'LOC109120859', 'LOC101245553', 'LOC101255756', 'LOC101256174', 'novel.93', 'LOC101260086', 'LOC101245803', 'LOC101246116', 'LOC101255353', 'LOC101264995', 'yfe37', 'TAO3', 'LOC101256426', 'EO', 'LOC101262964', 'LOC112941697', 'LOC101249256', 'LOC101256015', 'novel.92', 'LOC101263405', 'LOC101260960', 'LOC101251366', 'LOC101246396', 'opr2', 'LOC101246558', 'CYP77A19', 'LOC101250586', 'LOC101264047', 'LOC104649028', 'LOC101255874', 'LOC101266174', 'LOC101247833', 'LyesC2p089', 'LOC101266452', '20ox-2', 'SlAKR1', 'LOC101247914', 'SlSSR1', 'SlCKX3', 'LOC101246950', 'LOC101255011', 'LeNCED1', 'VKOR', 'LOC101252777', 'LOC101266267', 'LOC101249663', 'LOC101257228', 'LOC101267960', 'LOC101245297', 'ME2', 'LOC101249193', 'LOC101244634', 'SlGRX22', 'LOC101268276', 'LOC101268617', 'LOC101267917', 'LOC101263783', 'LOC101261339', 'LOC101257572', 'LOC101259372', 'Wfi1', 'LOC101253340', 'HDS', 'PRO2', 'SlALDH6B2', 'CYP724B2', 'LOC101254137', 'MSRA', 'PSBO', 'PAR2', 'LOC101264213', 'LOC101250559', 'LOC101252977', 'SSR1', 'SlCKX4', 'LOC101266918', 'LOC101245978', 'LyesC2p053', 'LOC101247061', 'LOC101261750', 'ACO3', 'LOC101258297', 'NR', 'TAP2', 'LOC101267376', 'LOC101252918', 'LOC101251223', 'LOC101247770', 'LOC101246651', 'GR', 'SlADH3F1a', 'LOC101245874', 'novel.915', 'ACO1', 'LOC101252171', 'LOC101261284', 'LOC101248098', 'LOC101248896', 'LOC101250006', 'PPO-2', 'LOC107648852', 'LOC101253283', 'MSRA5', 'LOC101245281', 'LOC101262998', 'LOC101260363', 'novel.973', 'LOC101267987', 'ME1', 'LOC101249699', 'LOC101258323', 'LOC101244392', 'OEE1', 'LOC101265835', 'POR2', 'LOC101254848', 'LOC101247232', 'TomloxE', 'OPR1', 'LOC101266160', 'novel.105', 'LOC101264773', 'CYP734A8', 'novel.673', 'SODCC.1', 'LOC101249981', 'LOC101252466', 'LOC101263035', 'LOC101265775', 'mMDH1', 'LOC101257397', 'PAR1', 'LOC101254669', 'LOC101258500', 'LOC101248790', 'SlscADH1', 'LOC101247804', 'TMP1', 'novel.928', 'novel.394', 'PETE', 'LOC101245261', 'SlCYP735A2', 'LOC101252232', 'pds', 'AOS3', 'LOC101267522', 'SlCKX2', 'LOC101262639', 'LOC101260469', 'LOC101252603', 'LOC101255340', 'LOC101250354', 'SlCKX7', 'SlAKR4B', 'LOC100191110', 'LOC101265488', 'TAO2', 'LOC101246763', 'TPx1', 'SlCYP735A1', 'CRTISO', 'LOC101248505', 'SSADH', 'LOC101252642', 'LOC101247777', 'LOC101264879', 'LOC101245293', 'ACO4-like', 'LOC101257319', 'LOC101250481', 'HMG2', 'LOC101266963', 'SDH', 'LOC101249786', 'ODD', 'LOC101250128', 'LOC101264004', 'Mdip1', 'LOC101264583', 'SlFBA4', 'LOC101256720', 'LOC101264681', 'mMDH2', 'SlCKX5', 'novel.107', 'novel.1175', 'LOC778326', 'LOC101254066', 'E8-6', 'LOC101264988', 'DXR', 'LOC101247497', 'mdh', 'SODCP.2', 'F3H', 'LOC101256520', 'LOXB', 'HMGR', 'LOC101254319', 'ACO4'})</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>LOC101261166;LOC101253541;LOC101266713;LOC101267611;SBPase;LOC101260852;LOC101264109;rbcS1;Rbcs-3B;LOC101253805;LOC101257875;LOC101264004;LOC101264255</t>
+          <t>SlCYP735A2;LOC101268833;LOC101246950;LOC101258500;LOC101244196;LOC104646213;LOC101266267;SlAKR1;HDS;OEE1;GA2ox2;SlAKR4B;SODCP.2;SD1;SlSSR1;LyesC2p070;LOC101247497;LOC778303;LOC101256685;SEND33;PETE;LOC101250481;F3H;LOC101266713;PSBO;LOC101251223;LyesC2p089;LOC101256015;LOC101258131;novel.77;LOC101252777;LOC101250006;LOC101257532;opr2;LOC101250714;zds;LOC101255011;LOC101253541;novel.92;LOC101246116;LOC101247061;LOC101267917;MSRA3;LyesC2p073;LOC101254066;LOC101252918;LOC101252232;ZEP;LOC101264213;LOC101252642;LOC101258323;E8-6;LOC101267118;LOC101248511;LOC778302;LOC101258297;LOC101256104;LOC101262785;LOC104649220;LOC101245553;LOC101264170;SO;LOC101252202;LOC101249763;mdh;LOC101249193;VDE;TAO3;LOC101268251;LOC101267987;MIOX;3OH-1;LOC112941697;LOC101255180;LOC101247770;SlFBA4;SODCC.1;LOC101254591;LOC101245261;LOC101254669;TAP2;LOC101248098;LOC101266452;LOC101262071;LOC101257572;TomloxE;novel.66;SlALDH2B7a;novel.673;LOC101244831;LOC101254497;novel.394;LOC101260363;LOC101264004;LeNCED1;CYP734A8;LOC112940024;novel.972;LOC100191110;LOC101258968;LOC544002;SlCKX4;LOC101265426;LOC101250561;LOC101245293;LOC101244007;LOC101266963;LyesC2p069;LOC101264047;LOC101245978;LOC101260086;LOC101244392;novel.928;LOC101268617;LOC101253283;SlGRX22;LOC101265488;MDHAR;LOC101262639;LOC101262964;NR;LOC101260468;LOC101247510;CYP724B2;LOC101246390;LOC101251366;LOC101252603;LOC101263783;LOC101245297;TPx1;VKOR;LOC101257319;LOC101250559;ACO4;LOC101250164;SSADH;PAR2;LOC101250354;3OH-2;SlCKX2;PAR1;LOC101249256;LOC101256520;TMP1;LOC104649028;LOC101253340;LOC101251653;LOC100134915;PRO2;LOC101261339;LOC101245803;LOC101250416;SlCKX1;LOC101243905;LOC101254720;LOC101249786;LOC101255756;SlADH12A1;LOC101249981;LOC101256426;LOC101246763;LOC101261750;LOC101261284;SlADH2B7d;ACO3;TPX2;SDH;LOC101247914;SlALDH6B2;LOC101248896;LOC101262295;SlCKX5;CrtR-b2;LOC101249670;ACO1;LOC101248253;HMG2;LOC101268276;LOC101254281;ACO4-like;LOC101246651;LOC101244717;LOC101247777;ME1;LyesC2p074;LOC101245874;LOC101254137;LOC101268013;LOC101255353;LOC101247232;LOC101259320;mMDH1;LOC101266918;LOC101262011;ME2;LOC101250012;CRTISO;TAO2;novel.105;LOC101263035;DXR;NSY;LOC101265285;LOC104644379;20ox-2;LOC101264777;LOC101250586;AOS2;LOC101264644;SlCKX7;LOC101258232;LOC101258933;LOC101267934;LyesC2p076;PPO-2;MSRA4;LOC101250128;SSR2;AOS3;novel.1159;LOC101247804;LOC101248222;LOC101249699;LOC101253022;novel.107;SlADH10A9;LOC101246396;LOC101055609;LOC107648852;LOC101266174;LOC101256306;LOC101256720;LOC101260860;novel.1175;LOC101252977;LOC101246558;CYP77A19;LOC101262998;LOC101244634;LOC101249663;LOC101245281;LOC101263405;LOC101260928;LOC101257228;novel.1062;LOC101254319;SlDMR6-1;LOC101250715;LOC101256174;LOC101248790;OPR1;LOXB;LOC101267576;LOC101244962;LOC101252171;LOC101264988;LOC101260960;LOC101266862;LOC101267376;Wfi1;LOC101264773;novel.93;mMDH2;LOC101244921;SlALD3H1;LOC101264132;novel.915;LOC101248505;LOC101246681;pds;LOC101252466;HMGR;POR2;yfe37;LOC101246642;LOC109120859;LOC101255117;LOC101253648;LOC778326;HPL;LOC101254848;LOC101265775;aco5;LOC101263406;LOC101257397;LOC101251312;SlCKX3;GR;LOC101264879;LOC101259372;LOC101255461;LOC101255583;nii1;Mdip1;LOC101264681;LOC101245370;LOC101267522;LOC104648171;LOC101262255;SlALDH11A3a;LOC101265835;EO;LOC104649012;LOC101245697;novel.973;LyesC2p053;gdh1;CYP85A1;PPO;LOC101247833;RBOH1;LOC101251883;LOC101266160;LOC101260280;PDH;LOC101264995;LOC101261488;LOC101259357;SlCYP735A1;SlADH3F1a;LOC101259369;novel.729;LOC101263535;TomloxC;LOC101243864;MSRA5;novel.185;LOC101260469;LOC101255340;ODD;LOC101257813;SlscADH1;SSR1;LOC101264583;LOC101267960;opr3;LOC101255874;MSRA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GO:0006629</t>
+          <t>GO:0031976</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lipid metabolic process</t>
+          <t>plastid thylakoid</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.490958867699495e-05</v>
+        <v>3.200053270506453e-10</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0109133720310275</v>
+        <v>4.499732048799288e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1687406142879203</v>
+        <v>-0.285424035542177</v>
       </c>
       <c r="G7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.969987630844116</v>
+        <v>-2.783917188644409</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.037650585174561</v>
+        <v>7.411523818969727</v>
       </c>
       <c r="J7" t="n">
-        <v>182</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>GO:0009534</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>frozenset({'LOC100134915', 'LOC101244092', 'LOC101260363', 'novel.572', 'LOC104649012', 'LOC101250164', 'LOC101261578', 'LOC101244831', 'LOC101246303', 'LOC101254424', 'LOC101257105', 'LOC101264132', 'LOC101256685', 'LOC101258705', 'PIIGLB1', 'LOC101249394', 'LOC101254720', 'LOC101250012', 'LOC543658', 'LOC101264777', 'LOC101264879', 'LOC101251311', 'LOC101248500', 'LOC101263151', 'LOC101248790', 'LOC101250517', 'AOS3', 'LOC101258806', 'LOC101260812', 'LOC101250354', 'LOC101255461', 'LOC101266174', 'LOC101246730', 'LOC101266963', 'CYP734A8', 'zds', 'LOC101250128', 'LOC101247250', 'HMG2', 'LOC101263090', 'LOC101250561', 'SlALDH2B7a', 'LOC101252202', 'LOC101264840', '20ox-2', 'LOC543694', 'LOC101255254', 'LOC101248511', 'LOC101249584', 'SlFRK3', 'LOC104645573', 'LOC101255340', 'LOC101260990', 'LOC101260607', 'LOC101255411', 'LOC101256694', 'AOS2', 'Psy1', 'LOC101263269', 'LOC101261405', 'LOC101267522', 'LOC101250807', 'LOC101245708', 'LOC101263181', 'LOC101266950', 'LOC101246651', '3OH-1', 'LOC101267959', 'GA2ox2', 'LOC101254497', 'LOC101267503', 'LOC101258506', 'dxs', 'HMGR', 'LOC101246264', 'LOC101250696', 'LOC101266485', 'LOC101268510', 'LOC101267665', 'LOC101252583', 'LOC101268830', 'LOC101247770', 'LOC101262198', 'LOC101250289', 'LOC101256513', 'LOC101252161', 'LOC101265793', 'LOC101259437', 'TomloxC', 'LOC101245370', 'novel.168', 'LOC101244514', 'LOC101252788', 'LOC101258355', 'LOC101246676', 'LOC101268146', 'LOC101247014', 'LOC101260469', 'LOC101245553', 'LOC101255353', 'Z-ISO', 'LOC101252453', 'LOC101250235', 'LOXB', 'dxs2', 'LOC101250586', 'LeNCED1', 'LOC101257528', 'LOC101259139', 'LOC101253180', 'LOC101254597', 'VDE', 'CYP85A1', 'LOC101258525', 'LOC101259572', 'LOC101245358', 'TIL_', 'LOC101244691', 'LOC101258273', 'GGPS2', 'novel.105', 'LOC101252025', 'LOC101255874', 'LOC101246731', 'novel.113', 'LOC101267934', 'CrtR-b2', 'LOC101254190', 'LOC101261928', 'LOC101260468', 'TIL', 'LOC101245297', '3OH-2', 'CYP724B2', 'LOC101262639', 'LOC101249518', 'LOC101249884', 'LOC101250473', 'LOC101266160', 'LOC109120859', 'LOC101266652', 'LOC101262503', 'LOC101245704', 'LOC101263535', 'LOC101245616', 'LOC104646084', 'CRTISO', 'LOC101252738', 'LOC101250481', 'TAO3', 'LOC101251763', 'LOC112940921', 'LOC101251962', 'LOC101246995', 'LOC101250011', 'LOC101244523', 'LOC101249057', 'LOC101249210', 'LOC101246396', 'LOC101261489', 'LOC101247110', 'LOC107648852', 'LOC101257572', 'LOC101249786', 'LOC101246390', 'LOC101247828', 'LOC101251516', 'LOC101249983', 'HPL', 'LOC100037490', 'LOC101263606', 'LOC101263085', 'LOC101254591', 'SlscADH1', 'DXR', 'LOC101244466', 'GAME1', 'LOC101266611', 'LOC101263783', 'LOC101263406', 'SppS', 'HDS'})</t>
+          <t>frozenset({'PETE', 'LOC101255514', 'LOC101245729', 'LyesC2p062', 'LOC101245421', 'LOC101254513', 'PsbQ', 'LyesC2p086', 'LOC101254882', 'SlCOR413IM1', 'LOC101243864', 'LOC101246731', 'LyesC2p073', 'LOC101259494', 'PIIGLB1', 'LOC101264109', 'CAB4', 'LOC101252117', 'LOC101252603', 'LyesC2p063', 'LOC101243905', 'LOC101262783', 'LOC101268227', 'LOC101245901', 'SPA', 'LOC101257833', 'LyesC2p074', 'LOC101251312', 'LOC101249164', 'LOC109120519', 'PSBO', 'LyesC2p076', 'LOC101262260', 'LOC101259357', 'LOC101249002', 'LOC101268563', 'LOC101260274', 'LyesC2p082', 'LOC101260607', 'LOC101249904', 'LOC101262218', 'LOC101264255', 'LyesC2p053', 'LyesC2p085', 'LOC544217', 'LOC101267006', 'TomloxC', 'LyesC2p075', 'LyesC2p069', 'LOC101259028', 'LOC101252151', 'VDE', 'LOC101246554', 'LOC101257061', 'LOC101250650', 'LOC101253342', 'LOC101253996', 'psbS', 'LyesC2p070', 'HrBP1', 'LOC101261284', 'LOC101245880', 'CAB9', 'LOC101255756', 'LOC101257676', 'LOC104649438', 'PPO-2', 'LOC101268832', 'NAGK', 'SlFBA4', 'LOC101256944', 'LOC101256426', 'PSBR', 'LOC101267919', 'LOC543932', 'LOC101245704', 'LOC101263249', 'LOC101245121', 'LOC101255672', 'LOC101255525', 'LOC101254806', 'LOC101257857', 'LOC101264609', 'LOC101244709', 'LOC101263132', 'LyesC2p072', 'LOC101259223', 'LyesC2p083', 'OEE1', 'LOC101263054', 'LOC101256427', 'LOC543930', 'LOC101268560', 'LOC104649028', 'LyesC2p089', 'LyesC2p084', 'LOC101263732', 'LOC101265555', 'LOC101262961', 'LOC100037730', 'LOC101262255', 'LyesC2p081', 'CAB7', 'PSBP', 'LOC101263269', 'LOC101259692', 'LOC101247687', 'VKOR', 'PPO', 'LOC101257542'})</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>LOC101250473;LOC101257105;LOC112940921;LOC101263269;LOC100037490;zds;SppS;LOC101247110;LOC101248790;SlscADH1;LOC101250164;LOC101250481;LOC101250289;Z-ISO;SlFRK3;PIIGLB1;LOC101251763;LOC101261578;LOC101258506;LOC101250012;20ox-2;LOC101252202;LOC101246303;LOC101266174;LOC100134915;LOC101251962;LOC101266611;novel.572;3OH-1;LOC101258525;LOC101263085;TIL;LOC101253180;LOC101254497;LOC101256694;LOC101252453;LOC104649012;LOC101249983;LOC101245616;DXR;LOC101268146;LOC101261405;LOC101245708;LOC101265793;LOC101266950;GGPS2;LOC101267959;LOC101260990;LOC101266963;LOC101264132;VDE;LOC101255874;LOC101263606;LOC101259437;LOC543658;LOC101260607;3OH-2;LOC101246390;LOC101255411;GA2ox2;LOC101261928;LOC101250128;HPL;LOC101258273;LOC101254190;SlALDH2B7a;LOC101254591;LOC101254597;LOC101249884;LOC101258705;LOC101255461;LOC101246651;LOC101258806;LOC101244691;LOC101249210;LeNCED1;LOC101244466;LOC101247014;LOC101250235;LOC101262639;LOC101251516;HDS;LOC101266485;LOC101268510;LOC101246396;LOC101250354;LOC101263535;LOXB;LOC101264879;LOC101252025;dxs;LOC101264777;HMG2;LOC101244092;LOC101256513;TAO3;LOC101260469;LOC107648852;LOC101257528;CYP85A1;LOC101246264;LOC101249057;LOC101245704;novel.113;LOC101257572;LOC101245358;LOC101247828;LOC109120859;LOC101246731;LOC101249394;LOC101255340;novel.105;LOC101254720;LOC101249786;LOC101252161;CRTISO;CYP724B2;LOC101264840;dxs2;LOC101260363;LOC101250807;LOC101262198;LOC101249518;LOC543694;LOC101258355;LOC101247250;LOC101248500;LOC101245553;TomloxC;LOC101268830;LOC101246730;LOC101248511;LOC101259139;LOC101263406;AOS2;LOC101261489;LOC101255254;LOC101250011;LOC101263090;LOC101259572;LOC101263783;LOC101251311;LOC101249584;LOC101266160;LOC101267522;LOC101255353;Psy1;LOC104646084;LOC101260812;LOC101267934;LOC101252788;LOC101244514;CrtR-b2;CYP734A8;LOC101245297;TIL_;LOC101263151;LOC101244523;LOC104645573;LOC101247770;LOC101246676;LOC101250561;novel.168;LOC101267665;LOC101267503;LOC101252738;LOC101246995;LOC101266652;LOC101250586;AOS3;LOC101252583;GAME1;LOC101254424;LOC101262503;LOC101250517;LOC101260468;LOC101244831;LOC101256685;LOC101250696;LOC101263181;LOC101245370;HMGR</t>
+          <t>LOC101262260;LOC101265555;OEE1;SPA;LOC101252151;LOC101249002;LyesC2p070;CAB9;LyesC2p086;PETE;LOC101245880;LOC101245729;LOC543932;PSBO;LyesC2p089;LyesC2p081;LyesC2p073;LOC101263054;LOC101262783;LOC101268832;psbS;LOC101263269;LOC101268227;LOC101255525;LOC101268560;VDE;LOC101245704;SlFBA4;LOC101257542;LOC101264109;LOC101264255;LOC101267006;LOC101255514;LOC101256944;LyesC2p082;LyesC2p069;LOC544217;LOC101268563;LOC101252603;LOC101263132;VKOR;PsbQ;LOC101246554;LOC104649028;LyesC2p062;LOC101244709;LyesC2p085;LOC101243905;LyesC2p083;LOC101255756;LOC101257061;LOC101256426;LOC101261284;LOC101245421;LOC101253342;LOC101257676;LOC101262961;LyesC2p074;LOC101245121;LOC101254806;LOC101259223;LOC101256427;LOC101263249;LOC101259692;LOC101257833;LOC101254513;LOC101245901;LOC101253996;LOC101260274;CAB7;LOC101263732;LOC101249164;LOC104649438;LyesC2p076;PPO-2;LyesC2p072;LOC101247687;LOC100037730;CAB4;PSBR;LOC101254882;PSBP;LOC101250650;LOC101246731;LOC101259494;LOC101262218;HrBP1;LOC101251312;LOC101257857;LOC543930;LOC101262255;NAGK;LyesC2p053;LOC101260607;PPO;LOC101249904;LyesC2p084;LOC109120519;LOC101259028;LOC101255672;LOC101259357;LOC101252117;LOC101264609;LyesC2p075;LyesC2p063;LOC101267919;TomloxC;PIIGLB1;LOC101243864;SlCOR413IM1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GO:0044281</t>
+          <t>GO:0004707</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>small molecule metabolic process</t>
+          <t>MAP kinase activity</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.539805577570018e-05</v>
+        <v>4.387369351016384e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0109133720310275</v>
+        <v>4.85722435948068e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2685085187005063</v>
+        <v>-0.004166666666666652</v>
       </c>
       <c r="G8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.227869987487793</v>
+        <v>-2.884768962860107</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.14775276184082</v>
+        <v>9.425561904907227</v>
       </c>
       <c r="J8" t="n">
-        <v>242</v>
+        <v>14</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101267346', 'novel.516', 'LOC101249670', 'LOC100134915', 'LOC101244092', 'ACS2', 'LOC101260363', 'LOC101258131', 'LOC101262091', 'LOC101254848', 'LOC101264480', 'LOC101249663', 'ME1', 'LOC101250164', 'LOC101254882', 'LOC101261578', 'gdh1', 'LOC109120519', 'LOC101257319', 'LOC101263817', 'LOC104644402', 'LOC101248029', 'LOC101256685', 'LOC101264132', 'LOC101257857', 'LOC101253541', 'LOC101264004', 'PIIGLB1', 'LOC101249394', 'LOC101254720', 'LOC101253805', 'LOC543658', 'LOC101251311', 'LOC101248500', 'LOC101248790', 'LOC101263369', 'LOC101258079', 'LOC104648641', 'AOS3', 'LOC101250891', 'LOC101254332', 'LOC544276', 'LOC101250354', 'LOC101249935', 'LOC101250791', 'LOC101266174', 'ARF1', 'SAHH', 'LOC101263675', 'NAOD', 'GABA-TP2', 'LOC101247250', 'LOC101256529', 'HMG2', 'LOC101250561', 'LOC101256077', 'LOC101253342', 'SlALDH2B7a', 'LOC101250058', 'LOC101252202', 'novel.706', 'LOC101264840', 'LOC101252837', '20ox-2', 'LOC543694', 'LOC101255254', 'LOC101248511', 'LOC101247891', 'LOC101249584', 'SlFRK3', 'SlFBA2', 'LOC101252466', 'LOC104645573', 'LOC101255340', 'LOC101260990', 'LOC101260607', 'LOC101255411', 'LOC101254281', 'LOC101256694', 'AOS2', 'LOC101256649', 'ACS6', 'LOC101245952', 'LOC101250807', 'LOC101254137', 'LOC101266950', 'LOC101244614', 'GA2ox2', '3OH-1', 'LOC101267959', 'LOC101254497', 'LOC101244800', 'LOC101258461', 'LOC101267503', 'PAL5', 'novel.312', 'LysRS', 'SAM1', 'LOC101267663', 'LOC101251366', 'dxs', 'LOC101258830', 'HMGR', 'LOC101246116', 'LOC101266485', 'LOC101268510', 'LOC101252583', 'LOC101247770', 'LOC101264863', 'LOC101264724', 'LOC104646631', 'LOC101254608', 'LOC101262198', 'LOC101264255', 'LOC101256513', 'LOC101252161', 'TomloxC', 'LOC101259236', 'LOC101245370', 'novel.168', 'LOC101260852', 'LOC101251035', 'LOC101250287', 'LOC101258355', 'LOC101258787', 'LOC101259725', 'LOC101268146', 'LOC101254112', 'LOC101266713', 'LOC101244469', 'LOC101263008', 'LOC101247014', 'LOC101244007', 'LOC101260469', 'GME1', 'LOC101247914', 'LOC101259235', 'LOC101268347', 'LOC101256592', 'LOC101245553', 'LOC101264109', 'LyesC2p062', 'LOC101252453', 'LOC101258500', 'LOXB', 'dxs2', 'LOC101250586', 'LeNCED1', 'LOC101267118', 'LOC101259139', 'LOC101251816', 'LOC101254597', 'NR', 'LOC101249166', 'LOC101259572', 'LOC101258525', 'LOC101055519', 'nii1', 'LOC101244691', 'HXK4', 'LOC101252192', 'LOC101245480', 'LOC101244882', 'LOC101265950', 'LOC778326', 'novel.105', 'LOC101247538', 'LOC101255874', 'LOC101252025', 'LOC101251091', 'novel.113', 'ureF', 'LOC101261928', 'LOC101247693', 'LOC101245297', 'LOC101264873', 'LOC101263281', '3OH-2', 'LOC101247047', 'LOC101261642', 'LOC543920', 'LOC101263879', 'LOC101250473', 'LOC101249193', 'LOC101264576', 'LOC101251350', 'LOC101267103', 'LOC101266160', 'LOC109120859', 'HXK3', 'LOC101262503', 'LOC101266918', 'GS1', 'LOC101263535', 'LOC101247833', 'LOC101259689', 'LOC101267184', 'LOC101252738', 'LOC101250481', 'TAO3', 'LOC101249671', 'LOC101251763', 'adc1', 'LOC112940921', 'LOC101246995', 'LOC101244523', 'GCH1', 'LOC101259366', 'LOC101249057', 'LOC101246283', 'GolS-1', 'LOC101246396', 'LOC101249786', 'LOC107648852', 'ACS4', 'LOC101248505', 'ribA', 'LOC101247828', 'MIOX', 'LOC101252977', 'HPL', 'LOC101260960', 'hdc', 'LOC101254439', 'LOC101258391', 'LOC101263606', 'LOC101263085', 'LOC101254591', 'LOC101244906', 'LOC101255271', 'LOC104648010', 'DXR', 'mdh', 'LOC101257261', 'LOC101248052', 'LOC101262221', 'LEAS1', 'LOC101257326', 'LOC101263406', 'SppS', 'HDS', 'LOC101252681'})</t>
+          <t>frozenset({'MAPK7', 'MAPK6', 'MPK3', 'MAPK12', 'LOC101245555', 'MAPK16', 'mpka1_3B1', 'MPK9', 'MAPK4', 'MAPK5', 'MAPK8', 'MPK2', 'MAPK14', 'MAPK10'})</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>LOC101250473;LOC101248052;LOC543920;LOC101259725;LOC101254848;LOC112940921;LOC101247833;LOC101259366;LOC101247538;SppS;LOC101248790;LOC101250164;LOC101250481;PAL5;LOC101249670;SlFRK3;GolS-1;PIIGLB1;LOC101266918;hdc;LOC101251763;LOC101261578;LOC101263008;LyesC2p062;LOC101263281;20ox-2;LOC101252202;LOC101267663;LOC101263369;LOC101260960;ACS4;LOC101264576;ribA;LOC101266174;LOC101264873;LOC100134915;LOC101256077;3OH-1;LOC101258525;LOC101254112;LOC101264863;LOC101245480;LOC101244882;LOC101263085;LOC101244469;LOC101254882;LOC101254497;LOC101256694;LOC101252453;LOC101252977;novel.312;DXR;LOC101268146;LOC101251366;ureF;LOC101266950;NAOD;LOC101267959;ACS6;LOC101251816;LOC101260990;LOC101244007;LOC101263817;LOC101264132;LysRS;LOC101255874;LOC101246116;LOC101247914;LOC101263606;LOC543658;LOC101260607;3OH-2;LOC101255411;LOC101249193;LOC101258079;LOC101258391;GA2ox2;LOC101257857;LOC101261928;GS1;SAHH;HPL;LOC101253541;LOC104648641;LOC101262221;LOC109120519;LOC101254137;gdh1;SlALDH2B7a;LOC101254591;LOC101254597;LOC101252681;LOC101251035;LOC101259235;LOC101250791;LOC101248505;LOC101244691;LOC101258787;LeNCED1;LOC101247014;LOC101266713;LOC778326;HDS;LOC101266485;MIOX;LOC101263675;LOC101268510;LOC101246396;LOC101264724;NR;LOC101253342;LOC101244800;LOC101249935;LOC101267103;LOC101250354;LOC101260852;LOC101264109;LOC101259689;LOC101268347;LOC101263535;LOXB;LOC101254281;LOC101257326;LOC101252025;dxs;HMG2;LOC101256529;LOC101244092;LOC101254332;LOC101267346;LOC101267118;LOC101251350;LOC101256513;TAO3;LOC104646631;LOC101256649;novel.706;LOC101260469;LOC107648852;mdh;LOC101258500;LOC101249057;novel.113;LOC101258830;LOC101247693;LOC101247828;LOC109120859;LOC101249394;LOC101250058;LOC101255340;LOC101249663;novel.105;LOC101250287;LOC101254720;HXK3;LOC101249166;LOC101253805;GABA-TP2;LOC101249786;LOC101252192;LOC101252161;LOC104648010;LOC101264840;LOC101249671;dxs2;LOC101260363;adc1;LOC101250807;LOC101262198;SlFBA2;LOC543694;ME1;LOC101258355;LOC101247250;LOC101256592;LOC101248500;HXK4;LOC101245553;TomloxC;LOC101244906;LOC101248511;LOC101259139;LOC101263406;AOS2;LOC101248029;LOC101264480;LOC101255254;LOC101251091;LOC101258131;GCH1;LOC101258461;LOC101259572;LOC101247047;LOC101251311;LOC101249584;LOC101257319;LOC101266160;LOC101264004;LOC104644402;LOC101244614;LOC101261642;LOC101254439;LOC101257261;LEAS1;LOC101250891;LOC101252837;LOC544276;LOC101245297;novel.516;LOC101245952;ACS2;LOC101252466;LOC101246283;SAM1;LOC101254608;LOC101244523;LOC104645573;LOC101247770;LOC101055519;LOC101250561;novel.168;LOC101267503;LOC101252738;LOC101247891;LOC101246995;LOC101259236;LOC101250586;AOS3;LOC101252583;nii1;LOC101267184;LOC101262503;LOC101263879;LOC101264255;GME1;LOC101265950;LOC101262091;LOC101256685;LOC101255271;ARF1;LOC101245370;HMGR</t>
+          <t>MAPK14;MAPK12;MAPK7;MAPK10;MPK2;MAPK6;LOC101245555;MPK9;MAPK16;mpka1_3B1;MPK3;MAPK4;MAPK8;MAPK5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GO:0032787</t>
+          <t>GO:0016101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>monocarboxylic acid metabolic process</t>
+          <t>diterpenoid metabolic process</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.806975822035309e-05</v>
+        <v>4.740565133648664e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01138394767882245</v>
+        <v>4.85722435948068e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2040296243847763</v>
+        <v>0.4038996768263795</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.726705551147461</v>
+        <v>-2.183874368667603</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.26828145980835</v>
+        <v>14.31729507446289</v>
       </c>
       <c r="J9" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101267346', 'LOC100134915', 'LOC101244092', 'LOC101264480', 'ME1', 'LOC101250164', 'LOC101261578', 'LOC104644402', 'LOC101264132', 'LOC101257857', 'PIIGLB1', 'LOC101254720', 'LOC101253805', 'LOC543658', 'LOC101251311', 'LOC101248790', 'LOC101258079', 'AOS3', 'LOC544276', 'LOC101250354', 'LOC101266174', 'GABA-TP2', 'LOC101256529', 'LOC101250561', 'LOC101250058', 'SlALDH2B7a', 'LOC101252202', 'novel.706', 'LOC101248511', 'SlFRK3', 'SlFBA2', 'LOC104645573', 'LOC101260990', 'LOC101260607', 'LOC101255411', 'LOC101256694', 'AOS2', 'LOC101256649', 'LOC101250807', 'LOC101254137', 'LOC101266950', 'LOC101267959', 'LOC101267503', 'PAL5', 'LOC101268510', 'LOC101252583', 'LOC101247770', 'LOC104646631', 'LOC101252161', 'TomloxC', 'LOC101256513', 'LOC101245370', 'novel.168', 'LOC101258355', 'LOC101244469', 'LOC101256592', 'LOC101252453', 'LOC101258500', 'LOXB', 'LOC101250586', 'LeNCED1', 'LOC101254597', 'LOC101259572', 'LOC101258525', 'LOC101244691', 'HXK4', 'LOC101245480', 'novel.105', 'LOC101255874', 'novel.113', 'LOC101245297', 'LOC101247047', 'LOC101267103', 'LOC109120859', 'HXK3', 'LOC101262503', 'LOC101263535', 'LOC101247833', 'LOC101252738', 'LOC101250481', 'TAO3', 'LOC112940921', 'LOC101246995', 'LOC101259366', 'LOC101249057', 'LOC101246396', 'LOC107648852', 'LOC101247828', 'LOC101252977', 'HPL', 'LOC101258391', 'LOC101263606', 'LOC101263085', 'LOC101254591', 'LOC101255271', 'DXR', 'LOC101263406', 'HDS'})</t>
+          <t>frozenset({'LOC101247014', 'novel.915', 'TPS14', 'LOC101250473', 'PHS1', 'LOC101248500', 'TPS17', 'LOC101246676', 'LOC543694', 'GA2ox2', 'LOC101249584', 'TPS28', '20ox-2', 'LOC101256685', 'TPS24', 'TPS37', 'TPS16', 'TPS31', 'TPS7', 'novel.572', '3OH-2', 'LOC101255340', 'MTS1', 'MTS2', 'LOC101254497', 'TPS36', 'TPS32', 'LOC101249786', 'SSTLE1', 'LOC101260363', 'TCTR1', 'TPS3', 'TPS33', 'LOC101262198', 'TPS39', 'TPS38', 'TPS35', '3OH-1'})</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>LOC112940921;LOC101247833;LOC101259366;LOC101248790;LOC101250164;LOC101250481;PAL5;SlFRK3;PIIGLB1;LOC101261578;LOC101252202;LOC101266174;LOC100134915;LOC101258525;LOC101245480;LOC101263085;LOC101244469;LOC101256694;LOC101252453;LOC101252977;DXR;LOC101266950;LOC101267959;LOC101260990;LOC101264132;LOC101255874;LOC101263606;LOC543658;LOC101260607;LOC101255411;LOC101258079;LOC101258391;LOC101257857;HPL;LOC101254137;SlALDH2B7a;LOC101254591;LOC101254597;LOC101244691;LeNCED1;HDS;LOC101268510;LOC101246396;LOC101267103;LOC101250354;LOC101263535;LOXB;LOC101256529;LOC101244092;LOC101267346;LOC101256513;TAO3;LOC104646631;LOC101256649;novel.706;LOC107648852;LOC101258500;LOC101249057;novel.113;LOC101247828;LOC109120859;LOC101250058;novel.105;LOC101254720;HXK3;LOC101253805;GABA-TP2;LOC101252161;LOC101250807;SlFBA2;ME1;LOC101258355;LOC101256592;HXK4;TomloxC;LOC101248511;LOC101263406;AOS2;LOC101264480;LOC101259572;LOC101247047;LOC101251311;LOC104644402;LOC544276;LOC101245297;LOC104645573;LOC101247770;LOC101250561;novel.168;LOC101267503;LOC101252738;LOC101246995;LOC101250586;AOS3;LOC101252583;LOC101262503;LOC101255271;LOC101245370</t>
+          <t>LOC543694;GA2ox2;TPS32;LOC101256685;TPS33;TPS37;TPS38;3OH-1;LOC101246676;LOC101254497;LOC101260363;TPS39;LOC101249584;MTS1;3OH-2;LOC101247014;LOC101262198;MTS2;TPS31;LOC101249786;SSTLE1;TPS35;20ox-2;TPS14;LOC101248500;LOC101250473;TPS24;novel.915;TPS36;novel.572;TPS16;TPS7;TPS28;TPS17;LOC101255340;PHS1;TCTR1;TPS3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GO:0019684</t>
+          <t>GO:0004553</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>photosynthesis, light reaction</t>
+          <t>hydrolase activity, hydrolyzing O-glycosyl compounds</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.194428108320808e-05</v>
+        <v>4.934699135914539e-10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01760817112795545</v>
+        <v>4.85722435948068e-07</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2620359738173672</v>
+        <v>0.1757244432092183</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9908742904663086</v>
+        <v>-1.694329380989075</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.55366849899292</v>
+        <v>10.04192161560059</v>
       </c>
       <c r="J10" t="n">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101253996', 'LOC101252117', 'LOC101260852', 'LOC101259692', 'LOC101254806', 'LOC101262255', 'CAB9', 'LyesC2p053', 'LOC101256426', 'LOC101254513', 'LOC101254882', 'LOC101262961', 'LOC101263132', 'LOC101250586', 'LOC101262260', 'LOC101259223', 'OEE1', 'SPA', 'CAB4', 'LOC101245729', 'LOC101257676', 'LOC101251312', 'LOC101255672', 'LOC101250650', 'LOC101249002', 'LOC104649438', 'LOC101252151', 'CAB7', 'PSBO'})</t>
+          <t>frozenset({'XTH16', 'XYL1', 'tXET-B2', 'XTH5', 'TAPG5', 'PGcat', 'Man4', 'LOC100529103', 'LIN8', 'LOC543511', 'LOC101266643', 'LOC101257783', 'LOC101247340', 'LOC101244370', 'CHI9', 'cellulase', 'LOC101254249', 'lin5', 'LOC101258151', 'TBG3', 'LOC101256574', 'SlArf_Xyl2', 'LOC101254891', 'LOC101252138', 'LOC101251335', 'CHI3', 'XTH9', 'TAPG1', 'LOC101265793', 'LOC101258669', 'Wiv-1', 'PS-2', 'XTH6', 'SlArf_Xyl1', 'LOC101254239', 'TPG6', 'Cel2', 'XTH7', 'PG2', 'LOC104645427', 'SlArf_Xyl3', 'novel.1103', 'tEG3', 'LOC101267699', 'LOC101248047', 'LOC101249056', 'LOC543987', 'LOC101263369', 'LOC101254849', 'LOC101258638', 'TAPG2', 'sfr2', 'LOC101261972', 'TAPG4', 'LeMAN2', 'LOC101246713', 'bmy3', 'SlArf_Xyl4', 'LOC101266770', 'LOC101256554', 'CHI17', 'LOC101253853', 'LOC101248575', 'LOC101268410', 'TBG6', 'LOC112941971', 'CHI14', 'TBG7', 'novel.622', 'LOC101265509', 'LOC101265927', 'LOC101264974', 'LOC101267232', 'XET2', 'tXET-B1', 'LOC101261871', 'ARF1', 'AI', 'MAN1', 'XTH1', 'AGAL', 'LOC101261650', 'TBG1', 'LOC101260647', 'TBG2', 'XET4', 'LOC101263519', 'XTH3', 'LOC101251735', 'LOC101265800', 'XOPG1', 'TBG5', 'LOC101247546'})</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>CAB7;LOC101250650;SPA;LOC101262255;LOC101254882;LOC101255672;CAB4;LOC101253996;LyesC2p053;LOC101245729;LOC101249002;LOC101259692;LOC101252117;LOC101263132;LOC101256426;OEE1;LOC101260852;LOC101259223;LOC101257676;LOC101251312;LOC104649438;LOC101252151;LOC101262260;PSBO;LOC101262961;CAB9;LOC101254806;LOC101250586;LOC101254513</t>
+          <t>AI;LOC101252138;LOC543511;tEG3;LOC101267699;SlArf_Xyl3;LOC101265927;CHI9;XTH7;LOC112941971;LOC101254891;XTH5;tXET-B2;XYL1;LOC101257783;LOC101265800;LOC101261650;MAN1;LOC543987;LOC101258669;TBG6;TAPG2;PGcat;LOC101246713;sfr2;LOC101254239;LOC101247340;TBG3;LOC101247546;TPG6;CHI17;tXET-B1;LOC101248575;lin5;CHI14;ARF1;bmy3;LOC101263519;LOC101254249;TBG5;Wiv-1;LOC101251735;TBG2;cellulase;XTH6;AGAL;XTH3;LOC101268410;CHI3;TBG7;Cel2;LOC101256554;LOC101265793;SlArf_Xyl4;novel.622;TAPG1;XET2;LOC101266770;PG2;LOC101261871;LOC101267232;LOC101264974;LOC101256574;PS-2;XTH9;LOC101263369;Man4;LOC101251335;novel.1103;XTH16;LOC104645427;XOPG1;LOC100529103;TAPG5;LOC101258638;LOC101266643;LOC101260647;XET4;LOC101258151;SlArf_Xyl1;LOC101254849;LeMAN2;LOC101253853;XTH1;SlArf_Xyl2;LOC101248047;LIN8;LOC101244370;LOC101249056;TBG1;TAPG4;LOC101265509;LOC101261972</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GO:0016998</t>
+          <t>GO:0016102</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cell wall macromolecule catabolic process</t>
+          <t>diterpenoid biosynthetic process</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.416047308774426e-05</v>
+        <v>7.409307832597448e-10</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01760817112795545</v>
+        <v>6.629983363296062e-07</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0005558643690939391</v>
+        <v>0.4059287102359238</v>
       </c>
       <c r="G11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4488855004310608</v>
+        <v>-1.77003014087677</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.156125545501709</v>
+        <v>14.41524314880371</v>
       </c>
       <c r="J11" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101256554', 'SlArf_Xyl2', 'LOC101266770', 'novel.622', 'CHI17', 'CHI9', 'ARF1', 'XYL1', 'LOC101254249', 'SlArf_Xyl4', 'CHI3', 'CHI14', 'LOC101254239', 'LOC101263519', 'LOC101266643', 'LOC101251335'})</t>
+          <t>frozenset({'LOC101247014', 'novel.915', 'TPS14', 'LOC101250473', 'PHS1', 'TPS17', 'LOC101246676', 'LOC543694', 'GA2ox2', 'LOC101249584', 'TPS28', '20ox-2', 'LOC101256685', 'TPS24', 'TPS37', 'TPS16', 'TPS31', 'TPS7', 'novel.572', '3OH-2', 'LOC101255340', 'MTS1', 'MTS2', 'LOC101254497', 'TPS36', 'TPS32', 'LOC101249786', 'SSTLE1', 'LOC101260363', 'TCTR1', 'TPS3', 'TPS33', 'LOC101262198', 'TPS39', 'TPS38', 'TPS35', '3OH-1'})</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>SlArf_Xyl4;novel.622;LOC101254239;LOC101263519;LOC101266643;CHI14;LOC101256554;CHI9;SlArf_Xyl2;CHI17;CHI3;XYL1;LOC101266770;LOC101254249;ARF1;LOC101251335</t>
+          <t>LOC543694;GA2ox2;TPS32;LOC101256685;TPS33;TPS37;TPS38;3OH-1;LOC101246676;LOC101254497;LOC101260363;TPS39;LOC101249584;MTS1;3OH-2;LOC101247014;LOC101262198;MTS2;TPS31;LOC101249786;SSTLE1;TPS35;20ox-2;TPS14;LOC101250473;TPS24;novel.915;TPS36;novel.572;TPS16;TPS7;TPS28;TPS17;LOC101255340;PHS1;TCTR1;TPS3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GO:0016053</t>
+          <t>GO:0008299</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>organic acid biosynthetic process</t>
+          <t>isoprenoid biosynthetic process</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.823832116821623e-05</v>
+        <v>2.270849022235528e-09</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01806760675198217</v>
+        <v>1.807483779133329e-06</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0.197186305984495</v>
+        <v>0.4403694928817978</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.037286996841431</v>
+        <v>-1.899494767189026</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.323330879211426</v>
+        <v>13.8458890914917</v>
       </c>
       <c r="J12" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>frozenset({'LOC100134915', 'LOC101244092', 'LOC101260363', 'LOC101254848', 'LOC101257319', 'LOC101263817', 'LOC104644402', 'LOC101256685', 'PIIGLB1', 'LOC101251311', 'LOC101248790', 'LOC104648641', 'AOS3', 'LOC101254332', 'LOC101266174', 'NAOD', 'GABA-TP2', 'LOC101256529', 'LOC101250561', 'LOC101252202', '20ox-2', 'LOC543694', 'LOC101247891', 'LOC101248511', 'SlFRK3', 'LOC101252466', 'LOC104645573', 'LOC101255340', 'LOC101255411', 'LOC101254281', 'LOC101256694', 'AOS2', 'LOC101250807', 'LOC101244614', '3OH-1', 'LOC101267959', 'GA2ox2', 'LOC101254497', 'LOC101267503', 'PAL5', 'LOC101267663', 'LOC101268510', 'LOC101252583', 'LOC101247770', 'LOC101254608', 'LOC101262198', 'LOC101252161', 'TomloxC', 'LOC101256513', 'LOC101259236', 'LOC101245370', 'LOC101259725', 'LOC101254112', 'LOC101244469', 'LOC101247014', 'GME1', 'LOC101247914', 'LOC101256592', 'LOC101258500', 'LOXB', 'LOC101250586', 'LeNCED1', 'LOC101055519', 'LOC101251816', 'LOC101244691', 'LOC101252192', 'novel.105', 'novel.113', 'LOC101247693', 'LOC101245297', '3OH-2', 'LOC543920', 'LOC101250473', 'LOC101251350', 'LOC101263535', 'GS1', 'LOC101247833', 'LOC101267184', 'LOC101250481', 'TAO3', 'LOC101259366', 'LOC101249057', 'LOC101246283', 'LOC101246396', 'LOC101249786', 'LOC107648852', 'MIOX', 'HPL', 'LOC101254439', 'LOC101258391', 'LOC101263606', 'LOC101254591', 'LEAS1', 'LOC101266918'})</t>
+          <t>frozenset({'LOC101250473', 'LOC101254591', 'PSY2', 'pds', 'LOC101262639', 'LOC101257572', 'ZEP', '3OH-2', 'LOC101255340', 'TTS2', 'LOC104645573', 'MTS2', 'LOC101254497', 'HDS', 'LOC101244523', 'TAO2', 'TPS33', 'NXD1', 'CRTISO', 'TPS35', '3OH-1', 'LOC101244466', 'dxs2', 'PHS1', 'TPS17', 'LOC101263090', 'TPS24', 'SppS', 'TPS16', 'TPS31', 'CrtR-b2', 'SlCPTBP', 'HMG2', 'MDC', 'LOC101266963', 'TPS32', 'LOC101249786', 'TPS3', 'NDPS1', 'novel.915', 'TPS14', 'GA2ox2', 'LOC101249584', 'TPS28', 'GGPS2', 'LOC101258806', 'LOC101256685', 'novel.572', 'zds', 'TAO3', 'LOC100037490', 'LOC101254190', 'LOC101260363', 'Psy1', 'novel.92', 'NSGT1', 'NSY', 'LOC101247014', 'LOC101246676', 'LOC101266160', 'LOC543694', 'DXR', 'LOC101249394', '20ox-2', 'LOC101250012', 'TPS37', 'TPS7', 'MTS1', 'dxs', 'TPS36', 'SSTLE1', 'TCTR1', 'LOC101262198', 'LeNCED1', 'TPS39', 'SlscADH1', 'TPS38', 'Z-ISO', 'HMGR', 'LOC543658'})</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>LOC101250473;LOC543920;LOC101259725;LOC101254848;LOC101247833;LOC101259366;LOC101248790;LOC101250481;PAL5;SlFRK3;PIIGLB1;LOC101266918;20ox-2;LOC101252202;LOC101267663;LOC101266174;LOC100134915;3OH-1;LOC101254112;LOC101244469;LOC101254497;LOC101256694;NAOD;LOC101267959;LOC101251816;LOC101263817;LOC101247914;LOC101263606;3OH-2;LOC101255411;LOC101258391;GA2ox2;GS1;HPL;LOC104648641;LOC101254591;LOC101244691;LeNCED1;LOC101247014;MIOX;LOC101268510;LOC101246396;LOC101263535;LOXB;LOC101254281;LOC101256529;LOC101244092;LOC101254332;LOC101251350;LOC101256513;TAO3;LOC107648852;LOC101258500;LOC101249057;novel.113;LOC101247693;LOC101255340;novel.105;GABA-TP2;LOC101249786;LOC101252192;LOC101252161;LOC101260363;LOC101250807;LOC101262198;LOC543694;LOC101256592;TomloxC;LOC101248511;AOS2;LOC101251311;LOC101257319;LOC104644402;LOC101244614;LOC101254439;LEAS1;LOC101245297;LOC101252466;LOC101246283;LOC101254608;LOC104645573;LOC101247770;LOC101055519;LOC101250561;LOC101267503;LOC101247891;LOC101259236;LOC101250586;AOS3;LOC101252583;LOC101267184;GME1;LOC101256685;LOC101245370</t>
+          <t>LOC543694;Psy1;HDS;GA2ox2;NDPS1;TPS32;LOC101256685;LOC101244523;zds;novel.92;ZEP;LOC101263090;TPS33;TPS37;TPS38;LOC104645573;TAO3;3OH-1;LOC101246676;LOC101254591;NXD1;LOC101257572;LOC101254497;LOC101260363;LeNCED1;LOC101266963;TPS39;PSY2;LOC101244466;LOC101262639;GGPS2;LOC101249584;MTS1;3OH-2;LOC101247014;LOC101262198;NSGT1;dxs;MTS2;TPS31;LOC101249394;LOC101249786;SSTLE1;LOC100037490;CrtR-b2;HMG2;TPS35;LOC101250012;CRTISO;LOC543658;TAO2;DXR;NSY;20ox-2;TPS14;LOC101250473;TPS24;novel.915;SppS;pds;HMGR;TPS36;novel.572;MDC;SlCPTBP;LOC101254190;TPS16;TPS7;LOC101266160;LOC101258806;Z-ISO;TPS28;TPS17;TTS2;LOC101255340;SlscADH1;PHS1;TCTR1;TPS3;dxs2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GO:0010207</t>
+          <t>GO:0034357</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>photosystem II assembly</t>
+          <t>photosynthetic membrane</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.24453112932453e-05</v>
+        <v>2.387208079725011e-09</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01851268577174622</v>
+        <v>1.807483779133329e-06</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1654475792406828</v>
+        <v>0.2709877800538331</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.579561710357666</v>
+        <v>-2.962695121765137</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.687627553939819</v>
+        <v>7.12045955657959</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101253996', 'LOC101252117', 'OEE1', 'LOC101263132', 'LOC101256426', 'LOC101254513', 'CAB9', 'LOC101255672', 'PSBO', 'LOC101259223'})</t>
+          <t>frozenset({'PETE', 'LOC101255514', 'LOC101245729', 'LyesC2p062', 'LOC101245421', 'LOC101254513', 'PsbQ', 'LyesC2p086', 'LOC101254882', 'SlCOR413IM1', 'LOC101243864', 'LyesC2p073', 'LOC101259494', 'LOC101264109', 'CAB4', 'LOC101252117', 'LOC101252603', 'LyesC2p063', 'LOC101262783', 'LOC101268227', 'SPA', 'LOC101257833', 'LyesC2p074', 'LOC101251312', 'LOC101249164', 'LOC109120519', 'PSBO', 'LyesC2p076', 'LOC101262260', 'LOC101249002', 'LOC101268563', 'LOC101260274', 'LyesC2p082', 'LOC101260607', 'LOC101249904', 'LOC101262218', 'LOC101264255', 'LyesC2p053', 'LyesC2p085', 'LOC101267006', 'LyesC2p075', 'LyesC2p069', 'LOC101259028', 'LOC101252151', 'VDE', 'MSH1', 'LOC101246554', 'LOC101250650', 'LOC101253342', 'LOC101253996', 'psbS', 'LyesC2p070', 'HrBP1', 'LOC101261284', 'LOC101245880', 'CAB9', 'LOC101257676', 'LOC104649438', 'LOC101268832', 'SlFBA4', 'LOC101256944', 'PSBR', 'LOC101267919', 'LOC543932', 'LOC101245704', 'LOC101263249', 'LOC101245121', 'LOC101255672', 'LOC101255525', 'LOC101254806', 'LOC101264609', 'LOC101244709', 'LOC101263132', 'LOC101248173', 'LyesC2p072', 'LOC101259223', 'LyesC2p083', 'LOC101248456', 'OEE1', 'LOC101263054', 'LOC101256427', 'LOC543930', 'LOC101268560', 'LOC104649028', 'LyesC2p089', 'LyesC2p084', 'LOC101263732', 'LOC101265555', 'LOC101262961', 'LOC101262255', 'LyesC2p081', 'CAB7', 'PSBP', 'LOC101247687', 'VKOR'})</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>LOC101255672;LOC101253996;LOC101252117;LOC101263132;LOC101256426;OEE1;LOC101259223;PSBO;CAB9;LOC101254513</t>
+          <t>LOC101262260;LOC101265555;OEE1;SPA;LOC101252151;LOC101249002;LyesC2p070;CAB9;LyesC2p086;PETE;LOC101245880;LOC101245729;LOC543932;PSBO;LyesC2p089;LyesC2p081;LyesC2p073;LOC101263054;LOC101262783;LOC101268832;psbS;LOC101268227;LOC101255525;LOC101268560;VDE;LOC101245704;SlFBA4;LOC101264109;LOC101264255;LOC101267006;LOC101255514;LOC101256944;LyesC2p082;LyesC2p069;LOC101268563;LOC101252603;LOC101263132;VKOR;PsbQ;LOC101246554;LOC104649028;LyesC2p062;LOC101244709;LyesC2p085;LyesC2p083;LOC101261284;LOC101245421;LOC101253342;LOC101257676;LOC101262961;LyesC2p074;LOC101245121;LOC101254806;LOC101259223;LOC101256427;LOC101263249;LOC101248456;LOC101257833;LOC101254513;LOC101253996;LOC101260274;CAB7;LOC101263732;LOC101249164;LOC104649438;LyesC2p076;LyesC2p072;LOC101247687;CAB4;PSBR;LOC101254882;PSBP;LOC101250650;LOC101259494;LOC101262218;HrBP1;LOC101251312;LOC543930;LOC101262255;LOC101248173;LyesC2p053;LOC101260607;LOC101249904;LyesC2p084;LOC109120519;LOC101259028;LOC101255672;LOC101252117;LOC101264609;LyesC2p075;LyesC2p063;LOC101267919;LOC101243864;MSH1;SlCOR413IM1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GO:0019752</t>
+          <t>GO:0009521</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carboxylic acid metabolic process</t>
+          <t>photosystem</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.875954888491657e-05</v>
+        <v>3.281112045357175e-09</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01974761729839121</v>
+        <v>2.306856133032191e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5424955368165274</v>
+        <v>0.2947987989420569</v>
       </c>
       <c r="G14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.27127993106842</v>
+        <v>-2.791295289993286</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.100940704345703</v>
+        <v>6.457737922668457</v>
       </c>
       <c r="J14" t="n">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>frozenset({'LOC101267346', 'LOC100134915', 'LOC101244092', 'ACS2', 'LOC101258131', 'LOC101254848', 'LOC101264480', 'ME1', 'LOC101250164', 'LOC101261578', 'gdh1', 'LOC101257319', 'LOC101263817', 'LOC104644402', 'LOC101248029', 'LOC101264132', 'LOC101257857', 'PIIGLB1', 'LOC101254720', 'LOC101253805', 'LOC543658', 'LOC101251311', 'LOC101248790', 'LOC104648641', 'LOC101258079', 'AOS3', 'LOC101250891', 'LOC101254332', 'LOC544276', 'LOC101250354', 'LOC101249935', 'LOC101266174', 'NAOD', 'GABA-TP2', 'LOC101256529', 'LOC101250561', 'LOC101250058', 'SlALDH2B7a', 'LOC101252202', 'novel.706', 'LOC101247891', 'LOC101248511', 'SlFRK3', 'SlFBA2', 'LOC101252466', 'LOC104645573', 'LOC101260990', 'LOC101260607', 'LOC101255411', 'LOC101254281', 'LOC101256694', 'AOS2', 'LOC101256649', 'ACS6', 'LOC101250807', 'LOC101254137', 'LOC101266950', 'LOC101244614', 'LOC101267959', 'LOC101267503', 'PAL5', 'LysRS', 'LOC101267663', 'LOC101258830', 'LOC101246116', 'LOC101268510', 'LOC101252583', 'LOC101247770', 'LOC101264863', 'LOC104646631', 'LOC101254608', 'LOC101256513', 'LOC101252161', 'TomloxC', 'LOC101259236', 'LOC101245370', 'novel.168', 'LOC101258355', 'LOC101259725', 'LOC101254112', 'LOC101244469', 'LOC101244007', 'GME1', 'LOC101247914', 'LOC101259235', 'LOC101245553', 'LOC101256592', 'LOC101252453', 'LOC101258500', 'LOXB', 'LOC101250586', 'LeNCED1', 'LOC101267118', 'LOC101055519', 'LOC101251816', 'LOC101254597', 'LOC101259572', 'LOC101258525', 'LOC101244691', 'HXK4', 'LOC101252192', 'LOC101245480', 'LOC101244882', 'novel.105', 'LOC101255874', 'LOC101251091', 'novel.113', 'LOC101247693', 'LOC101245297', 'LOC101264873', 'LOC101247047', 'LOC101261642', 'LOC543920', 'LOC101263879', 'LOC101249193', 'LOC101251350', 'LOC101267103', 'LOC109120859', 'HXK3', 'LOC101262503', 'LOC101263535', 'GS1', 'LOC101247833', 'LOC101267184', 'LOC101252738', 'LOC101250481', 'TAO3', 'adc1', 'LOC112940921', 'LOC101246995', 'LOC101259366', 'LOC101249057', 'LOC101246283', 'LOC101246396', 'LOC107648852', 'ACS4', 'LOC101247828', 'MIOX', 'LOC101252977', 'HPL', 'LOC101254439', 'hdc', 'LOC101258391', 'LOC101263606', 'LOC101263085', 'LOC101254591', 'LOC101255271', 'DXR', 'mdh', 'LOC101248052', 'LEAS1', 'LOC101263406', 'LOC101266918', 'HDS'})</t>
+          <t>frozenset({'LOC101263132', 'LOC101248173', 'LyesC2p072', 'PSBO', 'LOC101248456', 'OEE1', 'LOC101245729', 'LOC101262260', 'LOC101249002', 'LOC101245421', 'psbS', 'LOC101254513', 'LyesC2p070', 'PsbQ', 'LyesC2p086', 'LOC101268563', 'LyesC2p089', 'LOC101245880', 'CAB9', 'LOC101257676', 'LyesC2p073', 'LOC101259494', 'LOC101263732', 'LyesC2p053', 'LOC101265555', 'LyesC2p085', 'CAB4', 'LyesC2p075', 'PSBR', 'LyesC2p069', 'LyesC2p074', 'CAB7', 'LOC101245121', 'PSBP', 'LOC101255525', 'LOC101254806', 'LOC101255672', 'LOC101264609', 'LOC101252151'})</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>LOC101248052;LOC543920;LOC101259725;LOC101254848;LOC112940921;LOC101247833;LOC101259366;LOC101248790;LOC101250164;LOC101250481;PAL5;SlFRK3;PIIGLB1;LOC101266918;hdc;LOC101261578;LOC101252202;LOC101267663;ACS4;LOC101266174;LOC101264873;LOC100134915;LOC101258525;LOC101254112;LOC101264863;LOC101245480;LOC101244882;LOC101263085;LOC101244469;LOC101256694;LOC101252453;LOC101252977;DXR;LOC101266950;NAOD;LOC101267959;ACS6;LOC101251816;LOC101260990;LOC101244007;LOC101263817;LOC101264132;LysRS;LOC101255874;LOC101246116;LOC101247914;LOC101263606;LOC543658;LOC101260607;LOC101255411;LOC101249193;LOC101258079;LOC101258391;LOC101257857;GS1;HPL;LOC104648641;LOC101254137;gdh1;SlALDH2B7a;LOC101254591;LOC101254597;LOC101259235;LOC101244691;LeNCED1;HDS;MIOX;LOC101268510;LOC101246396;LOC101249935;LOC101267103;LOC101250354;LOC101263535;LOXB;LOC101254281;LOC101256529;LOC101244092;LOC101254332;LOC101267346;LOC101267118;LOC101251350;LOC101256513;TAO3;LOC104646631;LOC101256649;novel.706;LOC107648852;mdh;LOC101258500;LOC101249057;novel.113;LOC101258830;LOC101247693;LOC101247828;LOC109120859;LOC101250058;novel.105;LOC101254720;HXK3;LOC101253805;GABA-TP2;LOC101252192;LOC101252161;adc1;LOC101250807;SlFBA2;ME1;LOC101258355;LOC101256592;HXK4;LOC101245553;TomloxC;LOC101248511;LOC101263406;AOS2;LOC101248029;LOC101264480;LOC101251091;LOC101258131;LOC101259572;LOC101247047;LOC101251311;LOC101257319;LOC104644402;LOC101244614;LOC101261642;LOC101254439;LEAS1;LOC101250891;LOC544276;LOC101245297;ACS2;LOC101252466;LOC101246283;LOC101254608;LOC104645573;LOC101247770;LOC101055519;LOC101250561;novel.168;LOC101267503;LOC101252738;LOC101247891;LOC101246995;LOC101259236;LOC101250586;AOS3;LOC101252583;LOC101267184;LOC101262503;LOC101263879;GME1;LOC101255271;LOC101245370</t>
+          <t>LOC101262260;LOC101265555;OEE1;LOC101252151;LOC101249002;LyesC2p070;CAB9;LyesC2p086;LOC101245880;LOC101245729;PSBO;LyesC2p089;LyesC2p073;psbS;LOC101255525;LyesC2p069;LOC101268563;LOC101263132;PsbQ;LyesC2p085;LOC101245421;LOC101257676;LyesC2p074;LOC101245121;LOC101254806;LOC101248456;LOC101254513;CAB7;LOC101263732;LyesC2p072;CAB4;PSBR;PSBP;LOC101259494;LOC101248173;LyesC2p053;LOC101255672;LOC101264609;LyesC2p075</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>GO:0009535</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>chloroplast thylakoid membrane</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4.045992438185184e-09</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.489043973066048e-06</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2727636497914085</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-3.041707038879395</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.195065975189209</v>
+      </c>
+      <c r="J15" t="n">
+        <v>90</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>GO:0055035</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>frozenset({'PETE', 'LOC101255514', 'LOC101245729', 'LyesC2p062', 'LOC101254513', 'PsbQ', 'LyesC2p086', 'LOC101254882', 'SlCOR413IM1', 'LOC101243864', 'LyesC2p073', 'LOC101259494', 'LOC101264109', 'CAB4', 'LOC101252117', 'LOC101252603', 'LyesC2p063', 'LOC101262783', 'LOC101268227', 'SPA', 'LOC101257833', 'LyesC2p074', 'LOC101251312', 'LOC101249164', 'LOC109120519', 'PSBO', 'LyesC2p076', 'LOC101262260', 'LOC101249002', 'LOC101268563', 'LOC101260274', 'LyesC2p082', 'LOC101260607', 'LOC101249904', 'LOC101262218', 'LOC101264255', 'LyesC2p053', 'LyesC2p085', 'LOC101267006', 'LyesC2p075', 'LyesC2p069', 'LOC101259028', 'LOC101252151', 'VDE', 'LOC101246554', 'LOC101250650', 'LOC101253342', 'LOC101253996', 'psbS', 'LyesC2p070', 'HrBP1', 'LOC101261284', 'LOC101245880', 'CAB9', 'LOC101257676', 'LOC104649438', 'LOC101268832', 'SlFBA4', 'LOC101256944', 'PSBR', 'LOC101267919', 'LOC543932', 'LOC101245704', 'LOC101263249', 'LOC101255672', 'LOC101255525', 'LOC101254806', 'LOC101264609', 'LOC101244709', 'LOC101263132', 'LyesC2p072', 'LOC101259223', 'LyesC2p083', 'OEE1', 'LOC101263054', 'LOC101256427', 'LOC543930', 'LOC101268560', 'LOC104649028', 'LyesC2p089', 'LyesC2p084', 'LOC101263732', 'LOC101265555', 'LOC101262961', 'LOC101262255', 'LyesC2p081', 'CAB7', 'PSBP', 'LOC101247687', 'VKOR'})</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>LOC101262260;LOC101265555;OEE1;SPA;LOC101252151;LOC101249002;LyesC2p070;CAB9;LyesC2p086;PETE;LOC101245880;LOC101245729;LOC543932;PSBO;LyesC2p089;LyesC2p081;LyesC2p073;LOC101263054;LOC101262783;LOC101268832;psbS;LOC101268227;LOC101255525;LOC101268560;VDE;LOC101245704;SlFBA4;LOC101264109;LOC101264255;LOC101267006;LOC101255514;LOC101256944;LyesC2p082;LyesC2p069;LOC101268563;LOC101252603;LOC101263132;VKOR;PsbQ;LOC101246554;LOC104649028;LyesC2p062;LOC101244709;LyesC2p085;LyesC2p083;LOC101261284;LOC101253342;LOC101257676;LOC101262961;LyesC2p074;LOC101254806;LOC101259223;LOC101256427;LOC101263249;LOC101257833;LOC101254513;LOC101253996;LOC101260274;CAB7;LOC101263732;LOC101249164;LOC104649438;LyesC2p076;LyesC2p072;LOC101247687;CAB4;PSBR;LOC101254882;PSBP;LOC101250650;LOC101259494;LOC101262218;HrBP1;LOC101251312;LOC543930;LOC101262255;LyesC2p053;LOC101260607;LOC101249904;LyesC2p084;LOC109120519;LOC101259028;LOC101255672;LOC101252117;LOC101264609;LyesC2p075;LyesC2p063;LOC101267919;LOC101243864;SlCOR413IM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GO:0016114</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>terpenoid biosynthetic process</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5.362768119610615e-09</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.105042741254546e-06</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4517441034661657</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.676314115524292</v>
+      </c>
+      <c r="I16" t="n">
+        <v>14.03703212738037</v>
+      </c>
+      <c r="J16" t="n">
+        <v>70</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101247014', 'LOC101244466', 'novel.915', 'dxs2', 'TPS14', 'LOC101250473', 'PHS1', 'TPS17', 'LOC101246676', 'LOC101263090', 'LOC101254591', 'CRTISO', 'LOC101266160', 'PSY2', 'LOC543694', 'GA2ox2', 'TTS2', 'LOC101249584', 'pds', 'TPS28', 'GGPS2', 'LOC101249394', 'LOC101258806', '20ox-2', 'LOC101256685', 'TPS24', 'TPS37', 'LOC101262639', 'TPS16', 'TPS31', 'CrtR-b2', 'TPS7', 'novel.572', 'LOC101257572', 'zds', 'ZEP', 'TAO3', '3OH-2', 'LOC101255340', 'MTS1', 'dxs', 'LOC104645573', 'MTS2', 'LOC100037490', 'LOC101266963', 'LOC101254497', 'TPS36', 'TPS32', 'MDC', 'LOC101249786', 'SSTLE1', 'HDS', 'LOC101260363', 'TAO2', 'TCTR1', 'TPS33', 'LOC101262198', 'TPS3', 'Psy1', 'LeNCED1', 'TPS39', 'NXD1', 'SlscADH1', 'novel.92', 'TPS38', 'NSGT1', 'NSY', 'LOC543658', 'TPS35', '3OH-1'})</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>LOC543694;Psy1;HDS;GA2ox2;TPS32;LOC101256685;zds;novel.92;ZEP;LOC101263090;TPS33;TPS37;TPS38;LOC104645573;TAO3;3OH-1;LOC101246676;LOC101254591;NXD1;LOC101257572;LOC101254497;LOC101260363;LeNCED1;LOC101266963;TPS39;PSY2;LOC101244466;LOC101262639;GGPS2;LOC101249584;MTS1;3OH-2;LOC101247014;LOC101262198;NSGT1;dxs;MTS2;TPS31;LOC101249394;LOC101249786;SSTLE1;LOC100037490;CrtR-b2;TPS35;CRTISO;LOC543658;TAO2;NSY;20ox-2;TPS14;LOC101250473;TPS24;novel.915;pds;TPS36;novel.572;MDC;TPS16;TPS7;LOC101266160;LOC101258806;TPS28;TPS17;TTS2;LOC101255340;SlscADH1;PHS1;TCTR1;TPS3;dxs2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GO:0006720</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>isoprenoid metabolic process</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7.5190876603509e-09</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.111687768935217e-06</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4350922543611901</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-2.002668857574463</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13.92633724212646</v>
+      </c>
+      <c r="J17" t="n">
+        <v>84</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101250473', 'LOC101254591', 'PSY2', 'LOC101254720', 'pds', 'LOC101262639', 'LOC101257572', 'ZEP', '3OH-2', 'LOC101255340', 'MTS2', 'LOC104645573', 'TTS2', 'LOC101254497', 'HDS', 'LOC101244523', 'TAO2', 'TPS33', 'NXD1', 'CRTISO', 'TPS35', '3OH-1', 'LOC101244466', 'dxs2', 'PHS1', 'TPS17', 'LOC101263090', 'TPS24', 'SppS', 'TPS16', 'TPS31', 'CrtR-b2', 'SlCPTBP', 'HMG2', 'MDC', 'LOC101266963', 'TPS32', 'LOC101249786', 'TPS3', 'NDPS1', 'VDE', 'novel.915', 'TPS14', 'LOC101248500', 'GA2ox2', 'LOC101249584', 'TPS28', 'GGPS2', 'LOC101258806', 'LOC101256685', 'novel.572', 'zds', 'TAO3', 'LOC100037490', 'LOC101254190', 'LOC101260363', 'Psy1', 'novel.92', 'NSGT1', 'NSY', 'LOC101247014', 'LOC101246676', 'LOC101266160', 'LOC543694', 'DXR', 'LOC101263406', 'LOC101249394', '20ox-2', 'LOC101250012', 'TPS37', 'TPS7', 'MTS1', 'dxs', 'TPS36', 'SSTLE1', 'TCTR1', 'LOC101262198', 'LeNCED1', 'TPS39', 'SlscADH1', 'TPS38', 'Z-ISO', 'HMGR', 'LOC543658'})</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>LOC543694;Psy1;HDS;GA2ox2;NDPS1;TPS32;LOC101256685;LOC101244523;zds;novel.92;ZEP;LOC101263090;TPS33;TPS37;TPS38;LOC104645573;VDE;TAO3;3OH-1;LOC101246676;LOC101254591;NXD1;LOC101257572;LOC101254497;LOC101260363;LeNCED1;LOC101266963;TPS39;PSY2;LOC101244466;LOC101262639;GGPS2;LOC101249584;MTS1;3OH-2;LOC101247014;LOC101262198;NSGT1;dxs;MTS2;TPS31;LOC101249394;LOC101254720;LOC101249786;SSTLE1;LOC100037490;CrtR-b2;HMG2;TPS35;LOC101250012;CRTISO;LOC543658;TAO2;DXR;NSY;20ox-2;TPS14;LOC101248500;LOC101250473;TPS24;novel.915;SppS;pds;HMGR;TPS36;novel.572;MDC;LOC101263406;SlCPTBP;LOC101254190;TPS16;TPS7;LOC101266160;LOC101258806;Z-ISO;TPS28;TPS17;TTS2;LOC101255340;SlscADH1;PHS1;TCTR1;TPS3;dxs2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GO:0006721</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>terpenoid metabolic process</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9.678036093793711e-09</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.013732066905868e-06</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4450504199068711</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.758832573890686</v>
+      </c>
+      <c r="I18" t="n">
+        <v>13.97128486633301</v>
+      </c>
+      <c r="J18" t="n">
+        <v>74</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101247014', 'VDE', 'LOC101244466', 'novel.915', 'dxs2', 'TPS14', 'LOC101250473', 'PHS1', 'LOC101248500', 'TPS17', 'LOC101246676', 'LOC101263090', 'LOC101254591', 'CRTISO', 'LOC101266160', 'PSY2', 'LOC543694', 'LOC101254720', 'GA2ox2', 'LOC101263406', 'TTS2', 'LOC101249584', 'pds', 'TPS28', 'GGPS2', 'LOC101249394', 'LOC101258806', '20ox-2', 'LOC101256685', 'TPS24', 'TPS37', 'LOC101262639', 'TPS16', 'TPS31', 'CrtR-b2', 'TPS7', 'novel.572', 'LOC101257572', 'zds', 'ZEP', 'TAO3', '3OH-2', 'LOC101255340', 'MTS1', 'dxs', 'LOC104645573', 'MTS2', 'LOC100037490', 'LOC101266963', 'LOC101254497', 'TPS36', 'TPS32', 'MDC', 'LOC101249786', 'SSTLE1', 'HDS', 'LOC101260363', 'TAO2', 'TCTR1', 'TPS33', 'LOC101262198', 'TPS3', 'Psy1', 'LeNCED1', 'TPS39', 'NXD1', 'SlscADH1', 'novel.92', 'TPS38', 'NSGT1', 'NSY', 'LOC543658', 'TPS35', '3OH-1'})</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>LOC543694;Psy1;HDS;GA2ox2;TPS32;LOC101256685;zds;novel.92;ZEP;LOC101263090;TPS33;TPS37;TPS38;LOC104645573;VDE;TAO3;3OH-1;LOC101246676;LOC101254591;NXD1;LOC101257572;LOC101254497;LOC101260363;LeNCED1;LOC101266963;TPS39;PSY2;LOC101244466;LOC101262639;GGPS2;LOC101249584;MTS1;3OH-2;LOC101247014;LOC101262198;NSGT1;dxs;MTS2;TPS31;LOC101249394;LOC101254720;LOC101249786;SSTLE1;LOC100037490;CrtR-b2;TPS35;CRTISO;LOC543658;TAO2;NSY;20ox-2;TPS14;LOC101248500;LOC101250473;TPS24;novel.915;pds;TPS36;novel.572;MDC;LOC101263406;TPS16;TPS7;LOC101266160;LOC101258806;TPS28;TPS17;TTS2;LOC101255340;SlscADH1;PHS1;TCTR1;TPS3;dxs2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GO:0042651</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>thylakoid membrane</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.515026954409507e-08</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7.456205156126388e-06</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2710139776683014</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-3.224212169647217</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7.049505710601807</v>
+      </c>
+      <c r="J19" t="n">
+        <v>91</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>frozenset({'PETE', 'LOC101255514', 'LOC101245729', 'LyesC2p062', 'LOC101254513', 'PsbQ', 'LyesC2p086', 'LOC101254882', 'SlCOR413IM1', 'LOC101243864', 'LyesC2p073', 'LOC101259494', 'LOC101264109', 'CAB4', 'LOC101252117', 'LOC101252603', 'LyesC2p063', 'LOC101262783', 'LOC101268227', 'SPA', 'LOC101257833', 'LyesC2p074', 'LOC101251312', 'LOC101249164', 'LOC109120519', 'PSBO', 'LyesC2p076', 'LOC101262260', 'LOC101249002', 'LOC101268563', 'LOC101260274', 'LyesC2p082', 'LOC101260607', 'LOC101249904', 'LOC101262218', 'LOC101264255', 'LyesC2p053', 'LyesC2p085', 'LOC101267006', 'LyesC2p075', 'LyesC2p069', 'LOC101259028', 'LOC101252151', 'VDE', 'MSH1', 'LOC101246554', 'LOC101250650', 'LOC101253342', 'LOC101253996', 'psbS', 'LyesC2p070', 'HrBP1', 'LOC101261284', 'LOC101245880', 'CAB9', 'LOC101257676', 'LOC104649438', 'LOC101268832', 'SlFBA4', 'LOC101256944', 'PSBR', 'LOC101267919', 'LOC543932', 'LOC101245704', 'LOC101263249', 'LOC101255672', 'LOC101255525', 'LOC101254806', 'LOC101264609', 'LOC101244709', 'LOC101263132', 'LyesC2p072', 'LOC101259223', 'LyesC2p083', 'OEE1', 'LOC101263054', 'LOC101256427', 'LOC543930', 'LOC101268560', 'LOC104649028', 'LyesC2p089', 'LyesC2p084', 'LOC101263732', 'LOC101265555', 'LOC101262961', 'LOC101262255', 'LyesC2p081', 'CAB7', 'PSBP', 'LOC101247687', 'VKOR'})</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>LOC101262260;LOC101265555;OEE1;SPA;LOC101252151;LOC101249002;LyesC2p070;CAB9;LyesC2p086;PETE;LOC101245880;LOC101245729;LOC543932;PSBO;LyesC2p089;LyesC2p081;LyesC2p073;LOC101263054;LOC101262783;LOC101268832;psbS;LOC101268227;LOC101255525;LOC101268560;VDE;LOC101245704;SlFBA4;LOC101264109;LOC101264255;LOC101267006;LOC101255514;LOC101256944;LyesC2p082;LyesC2p069;LOC101268563;LOC101252603;LOC101263132;VKOR;PsbQ;LOC101246554;LOC104649028;LyesC2p062;LOC101244709;LyesC2p085;LyesC2p083;LOC101261284;LOC101253342;LOC101257676;LOC101262961;LyesC2p074;LOC101254806;LOC101259223;LOC101256427;LOC101263249;LOC101257833;LOC101254513;LOC101253996;LOC101260274;CAB7;LOC101263732;LOC101249164;LOC104649438;LyesC2p076;LyesC2p072;LOC101247687;CAB4;PSBR;LOC101254882;PSBP;LOC101250650;LOC101259494;LOC101262218;HrBP1;LOC101251312;LOC543930;LOC101262255;LyesC2p053;LOC101260607;LOC101249904;LyesC2p084;LOC109120519;LOC101259028;LOC101255672;LOC101252117;LOC101264609;LyesC2p075;LyesC2p063;LOC101267919;LOC101243864;MSH1;SlCOR413IM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GO:0006082</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>organic acid metabolic process</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2.348573942654788e-08</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.100810157978623e-05</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2812894393625487</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-3.468230009078979</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12.817946434021</v>
+      </c>
+      <c r="J20" t="n">
+        <v>242</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH2B7d', 'novel.168', 'LOC101258525', 'LOC101256649', 'LOC101250473', 'LOC101245297', 'LOC101263085', 'ME2', 'LOC101254591', 'SlGGP-LIKE', 'LEAS1', 'LOC101249193', 'LOC101267118', 'SlFBA2', 'LOC112940921', 'LOC101256592', 'LOC101254720', 'LOC101245952', 'LOC101245370', 'LOC101255271', 'LOC101256077', 'LOC100134915', 'AOS3', 'LOC104648641', 'LOC101258131', 'SlFBA3', 'SlFRK3', 'SlADH11A4a', 'PIIGLB1', 'PAL3', 'HXK3', 'PDH', 'ZEP', '3OH-2', 'LOC101263879', 'LOC101255340', 'SK', 'LOC101250354', 'LOC104644402', 'LOC104645573', 'MIOX', 'LOC101254497', 'LOC101264480', 'HDS', 'TAO2', 'SlFBA8', 'PRO2', 'SlALDH6B2', 'LOC101250058', 'LOC101258391', 'SlDMR6-1', 'SNF1', 'LOC101264863', 'LOC101258461', 'OAT', 'novel.966', 'SCOA', '3OH-1', 'LOC101254137', 'gdh1', 'hdc', 'MKS1b', 'SSADH', 'LOC101248511', 'LOC101252977', 'PHS1', 'LOC101259236', 'LOC101259572', 'PP2Ac1', 'THM16', 'LOC101263535', 'LOC101252681', 'LOC101258787', 'MKS1d', 'LOC101249057', 'AOS2', 'LOC101264873', 'LOC101257319', 'LOC101266918', 'PAL2', 'WRKYIId', 'MKS1e', 'LOC101250481', 'HPL', 'LOC101260607', 'SlALDH2B7a', 'MKK2', 'LOC101254597', 'LOC101255411', 'LOC101244614', 'LOC101256694', 'TPS24', 'MST1', 'LysRS', 'LOC101252202', 'TomloxC', 'LOC101256529', 'LOC101267103', 'NAOD', 'NR', 'LOC778303', 'LOC101249786', 'LOC101254281', 'nii1', 'LOC101244007', 'LOC544276', 'LOC101264132', 'LOC101251091', 'LOC101254608', 'opr3', 'LOC101252192', 'PP2Ac2', 'LOC101247770', 'LOC101267184', 'LOC101252738', 'LOC101268347', 'LOC101259725', 'LOC101259689', 'LOC101244882', 'LOC101261578', 'LOC101252453', 'ACS2', 'LOC101266950', 'LOC104646631', 'LOC101247693', 'novel.915', 'GS1', 'LOC101251350', 'GABA-TP2', 'LOC101259235', 'LOC101246995', 'LOC101258355', 'LOC109120859', 'novel.312', 'LOC101257261', 'SlFBA1', 'GA2ox2', 'PGH1', 'LOC101250561', 'LOC101267663', 'PAL5', 'SlMYB21', 'OTC', 'LOC101245553', 'LOC101254439', 'LOC101252161', 'ACS6', 'LOC101263817', 'LOC101244092', 'THM27', 'novel.879', 'LOC101256685', 'SlFBA6', 'LOC107648852', 'LOC101246116', 'LOC101245480', 'NAGK', 'LOC101251311', 'LOC101263606', 'TAO3', 'LOC543920', 'LOC101251816', 'LOC101250807', 'MST2', 'LOC101258830', 'LOC101250791', 'LOC101260363', 'SlADH12A1', 'LOC101261642', 'ACS4', 'ME1', 'LOC101268510', 'NRT2.2', 'LOC101257857', 'HXK4', 'mMDH2', 'LOC101262091', 'LOC101250891', 'LOC101258079', 'novel.92', 'LOC101055519', 'MKS1a', 'LOC101260990', 'LOC101246283', 'LOC101247014', 'GME1', 'LOC104648010', 'LOC101248029', 'LOC101246396', 'SIZ1', 'LOC101244469', 'LOC778326', 'LOC101254848', 'LOC101250164', 'LOC101252583', 'LOC101249935', 'LOC101267346', 'TomloxE', 'OPR1', 'LOC101250586', 'PAT', 'LOC101254332', 'LOC101255874', 'novel.105', 'LOC543694', 'LOC101266174', 'LOC101267503', 'LOC101267959', 'LOC101247833', 'DXR', 'LOC101263406', 'LOC101248052', 'LOC101262503', 'LOC101254112', 'adc1', 'LOC101249671', 'ODC', 'LOC101247891', 'Slalpha-kGDH', 'LOC101247828', 'LOC101247914', '20ox-2', 'Sip1', 'LOC101252466', 'NAOAT', 'LOC101244691', 'mdh', 'LOC101259366', 'novel.113', 'LOC101253805', 'SlFBA7', 'LOC101247047', 'mMDH1', 'TCTR1', 'LOC101262198', 'LeNCED1', 'LOC101258500', 'LOC101248790', 'LOC101256513', 'novel.706', 'LOXB', 'LOC543658'})</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>LOC543694;LOC101250791;LOC101258500;NAOD;HDS;GA2ox2;LOC101247891;LOC101252161;LOC101263817;SlFBA1;LOC778303;LOC101256685;PP2Ac2;MKS1e;LOC101244691;LOC101251816;LOC104646631;SlGGP-LIKE;MKS1d;LOC101250481;LOC101247828;LOC101258131;LOC101250807;LOC101247047;LOC101249671;LOC101263606;LEAS1;LOC101258461;LOC104648641;novel.92;LOC101246116;LOC101249935;LOC101263085;HXK4;ZEP;LOC101252192;LOC101256077;adc1;GABA-TP2;PGH1;LOC101267118;LOC101250058;LOC101248511;LOC101252453;LOC101262503;HXK3;LOC101245553;SlMYB21;novel.113;LOC101252202;mdh;LOC101251091;LOC101249193;LOC104645573;LOC101256592;TAO3;LOC101261578;LOC101267503;MIOX;ODC;3OH-1;LOC101245952;LOC101247770;LOC101259725;SIZ1;LOC101254591;LOC101259366;ACS6;LOC101255271;LOC112940921;TomloxE;LysRS;GME1;SlALDH2B7a;LOC101254497;LOC101260363;LOC101263879;LOC101253805;LeNCED1;LOC101251350;SlFBA3;LOC101250561;THM16;MST2;LOC101244007;LOC101264863;LOC101259572;ACS2;LOC101264873;LOC101249057;LOC101254439;LOC101267663;LOC101258079;NR;LOC101251311;LOC101268510;LOC101245297;LOC101254608;LOC101256694;LOC101257319;Slalpha-kGDH;PAT;LOC101250164;SSADH;PP2Ac1;LOC101250354;SlADH11A4a;3OH-2;SlFBA7;LOC101266950;LOC101247014;LOC101257261;novel.966;LOC101259236;LOC100134915;LOC101262198;PRO2;LOC101258355;LOC101254720;LOC101249786;SlADH12A1;SlADH2B7d;SlFRK3;ACS4;LOC101247914;SlALDH6B2;SlFBA6;MKS1a;LOC101247693;LOC101254281;LOC101244882;ME1;LOC101260990;LOC101248029;LOC101244092;novel.879;LOC101254137;LOC101248052;mMDH1;LOC101266918;LOC101254332;LOC101254597;ME2;Sip1;PAL3;SK;LOC543658;LOC101055519;LOC104648010;TAO2;novel.105;MKK2;DXR;LOC101252583;20ox-2;NRT2.2;LOC101258787;LOC101250586;AOS2;PAL5;LOC101256529;AOS3;PAL2;LOC101250473;LOC101259235;TPS24;LOC101255411;hdc;LOC101246396;LOC107648852;LOC101266174;LOC101252977;LOC101256649;LOC101259689;LOC101244469;SlDMR6-1;SlFBA2;LOC101267346;LOC101261642;LOC101248790;OPR1;LOXB;LOC101268347;LOC544276;mMDH2;MST1;OTC;LOC101264132;novel.915;LOC101264480;LOC101267103;LOC101252466;LOC101267184;LOC109120859;LOC778326;OAT;SlFBA8;LOC101244614;HPL;LOC101254848;SCOA;WRKYIId;MKS1b;SNF1;LOC101263406;novel.168;LOC101257857;nii1;LOC101245370;LOC101258391;NAGK;LOC101256513;NAOAT;gdh1;LOC101260607;LOC543920;LOC101247833;PDH;LOC101252738;LOC101267959;LOC101262091;THM27;novel.706;LOC101250891;LOC101245480;LOC101252681;GS1;LOC101263535;LOC101246283;TomloxC;PIIGLB1;novel.312;LOC101255340;LOC101246995;LOC101254112;LOC104644402;LOC101258525;PHS1;TCTR1;LOC101258830;opr3;LOC101255874</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GO:0046527</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>glucosyltransferase activity</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3.012912579563768e-08</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.348004478211189e-05</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1727798665723622</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.69697380065918</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10.87780475616455</v>
+      </c>
+      <c r="J21" t="n">
+        <v>58</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101263151', 'XTH16', 'GAME3', 'LOC101260997', 'tXET-B2', 'XTH5', 'LOC101055573', 'LOC101255510', 'LOC101260093', 'XTH9', 'LOC101263090', 'LOC101259221', 'GAME1', 'LOC101254402', 'LOC101255377', 'LOC101251337', 'SlGGP-LIKE', 'SlUGT75C1', 'LOC101265927', 'LOC101256154', 'LOC101249176', 'ert1b', 'twi1', 'LOC101268453', 'sus3', 'LOC101248661', 'LOC101252007', 'LOC100529103', 'XET2', 'tXET-B1', 'sps', 'LOC101261871', 'LOC101256157', 'LOC101246612', 'LOC101258806', 'LOC543511', 'LOC101258947', 'XTH1', 'LOC101258117', 'XTH6', 'LOC101244237', 'SUS4', 'LOC101251018', 'LOC101251036', 'XET4', 'LOC101247047', 'gtsatom', 'XTH7', 'LOC101259617', 'XTH3', 'LOC101268254', 'LOC101250431', 'LOC101250058', 'LOC101253864', 'novel.706', 'LOC101258702', 'novel.70', 'LOC101256574'})</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>LOC543511;LOC101268254;LOC101251036;LOC101259617;SlGGP-LIKE;LOC101265927;LOC101247047;XTH7;XTH5;tXET-B2;LOC101055573;LOC101263090;gtsatom;LOC101250058;LOC101251337;tXET-B1;sus3;LOC101254402;LOC101251018;LOC101248661;LOC101255510;ert1b;LOC101260997;SUS4;LOC101256157;LOC101250431;XTH6;XTH3;twi1;GAME1;LOC101255377;XET2;LOC101246612;LOC101253864;LOC101263151;LOC101261871;LOC101259221;LOC101260093;LOC101244237;LOC101256574;novel.70;XTH9;LOC101258702;GAME3;XTH16;LOC101252007;LOC100529103;LOC101256154;XET4;LOC101268453;LOC101258117;SlUGT75C1;XTH1;LOC101258806;novel.706;LOC101258947;LOC101249176;sps</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GO:0009835</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fruit ripening</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6.906734353112214e-08</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.955782010334066e-05</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.05300211185642364</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.702387094497681</v>
+      </c>
+      <c r="I22" t="n">
+        <v>12.00972557067871</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>frozenset({'XTH16', 'tXET-B2', 'TAPG5', 'ACO1', 'XTH9', 'E8-6', 'TAPG1', 'SlUGT75C1', 'LOC101265927', 'LOC101254720', 'PME2.1', 'TAPG2', 'ACO4-like', 'PE1', 'PS-2', 'tXET-B1', 'ACS6', 'TAPG4', 'LOC101245697', 'ACO3', 'ACS2', 'TPG6', 'LOC101251036', 'PG2', 'ODD', 'ACS4', 'LeNCED1', 'novel.70', 'ACO4'})</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>LOC101251036;LOC101265927;tXET-B2;E8-6;TAPG2;ACS6;LeNCED1;TPG6;tXET-B1;ACS2;ACO4;LOC101254720;ACO3;ACS4;ACO1;ACO4-like;TAPG1;PG2;PS-2;novel.70;XTH9;XTH16;TAPG5;LOC101245697;PE1;SlUGT75C1;PME2.1;ODD;TAPG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GO:0016798</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>hydrolase activity, acting on glycosyl bonds</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7.815240229938313e-08</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.205225399303451e-05</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1686859056061009</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.516648650169373</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.27792167663574</v>
+      </c>
+      <c r="J23" t="n">
+        <v>101</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>frozenset({'XTH16', 'XYL1', 'tXET-B2', 'XTH5', 'TAPG5', 'PGcat', 'Man4', 'LOC100529103', 'LIN8', 'LOC543511', 'LOC101266643', 'LOC101257783', 'LOC101247340', 'LOC101262778', 'LOC101244370', 'LOC101267869', 'CHI9', 'cellulase', 'LOC101254249', 'lin5', 'LOC101258151', 'TBG3', 'LOC101256574', 'SlArf_Xyl2', 'LOC101254891', 'LOC101263652', 'LOC101252138', 'LOC101251335', 'CHI3', 'XTH9', 'TAPG1', 'LOC101265793', 'LOC101258669', 'Wiv-1', 'PS-2', 'XTH6', 'SlArf_Xyl1', 'LOC101254239', 'TPG6', 'Cel2', 'XTH7', 'PG2', 'LOC104645427', 'SlArf_Xyl3', 'novel.1103', 'tEG3', 'LOC101267699', 'LOC101248047', 'LOC101249056', 'LOC543987', 'LOC101263369', 'LOC101254849', 'LOC101258638', 'TAPG2', 'sfr2', 'LOC101261972', 'TAPG4', 'LeMAN2', 'LOC101246713', 'bmy3', 'SlArf_Xyl4', 'LOC101266770', 'LOC101256554', 'CHI17', 'LOC101252835', 'LOC101253853', 'LOC101248575', 'LOC101268410', 'TBG6', 'LOC112941971', 'CHI14', 'TBG7', 'novel.622', 'LOC101265509', 'LOC101265927', 'LOC101264974', 'LOC101246977', 'LOC101267232', 'XET2', 'tXET-B1', 'LOC101261871', 'ARF1', 'AI', 'MAN1', 'XTH1', 'AGAL', 'LOC101261650', 'TBG1', 'LOC101260647', 'TBG2', 'XET4', 'LOC101263519', 'XTH3', 'LOC101251735', 'LOC101265800', 'LOC101267766', 'XOPG1', 'TBG5', 'TLOG1', 'LOC101247546', 'LOC101246083'})</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>AI;LOC101252138;LOC543511;tEG3;LOC101263652;LOC101267699;SlArf_Xyl3;LOC101265927;CHI9;XTH7;LOC112941971;LOC101254891;XTH5;tXET-B2;XYL1;LOC101257783;LOC101265800;LOC101261650;MAN1;LOC543987;LOC101258669;TBG6;TAPG2;PGcat;LOC101246713;sfr2;TLOG1;LOC101254239;LOC101247340;TBG3;LOC101247546;TPG6;CHI17;tXET-B1;LOC101248575;lin5;CHI14;ARF1;bmy3;LOC101263519;LOC101254249;TBG5;Wiv-1;LOC101251735;TBG2;cellulase;XTH6;AGAL;XTH3;LOC101268410;CHI3;TBG7;Cel2;LOC101256554;LOC101265793;SlArf_Xyl4;novel.622;TAPG1;XET2;LOC101266770;PG2;LOC101261871;LOC101267869;LOC101267232;LOC101264974;LOC101256574;PS-2;XTH9;LOC101263369;Man4;LOC101262778;LOC101251335;LOC101267766;novel.1103;XTH16;LOC104645427;LOC101246977;LOC101246083;XOPG1;LOC100529103;TAPG5;LOC101258638;LOC101252835;LOC101266643;LOC101260647;XET4;LOC101258151;SlArf_Xyl1;LOC101254849;LeMAN2;LOC101253853;XTH1;SlArf_Xyl2;LOC101248047;LIN8;LOC101244370;LOC101249056;TBG1;TAPG4;LOC101265509;LOC101261972</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GO:0010315</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>auxin export across the plasma membrane</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.33950946284944e-07</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5.273916657130814e-05</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1767563691577655</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-3.435880184173584</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10.29357624053955</v>
+      </c>
+      <c r="J24" t="n">
+        <v>12</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>frozenset({'PIN2', 'LOC101249663', 'PIN3', 'PIN9', 'PIN10', 'LOC100527965', 'LOC101248505', 'PIN5', 'PIN7', 'PIN4', 'PIN8', 'PIN6'})</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PIN2;PIN10;PIN9;PIN8;PIN6;PIN5;PIN7;PIN3;LOC100527965;LOC101249663;LOC101248505;PIN4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GO:0010329</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>auxin efflux transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3.217867180909268e-07</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0001218210256218843</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1774775988847222</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.416169881820679</v>
+      </c>
+      <c r="I25" t="n">
+        <v>10.15438556671143</v>
+      </c>
+      <c r="J25" t="n">
+        <v>12</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>GO:0080161</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>frozenset({'PIN2', 'PIN3', 'PIN9', 'PIN10', 'LOC100527965', 'LOC101256077', 'PIN5', 'MDR1', 'PIN7', 'PIN4', 'PIN8', 'PIN6'})</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>PIN2;PIN10;PIN9;LOC101256077;PIN8;PIN6;PIN5;PIN7;PIN3;LOC100527965;PIN4;MDR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GO:0009526</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>plastid envelope</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3.845032021198986e-07</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0001401727784617097</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.1800337217875952</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.11921215057373</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7.567234516143799</v>
+      </c>
+      <c r="J26" t="n">
+        <v>158</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>frozenset({'PETE', 'LOC101255514', 'LOC101249846', 'LOC101263085', 'LOC101245729', 'LyesC2p062', 'LOC101254513', 'PsbQ', 'LOC101244306', 'SlFBA2', 'LyesC2p086', 'LOC101254882', 'LOC101256592', 'SlCOR413IM1', 'LOC101260852', 'LOC101255271', 'LOC101256077', 'LOC101243864', 'LyesC2p073', 'LOC101259494', 'SlFBA3', 'LOC101264109', 'CAB4', 'LOC101252117', 'LOC101255583', 'LOC101252603', 'LyesC2p063', 'LOC101262783', 'LOC101268227', 'SPA', 'LOC101264480', 'HDS', 'MDHAR', 'LOC101244176', 'LyesC2p074', 'LOC101257833', 'pGlcT1', 'LOC101258970', 'CRTISO', 'LOC101251312', 'LOC101260856', 'LOC101244466', 'LOC101249164', 'LOC109120519', 'PSBO', 'LOC101245518', 'LOC101248511', 'LyesC2p076', 'LOC101252977', 'LOC101254229', 'LOC101262260', 'LOC101249002', 'SlHDA3', 'LOC101245293', 'LOC101268563', 'LOC101260274', 'VGT1', 'LyesC2p082', 'AOS2', 'LOC101260607', 'LOC101249904', 'LOC101253221', 'LOC101262218', 'HPL', 'LOC101264255', 'LyesC2p053', 'LyesC2p085', 'TPS24', 'LOC544217', 'LOC101267006', 'CrtR-b2', 'LOC101252202', 'LyesC2p075', 'LOC101258297', 'novel.1062', 'LOC101266963', 'LyesC2p069', 'LOC101259028', 'LOC101265217', 'LOC101055526', 'LOC101252151', 'SlTIP2-2', 'VDE', 'LOC101246554', 'LOC101250650', 'LOC101253342', 'LOC101248500', 'LOC101246995', 'LOC101253996', 'psbS', 'LyesC2p070', 'HrBP1', 'SlFBA1', 'pGlcT3', 'LOC101266486', 'LOC101261284', 'LOC101245880', 'sfr2', 'LOC101248098', 'sos1', 'CAB9', 'LOC101257676', 'LOC104649438', 'LOC101264583', 'LOC101268832', 'SlFBA4', 'LOC101256944', 'PSBR', 'LOC101267919', 'novel.82', 'LOC543932', 'LOC101245704', 'LOC101263249', 'novel.817', 'LOC101244516', 'LOC101255525', 'LOC101254806', 'LOC101257857', 'LOC101255672', 'TOC75-III', 'LOC101264609', 'LOC101244709', 'LOC101250405', 'LOC101263132', 'LyesC2p072', 'LOC101259223', 'LyesC2p083', 'LOC101265242', 'OEE1', 'LOC101263054', 'LOC101246143', 'LOC101256427', 'LOC543930', 'LOC101268560', 'TIL_', 'LOC101250586', 'LOC104649028', 'SlVTE5', 'TIL', 'LyesC2p089', 'LyesC2p084', 'SlVP2', 'LOC101265790', 'ELIP', 'LOC101263732', 'LOC101265555', 'LOC101262961', 'LOC100037730', 'pGlcT4', 'LOC101262255', 'LyesC2p081', 'CAB7', 'LOC101252931', 'PSBP', 'LOC101247687', 'LOC101256513', 'VKOR', 'Z-ISO'})</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>LOC101262260;LOC101250405;LOC101265555;HDS;OEE1;LOC101265790;SPA;LOC101252151;LOC101249002;LyesC2p070;CAB9;LyesC2p086;SlFBA1;PETE;LOC101245880;LOC101245729;LOC543932;PSBO;LyesC2p089;LOC101265217;LyesC2p081;LOC101244176;LOC101254229;ELIP;LOC101249846;LOC101263085;LyesC2p073;LOC101263054;LOC101256077;LOC101262783;LOC101268832;psbS;LOC101248511;LOC101258297;LOC101268227;LOC101255525;LOC101268560;LOC101252202;pGlcT3;LOC101256592;VDE;LOC101245704;LOC101244516;novel.82;SlFBA4;sfr2;LOC101258970;LOC101255271;LOC101248098;LOC101252931;LOC101264109;LOC101264255;LOC101267006;LOC101255514;LOC101256944;SlFBA3;LyesC2p082;LOC101245293;LOC101266963;LyesC2p069;LOC544217;LOC101265242;LOC101244466;MDHAR;LOC101268563;LOC101252603;LOC101263132;VKOR;LOC101246143;PsbQ;LOC101246554;LOC101245518;LOC104649028;pGlcT4;LyesC2p062;LOC101244709;LyesC2p085;LOC101266486;LyesC2p083;LOC101261284;TIL_;SlVP2;LOC101055526;LOC101253342;LOC101257676;SlTIP2-2;CrtR-b2;LOC101262961;sos1;LyesC2p074;LOC101254806;LOC101259223;LOC101256427;LOC101263249;VGT1;LOC101257833;LOC101254513;CRTISO;LOC101253996;LOC101260274;CAB7;LOC101244306;LOC101253221;LOC101250586;LOC101263732;LOC101249164;AOS2;LOC104649438;LyesC2p076;novel.817;LOC101248500;LOC101260852;TPS24;LyesC2p072;LOC101247687;LOC100037730;LOC101252977;CAB4;novel.1062;SlFBA2;PSBR;LOC101254882;PSBP;LOC101264480;LOC101250650;LOC101259494;LOC101262218;HPL;HrBP1;LOC101251312;LOC101257857;LOC101255583;LOC543930;pGlcT1;LOC101262255;LOC101256513;LyesC2p053;TOC75-III;LOC101260607;LOC101260856;Z-ISO;LOC101249904;LyesC2p084;LOC109120519;SlHDA3;LOC101259028;LOC101255672;LOC101252117;LOC101264609;LyesC2p075;LyesC2p063;TIL;LOC101267919;LOC101243864;LOC101246995;SlCOR413IM1;LOC101264583;SlVTE5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GO:0006629</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lipid metabolic process</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4.030317347740513e-07</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.000140284913206643</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.1369949167831766</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2.748182535171509</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13.60379123687744</v>
+      </c>
+      <c r="J27" t="n">
+        <v>245</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH2B7d', 'novel.168', 'LOC101258525', 'LOC101250473', 'LOC101245297', 'LOC101263085', 'LOC101254591', 'PLC7', 'PLDb2', 'PSY2', 'LOC112940921', 'LOC101254720', 'LOC101244514', 'LOC101245370', 'LOC101267665', 'LOC100134915', 'pds', 'LOC101246731', 'AOS3', 'LOC101267522', 'LOC101257105', 'TPLD', 'MKS2c', 'SlFRK3', 'LOC101263783', 'PIIGLB1', 'LOC101251516', 'MKS2b', 'LOC101262639', 'LOC101260469', 'LOC101257572', 'ZEP', 'LOC104649012', '3OH-2', 'LOC101260468', 'LOC101255340', 'LOC101250354', 'MTS2', 'LOC104645573', 'TTS2', 'LOC101260812', 'LOC101254497', 'HDS', 'LOC101244523', 'TAO2', 'TPS33', 'LOC101264777', 'CYP724B2', 'NXD1', 'LOC101258506', 'SNF1', 'LOC101266611', 'TPS35', 'CRTISO', '3OH-1', 'LOC101263151', 'LOC101244466', 'dxs2', 'LOC101264840', 'MKS1b', 'LOC101248511', 'LOC101249518', 'PHS1', 'LOC101259139', 'TPS17', 'LOC101263090', 'LOC101259572', 'PP2Ac1', 'LOC101267934', 'LOC101265793', 'LOC101264879', 'LOC101263535', 'LOC101250011', 'LOC101250696', 'MKS1d', 'LOC101249057', 'LOC101252788', 'AOS2', 'LOC101260607', 'SlGPAT6', 'LOC101250481', 'MKS1e', 'HPL', 'LOC101246303', 'SlALDH2B7a', 'PLDa1', 'LOC101249884', 'LOC101254597', 'LOC101255411', 'LOC101255461', 'LOC101244831', 'LOC101256694', 'TPS24', 'SppS', 'TPS16', 'TPS31', 'LOC101251962', 'CrtR-b2', 'LOC101252202', 'TomloxC', 'SlCPTBP', 'PLDa2', 'HMG2', 'MDC', 'novel.729', 'LOC101266963', 'TPS32', 'LOC101249786', 'TPS3', 'LOC101264132', 'opr3', 'LOC101250235', 'LOC101247770', 'PP2Ac2', 'LOC101261928', 'LOC101252738', 'LOC101246651', 'LOC101249210', 'NDPS1', 'LOC101250128', 'PLDb1', 'LOC101261578', 'LOC101252453', 'LOC101266950', 'VDE', 'novel.915', 'LOC101257528', 'LOC101246390', 'MKS2', 'TPS14', 'LOC101248500', 'LOC101259437', 'LOC101246995', 'novel.1112', 'LOC101258355', 'LOC109120859', 'LOC101251763', 'LOC101246730', 'GA2ox2', 'LOC101250561', 'SlMYB21', 'LOC101249584', 'LOC101245553', 'TPS28', 'novel.93', 'LOC101252161', 'GGPS2', 'SD1', 'LOC101244092', 'LOC101258806', 'THM27', 'novel.879', 'LOC101256685', 'LOC101261489', 'LOC107648852', 'LOC101255353', 'LOC101251311', 'LOC101263606', 'novel.572', 'zds', 'TAO3', 'LOC101254424', 'LOC100037490', 'LOC101250807', 'LOC101250289', 'LOC101268146', 'LOC101254190', 'LOC101245704', 'LOC101260363', 'LOC101245708', 'LOC101268510', 'Psy1', 'CYP85A1', 'novel.92', 'LOC101250517', 'NSGT1', 'NSY', 'MKS1a', 'LOC101260990', 'LOC101245358', 'LOC101263181', 'LOC101247014', 'LOC101255254', 'LOC101246396', 'LOC101266652', 'LOC101246264', 'LOC101246676', 'LOC101250164', 'LOC101252583', 'GAME1', 'TomloxE', 'TIL_', 'OPR1', 'LOC101250586', 'LOC104646084', 'LOC101266160', 'LOC101247110', 'LOC101255874', 'novel.105', 'LOC543694', 'LOC101266174', 'LOC101267503', 'LOC101249983', 'LOC101267959', 'DXR', 'LOC101263406', 'TIL', 'LOC101262503', 'LOC101252025', 'CYP734A8', 'LOC101258705', 'THM6', 'LOC101268830', 'LOC101249394', 'LOC101247828', '20ox-2', 'LOC101250012', 'TPS37', 'Sip1', 'LOC101253180', 'LOC101244691', 'LOC101245616', 'TPS7', 'novel.113', 'LOC101247250', 'MTS1', 'dxs', 'TPS36', 'SSTLE1', 'LOC101261405', 'TCTR1', 'LOC101262198', 'LeNCED1', 'LOC101258273', 'LOC101263269', 'TPS39', 'LOC101266485', 'LOC101248790', 'TPS38', 'LOC101256513', 'LOXB', 'HMGR', 'Z-ISO', 'SlscADH1', 'LOC543658'})</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>LOC543694;Psy1;SlGPAT6;LOC101247250;HDS;GA2ox2;LOC101252161;SD1;NDPS1;TPS32;LOC101256685;PP2Ac2;MKS1e;LOC101244691;MKS1d;LOC101250481;LOC101247828;LOC101244523;LOC101250807;LOC101253180;novel.1112;LOC101251962;LOC101263606;LOC101252025;LOC101258273;LOC101264840;zds;novel.92;LOC101261405;THM6;LOC101263085;LOC101268830;ZEP;LOC101263090;MKS2b;TPS33;LOC101248511;LOC101263269;LOC101252453;LOC101262503;LOC101266652;LOC101245553;TPS37;SlMYB21;novel.113;LOC101257528;TPS38;LOC101252202;LOC104645573;VDE;LOC101246264;TAO3;LOC101245704;LOC101261578;LOC101267503;LOC101250696;3OH-1;LOC101247770;LOC101247110;LOC101246676;LOC101254591;NXD1;LOC112940921;LOC101257572;LOC101258506;TomloxE;SlALDH2B7a;MKS2;PLC7;LOC101244831;LOC101254497;LOC101260363;LeNCED1;CYP734A8;LOC101259139;LOC101250561;LOC101266963;LOC101259572;LOC101250517;TPS39;PSY2;LOC101249057;LOC101244466;LOC101262639;LOC101260468;CYP724B2;LOC101251311;LOC101246390;LOC101263783;LOC101268510;LOC101245297;LOC101256694;LOC101261928;GGPS2;LOC101250164;PP2Ac1;LOC101249584;MTS1;LOC101250354;LOC101249518;3OH-2;LOC101249210;LOC101266950;LOC101247014;LOC101246303;LOC101250011;LOC101266485;LOC100134915;LOC101262198;NSGT1;dxs;LOC101258355;MTS2;TPS31;LOC101249394;LOC101254720;LOC101249786;LOC101261489;SSTLE1;TIL_;SlADH2B7d;SlFRK3;LOC101251516;LOC100037490;LOC101252788;CrtR-b2;MKS1a;LOC101265793;HMG2;LOC101246651;GAME1;LOC101255254;LOC101260990;LOC101244092;novel.879;LOC101263151;TPS35;LOC101255353;LOC101249983;LOC101254597;Sip1;PLDa2;LOC101250012;CRTISO;LOC543658;LOC101267665;TAO2;novel.105;LOC101244514;DXR;NSY;LOC101252583;20ox-2;LOC101260812;LOC101264777;LOC101266611;LOC101250586;AOS2;LOC101267934;LOC101250235;LOC101250128;TPS14;AOS3;LOC101248500;LOC101246730;LOC101250473;TPS24;LOC101257105;LOC101255411;LOC101246396;LOC107648852;LOC101266174;TPLD;LOC101248790;OPR1;LOXB;LOC101245358;LOC101263181;novel.93;LOC104646084;LOC101264132;novel.915;MKS2c;SppS;pds;HMGR;TPS36;novel.572;LOC101246731;LOC109120859;LOC101259437;MDC;HPL;LOC101249884;MKS1b;SNF1;LOC101263406;LOC101245616;novel.168;SlCPTBP;LOC101264879;LOC101255461;LOC101254190;TPS16;LOC101250289;LOC101268146;LOC101245370;LOC101267522;LOC104649012;LOC101256513;CYP85A1;LOC101260607;PLDa1;TPS7;LOC101266160;LOC101258806;Z-ISO;TPS28;LOC101252738;LOC101267959;TPS17;TTS2;PLDb2;THM27;LOC101254424;LOC101251763;novel.729;LOC101263535;TIL;TomloxC;PIIGLB1;LOC101258705;PLDb1;LOC101260469;LOC101255340;LOC101246995;SlscADH1;LOC101258525;PHS1;TCTR1;TPS3;dxs2;opr3;LOC101245708;LOC101255874</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GO:0042170</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>plastid membrane</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4.133152984854869e-07</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.000140284913206643</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1314395917309235</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-2.992159366607666</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.19016695022583</v>
+      </c>
+      <c r="J28" t="n">
+        <v>131</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>frozenset({'PETE', 'LOC101255514', 'LOC101263085', 'LOC101245729', 'LyesC2p062', 'LOC101254513', 'PsbQ', 'LOC101244306', 'LyesC2p086', 'LOC101254882', 'SlCOR413IM1', 'LOC101243864', 'LyesC2p073', 'LOC101259494', 'LOC101264109', 'CAB4', 'LOC101252117', 'LOC101255583', 'LOC101252603', 'LyesC2p063', 'LOC101262783', 'LOC101268227', 'SPA', 'LOC101257833', 'LyesC2p074', 'LOC101244176', 'pGlcT1', 'LOC101258970', 'CRTISO', 'LOC101251312', 'LOC101260856', 'LOC101244466', 'LOC101249164', 'LOC109120519', 'PSBO', 'LOC101245518', 'LyesC2p076', 'LOC101254229', 'LOC101262260', 'LOC101249002', 'LOC101268563', 'LOC101260274', 'VGT1', 'LyesC2p082', 'AOS2', 'LOC101260607', 'LOC101249904', 'LOC101253221', 'LOC101262218', 'HPL', 'LOC101264255', 'LyesC2p053', 'LyesC2p085', 'TPS24', 'LOC101267006', 'CrtR-b2', 'LOC101252202', 'LyesC2p075', 'LOC101258297', 'novel.1062', 'LOC101266963', 'LyesC2p069', 'LOC101259028', 'LOC101265217', 'LOC101055526', 'LOC101252151', 'VDE', 'LOC101246554', 'LOC101250650', 'LOC101253342', 'LOC101248500', 'LOC101253996', 'psbS', 'LyesC2p070', 'HrBP1', 'pGlcT3', 'LOC101261284', 'LOC101245880', 'sfr2', 'CAB9', 'LOC101257676', 'LOC104649438', 'LOC101268832', 'SlFBA4', 'LOC101256944', 'PSBR', 'LOC101267919', 'novel.82', 'LOC543932', 'LOC101245704', 'LOC101263249', 'novel.817', 'LOC101255672', 'LOC101255525', 'LOC101254806', 'TOC75-III', 'LOC101264609', 'LOC101244709', 'LOC101263132', 'LyesC2p072', 'LOC101259223', 'LyesC2p083', 'OEE1', 'LOC101263054', 'LOC101246143', 'LOC101256427', 'LOC543930', 'LOC101268560', 'TIL_', 'LOC101250586', 'LOC104649028', 'SlVTE5', 'TIL', 'LyesC2p089', 'LyesC2p084', 'LOC101265790', 'ELIP', 'LOC101263732', 'LOC101265555', 'LOC101262961', 'LOC100037730', 'pGlcT4', 'LOC101262255', 'LyesC2p081', 'CAB7', 'LOC101252931', 'PSBP', 'LOC101247687', 'LOC101256513', 'VKOR', 'Z-ISO'})</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>LOC101262260;LOC101265555;OEE1;LOC101265790;SPA;LOC101252151;LOC101249002;LyesC2p070;CAB9;LyesC2p086;PETE;LOC101245880;LOC101245729;LOC543932;PSBO;LyesC2p089;LOC101265217;LyesC2p081;LOC101244176;LOC101254229;ELIP;LOC101263085;LyesC2p073;LOC101263054;LOC101262783;LOC101268832;psbS;LOC101258297;LOC101268227;LOC101255525;LOC101268560;LOC101252202;pGlcT3;VDE;LOC101245704;novel.82;SlFBA4;sfr2;LOC101258970;LOC101252931;LOC101264109;LOC101264255;LOC101267006;LOC101255514;LOC101256944;LyesC2p082;LOC101266963;LyesC2p069;LOC101244466;LOC101268563;LOC101252603;LOC101263132;VKOR;LOC101246143;PsbQ;LOC101246554;LOC101245518;LOC104649028;pGlcT4;LyesC2p062;LOC101244709;LyesC2p085;LyesC2p083;LOC101261284;TIL_;LOC101055526;LOC101253342;LOC101257676;CrtR-b2;LOC101262961;LyesC2p074;LOC101254806;LOC101259223;LOC101256427;LOC101263249;VGT1;LOC101257833;LOC101254513;CRTISO;LOC101253996;LOC101260274;CAB7;LOC101244306;LOC101253221;LOC101250586;LOC101263732;LOC101249164;AOS2;LOC104649438;LyesC2p076;novel.817;LOC101248500;TPS24;LyesC2p072;LOC101247687;LOC100037730;CAB4;novel.1062;PSBR;LOC101254882;PSBP;LOC101250650;LOC101259494;LOC101262218;HPL;HrBP1;LOC101251312;LOC101255583;LOC543930;pGlcT1;LOC101262255;LOC101256513;LyesC2p053;TOC75-III;LOC101260607;LOC101260856;Z-ISO;LOC101249904;LyesC2p084;LOC109120519;LOC101259028;LOC101255672;LOC101252117;LOC101264609;LyesC2p075;LyesC2p063;TIL;LOC101267919;LOC101243864;SlCOR413IM1;SlVTE5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GO:0009523</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>photosystem II</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5.281429451274519e-07</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.000173283700296317</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.2486109322645913</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-3.091257810592651</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.437141895294189</v>
+      </c>
+      <c r="J29" t="n">
+        <v>29</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101263132', 'LOC101248173', 'LyesC2p072', 'PSBO', 'LOC101248456', 'OEE1', 'LOC101245729', 'LOC101249002', 'psbS', 'LOC101254513', 'PsbQ', 'LyesC2p086', 'LOC101268563', 'LyesC2p089', 'LOC101245880', 'CAB9', 'LOC101257676', 'LyesC2p073', 'LOC101259494', 'LyesC2p053', 'LyesC2p085', 'CAB4', 'LyesC2p075', 'PSBR', 'LyesC2p074', 'CAB7', 'PSBP', 'LOC101255672', 'LOC101255525'})</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OEE1;LOC101249002;CAB9;LyesC2p086;LOC101245880;LOC101245729;PSBO;LyesC2p089;LyesC2p073;psbS;LOC101255525;LOC101268563;LOC101263132;PsbQ;LyesC2p085;LOC101257676;LyesC2p074;LOC101248456;LOC101254513;CAB7;LyesC2p072;CAB4;PSBR;PSBP;LOC101259494;LOC101248173;LyesC2p053;LOC101255672;LyesC2p075</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GO:0010333</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>terpene synthase activity</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6.256891305524697e-07</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0001934926971820487</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2459037161863876</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-1.98649001121521</v>
+      </c>
+      <c r="I30" t="n">
+        <v>14.52439308166504</v>
+      </c>
+      <c r="J30" t="n">
+        <v>21</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>GO:0016838</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>frozenset({'TPS14', 'PHS1', 'TPS17', 'LOC101246676', 'TPS28', 'TPS24', 'TPS37', 'TPS16', 'TPS31', 'TPS7', 'novel.572', 'MTS1', 'MTS2', 'TPS36', 'TPS32', 'SSTLE1', 'TPS3', 'TPS33', 'TPS39', 'TPS38', 'TPS35'})</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>TPS32;TPS33;TPS37;TPS38;LOC101246676;TPS39;MTS1;MTS2;TPS31;SSTLE1;TPS35;TPS14;TPS24;TPS36;novel.572;TPS16;TPS7;TPS28;TPS17;PHS1;TPS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>GO:0009862</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>systemic acquired resistance, salicylic acid mediated signaling pathway</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0.0001264451554685288</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.04779626876710388</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.01703428225745846</v>
-      </c>
-      <c r="G15" t="b">
+      <c r="C31" t="n">
+        <v>6.290527593036228e-07</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0001934926971820487</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.001998368560506537</v>
+      </c>
+      <c r="G31" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="n">
-        <v>-2.232618808746338</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-6.670547485351562</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="H31" t="n">
+        <v>-2.531773090362549</v>
+      </c>
+      <c r="I31" t="n">
+        <v>12.92324542999268</v>
+      </c>
+      <c r="J31" t="n">
+        <v>13</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>frozenset({'NIM1', 'HDS', 'NML1', 'LOC112940921', 'novel.168', 'LOC101253176', 'LOC101252520', 'LOC104648550', 'LOC101252192', 'XSP10', 'NML2', 'LOC101260990', 'LOC101261578'})</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>HDS;XSP10;NML1;LOC101253176;LOC101252192;LOC101261578;LOC112940921;LOC101260990;LOC104648550;LOC101252520;novel.168;NML2;NIM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GO:0015144</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>carbohydrate transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7.557727423717065e-07</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.000218796208916609</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1304759518882602</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-2.136860132217407</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.892946243286133</v>
+      </c>
+      <c r="J32" t="n">
+        <v>27</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101246848', 'SUT2', 'STP12', 'PMT6', 'LOC101263002', 'LOC101259076', 'std1', 'LOC101259239', 'pGlcT3', 'VGT1', 'SFP6', 'ht2', 'ht1', 'SUT4', 'VGT2', 'pGlcT4', 'SFP4', 'LOC101265318', 'LOC101263500', 'st3', 'LOC101251853', 'SFP11', 'STP18', 'STP11', 'PMT5', 'pGlcT1', 'SFP5'})</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>LOC101265318;VGT2;LOC101259239;SFP5;STP11;ht1;pGlcT3;SFP4;SFP6;ht2;STP12;std1;LOC101263500;pGlcT4;PMT5;PMT6;LOC101251853;SUT2;VGT1;st3;SUT4;LOC101263002;pGlcT1;SFP11;LOC101246848;STP18;LOC101259076</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GO:0048046</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>apoplast</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8.037267255889714e-07</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0002260309188563499</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.04625370418386232</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-1.680472850799561</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10.51479339599609</v>
+      </c>
+      <c r="J33" t="n">
+        <v>83</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>frozenset({'XTH16', 'tXET-B2', 'XTH5', 'novel.710', 'SBT1', 'SlFBA2', 'LOC101260852', 'LOC101246731', 'LOC101244214', 'novel.438', 'SlFBA3', 'LOC101267917', 'LOC543511', 'LOC101254166', 'Stig1', 'LOC100191110', 'LOC101251653', 'LOC101247488', 'P69A', 'LOC101244124', 'LOC101256574', 'LOC101260130', 'novel.867', 'XTH9', 'LOC101268808', 'LOC104648550', 'Xegip', 'LOC544217', 'LOC101251962', 'LOC101252520', 'LOC109121167', 'XTH6', 'SlArf_Xyl1', 'p69c', 'p69F', 'LOC101254239', 'LOC101245035', 'LOC101267778', 'XTH7', 'PG2', 'LOC104645427', 'SlArf_Xyl3', 'LOC101268065', 'LOC101253176', 'LOC101266976', 'tEG3', 'LOC101246103', 'LOC101258317', 'XSP10', 'SlFBA1', 'Mdip1', 'LOC101253826', 'SlArf_Xyl4', 'LOC101246829', 'LOC101257768', 'P69B', 'LOC101265484', 'LOC101055519', 'Lemir', 'LOC109118719', 'TBG6', 'LOC112941971', 'TBG7', 'LOC101255625', 'LOC101265242', 'LOC101265927', 'LOC101247374', 'LOC101250380', 'XET2', 'tXET-B1', 'novel.670', 'LOC101261871', 'ARF1', 'XTH1', 'TBG2', 'XET4', 'LOC101263519', 'XTH3', 'LOC101248557', 'LOC101244503', 'LOC101263269', 'TBG5', 'p69d'})</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>LOC109118719;LOC101258317;LOC543511;tEG3;LOC101253826;SlArf_Xyl3;SlFBA1;p69c;XSP10;LOC101268808;LOC101265927;LOC101251962;XTH7;Lemir;P69B;LOC101267917;LOC112941971;XTH5;tXET-B2;LOC101253176;Xegip;LOC101263269;TBG6;Stig1;LOC101250380;SBT1;LOC101244124;LOC101254239;LOC101244503;tXET-B1;LOC100191110;SlFBA3;LOC544217;LOC101265242;novel.710;ARF1;LOC101257768;LOC101263519;TBG5;TBG2;LOC101251653;XTH6;LOC101265484;XTH3;P69A;TBG7;SlArf_Xyl4;LOC101248557;XET2;LOC104648550;PG2;LOC101252520;LOC101261871;LOC101260130;LOC101055519;novel.438;LOC101256574;LOC101260852;LOC101247488;LOC101255625;LOC101254166;XTH9;SlFBA2;p69d;XTH16;LOC101268065;LOC101266976;LOC104645427;LOC101246731;XET4;LOC109121167;Mdip1;novel.867;LOC101267778;SlArf_Xyl1;p69F;LOC101244214;LOC101246829;LOC101246103;XTH1;LOC101247374;LOC101245035;novel.670</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GO:0043436</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>oxoacid metabolic process</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1.157831151237145e-06</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0003165703339340894</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3157863285647458</v>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-3.374885559082031</v>
+      </c>
+      <c r="I34" t="n">
+        <v>12.96243095397949</v>
+      </c>
+      <c r="J34" t="n">
+        <v>223</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH2B7d', 'novel.168', 'LOC101258525', 'LOC101256649', 'LOC101245297', 'LOC101263085', 'ME2', 'LOC101254591', 'SlGGP-LIKE', 'LEAS1', 'LOC101249193', 'LOC101267118', 'SlFBA2', 'LOC112940921', 'LOC101256592', 'LOC101254720', 'LOC101245952', 'LOC101245370', 'LOC101255271', 'LOC101256077', 'LOC100134915', 'AOS3', 'LOC104648641', 'LOC101258131', 'SlFBA3', 'SlFRK3', 'SlADH11A4a', 'PIIGLB1', 'PAL3', 'HXK3', 'PDH', 'ZEP', 'LOC101263879', 'SK', 'LOC101250354', 'LOC104644402', 'LOC104645573', 'MIOX', 'LOC101264480', 'HDS', 'TAO2', 'SlFBA8', 'PRO2', 'SlALDH6B2', 'LOC101250058', 'LOC101258391', 'SlDMR6-1', 'SNF1', 'LOC101264863', 'LOC101258461', 'OAT', 'novel.966', 'SCOA', 'LOC101254137', 'gdh1', 'hdc', 'MKS1b', 'SSADH', 'LOC101248511', 'LOC101252977', 'LOC101259236', 'LOC101259572', 'PP2Ac1', 'THM16', 'LOC101263535', 'LOC101252681', 'LOC101258787', 'MKS1d', 'LOC101249057', 'AOS2', 'LOC101264873', 'LOC101257319', 'LOC101266918', 'PAL2', 'WRKYIId', 'LOC101250481', 'MKS1e', 'HPL', 'LOC101260607', 'SlALDH2B7a', 'LOC101254597', 'LOC101255411', 'LOC101244614', 'LOC101256694', 'MST1', 'LysRS', 'LOC101252202', 'TomloxC', 'LOC101256529', 'LOC101267103', 'NAOD', 'NR', 'LOC778303', 'LOC101254281', 'nii1', 'LOC101244007', 'LOC544276', 'LOC101264132', 'LOC101251091', 'LOC101254608', 'opr3', 'LOC101252192', 'PP2Ac2', 'LOC101247770', 'LOC101267184', 'LOC101252738', 'LOC101268347', 'LOC101259725', 'LOC101244882', 'LOC101261578', 'LOC101252453', 'ACS2', 'LOC101266950', 'LOC104646631', 'LOC101247693', 'GS1', 'LOC101251350', 'GABA-TP2', 'LOC101259235', 'LOC101246995', 'LOC101258355', 'LOC109120859', 'novel.312', 'LOC101257261', 'SlFBA1', 'PGH1', 'LOC101250561', 'LOC101267663', 'OTC', 'PAL5', 'SlMYB21', 'LOC101245553', 'LOC101254439', 'LOC101252161', 'ACS6', 'LOC101263817', 'LOC101244092', 'THM27', 'novel.879', 'SlFBA6', 'LOC107648852', 'LOC101246116', 'LOC101245480', 'NAGK', 'LOC101251311', 'LOC101263606', 'TAO3', 'LOC543920', 'LOC101251816', 'LOC101250807', 'MST2', 'LOC101258830', 'LOC101250791', 'SlADH12A1', 'LOC101261642', 'ACS4', 'ME1', 'LOC101268510', 'NRT2.2', 'LOC101257857', 'HXK4', 'mMDH2', 'LOC101262091', 'LOC101250891', 'LOC101258079', 'novel.92', 'LOC101055519', 'MKS1a', 'LOC101260990', 'LOC101246283', 'GME1', 'LOC104648010', 'LOC101248029', 'LOC101246396', 'SIZ1', 'LOC101244469', 'LOC778326', 'LOC101254848', 'LOC101250164', 'LOC101252583', 'LOC101249935', 'LOC101267346', 'TomloxE', 'OPR1', 'LOC101250586', 'PAT', 'LOC101254332', 'LOC101255874', 'novel.105', 'LOC101266174', 'LOC101267959', 'LOC101267503', 'LOC101247833', 'DXR', 'LOC101263406', 'LOC101248052', 'LOC101262503', 'LOC101254112', 'adc1', 'LOC101249671', 'ODC', 'LOC101247891', 'Slalpha-kGDH', 'LOC101247828', 'LOC101247914', 'Sip1', 'LOC101252466', 'NAOAT', 'LOC101244691', 'mdh', 'LOC101259366', 'novel.113', 'LOC101253805', 'SlFBA7', 'LOC101247047', 'mMDH1', 'LeNCED1', 'LOC101258500', 'LOC101248790', 'LOC101256513', 'novel.706', 'LOXB', 'LOC543658'})</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>LOC101250791;LOC101258500;NAOD;HDS;LOC101247891;LOC101252161;LOC101263817;SlFBA1;LOC778303;PP2Ac2;MKS1e;LOC101244691;LOC101251816;LOC104646631;SlGGP-LIKE;MKS1d;LOC101250481;LOC101247828;LOC101258131;LOC101250807;LOC101247047;LOC101249671;LOC101263606;LEAS1;LOC101258461;LOC104648641;novel.92;LOC101246116;LOC101249935;LOC101263085;HXK4;ZEP;LOC101252192;LOC101256077;adc1;GABA-TP2;PGH1;LOC101267118;LOC101250058;LOC101248511;LOC101252453;LOC101262503;HXK3;LOC101245553;SlMYB21;novel.113;LOC101252202;mdh;LOC101251091;LOC101249193;LOC104645573;LOC101256592;TAO3;LOC101261578;LOC101267503;MIOX;ODC;LOC101245952;LOC101247770;LOC101259725;SIZ1;LOC101254591;LOC101259366;ACS6;LOC101255271;LOC112940921;TomloxE;LysRS;GME1;SlALDH2B7a;LOC101263879;LOC101253805;LeNCED1;LOC101251350;SlFBA3;LOC101250561;THM16;MST2;LOC101244007;LOC101264863;LOC101259572;ACS2;LOC101264873;LOC101249057;LOC101254439;LOC101267663;LOC101258079;NR;LOC101251311;LOC101268510;LOC101245297;LOC101254608;LOC101256694;LOC101257319;Slalpha-kGDH;PAT;LOC101250164;SSADH;PP2Ac1;LOC101250354;SlADH11A4a;SlFBA7;LOC101266950;LOC101257261;novel.966;LOC101259236;LOC100134915;PRO2;LOC101258355;LOC101254720;SlADH12A1;SlADH2B7d;SlFRK3;ACS4;LOC101247914;SlALDH6B2;SlFBA6;MKS1a;LOC101247693;LOC101254281;LOC101244882;ME1;LOC101260990;LOC101248029;LOC101244092;novel.879;LOC101254137;LOC101248052;mMDH1;LOC101266918;LOC101254332;LOC101254597;ME2;Sip1;PAL3;SK;LOC543658;LOC101055519;LOC104648010;TAO2;novel.105;DXR;LOC101252583;NRT2.2;LOC101258787;LOC101250586;AOS2;PAL5;LOC101256529;AOS3;PAL2;LOC101259235;LOC101255411;hdc;LOC101246396;LOC107648852;LOC101266174;LOC101252977;LOC101256649;LOC101244469;SlDMR6-1;SlFBA2;LOC101267346;LOC101261642;LOC101248790;OPR1;LOXB;LOC101268347;LOC544276;mMDH2;MST1;OTC;LOC101264132;LOC101264480;LOC101267103;LOC101252466;LOC101267184;LOC109120859;LOC778326;OAT;SlFBA8;LOC101244614;HPL;LOC101254848;SCOA;WRKYIId;MKS1b;SNF1;LOC101263406;novel.168;LOC101257857;nii1;LOC101245370;LOC101258391;NAGK;LOC101256513;NAOAT;gdh1;LOC101260607;LOC543920;LOC101247833;PDH;LOC101252738;LOC101267959;LOC101262091;THM27;novel.706;LOC101250891;LOC101245480;LOC101252681;GS1;LOC101263535;LOC101246283;TomloxC;PIIGLB1;novel.312;LOC101246995;LOC101254112;LOC104644402;LOC101258525;LOC101258830;opr3;LOC101255874</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GO:0009507</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>chloroplast</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1.274385991557648e-06</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0003390211166189711</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.02811558528757412</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-2.864698171615601</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8.055773735046387</v>
+      </c>
+      <c r="J35" t="n">
+        <v>370</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101263085', 'LOC101245421', 'LOC101262888', 'LOC101254882', 'LOC101256592', 'SlCOR413IM1', 'LOC101244514', 'LOC101245370', 'LOC101255271', 'LOC101258293', 'LyesC2p073', 'LOC101247851', 'SlFBA3', 'PIIGLB1', 'CAB4', 'LOC101255583', 'ZEP', 'MTS2', 'LOC101251653', 'LOC101263675', 'LOC101255358', 'MDHAR', 'LOC101257833', 'LOC101255295', 'LOC101268200', 'LOC101258151', 'LOC101251312', 'LOC101267611', 'LOC101252138', 'LOC101248511', 'LOC101254229', 'LOC101247293', 'LyesC2p087', 'LOC101245112', 'LOC101253221', 'LOC544217', 'LOC101252202', 'TomloxC', 'LOC101263281', 'novel.1062', 'LyesC2p069', 'LOC101254281', 'LOC101259028', 'nii1', 'TPS3', 'LOC101254608', 'LOC101265217', 'NDPS1', 'LOC101252151', 'LOC101258785', 'LOC101264062', 'LyesC2p070', 'SlIPT2', 'LOC101253541', 'LOC101250561', 'LOC101266486', 'CAB9', 'LOC101261489', 'zds', 'LOC100037490', 'LOC101257971', 'SlIPT4', 'LOC101255672', 'LOC101250891', 'TOC75-III', 'NSY', 'LOC101263132', 'LyesC2p072', 'LOC101262221', 'LOC101256427', 'LOC543930', 'PAT', 'LOC101251285', 'LOC101267959', 'LOC101254112', 'ELIP', 'LOC101266713', 'LOC101263732', 'LOC101265555', 'LOC101255435', 'LOC100037730', 'LOC104644379', 'LOC101253805', 'SEND33', 'LOC101249417', 'LOC101262255', 'LyesC2p081', 'LOC101252931', 'LOC101265931', 'LOC101256513', 'PPO', 'LOC101257542', 'LOC101249846', 'PsbQ', 'SlFBA2', 'LyesC2p086', 'SlALD3H1', 'LOC101243864', 'SSR2', 'novel.895', 'ribA', 'SlFRK3', 'MKS2b', 'LOC101264109', 'SK', 'LOC101243905', 'LOC101262783', 'LOC101245901', 'LOC101264480', 'LyesC2p074', 'SGR1', 'SNF1', 'pGlcT1', 'LOC101260856', 'LOC101244466', 'LOC101244717', 'LOC101249164', 'LOC101245518', 'LyesC2p076', 'LOC101262260', 'LOC101259357', 'LOC101259572', 'SlIPT1', 'LyesC2p080', 'SlHDA3', 'PDF1B', 'AgpL1', 'LOC101261433', 'LOC101249057', 'AOS2', 'LOC101260607', 'LOC101249327', 'HPL', 'LyesC2p085', 'TPS24', 'LOC101267006', 'CrtR-b2', 'LyesC2p075', 'Cel2', 'LOC101255915', 'SlArf_Xyl3', 'LOC101055609', 'LOC101055526', 'LOC101248838', 'LOC101247693', 'VDE', 'LOC101246554', 'LOC101264145', 'LOC101253342', 'LOC101248500', 'LOC101267425', 'psbS', 'LOC101257407', 'SlFBA1', 'sos1', 'LOC101255756', 'GGPS2', 'TCP4', 'LOC101256426', 'EO', 'LOC101267919', 'LyesC2p071', 'MST2', 'LOC543932', 'LOC101263249', 'LOC101255525', 'LOC101055519', 'LOC101250405', 'LOC101263054', 'LOC101267346', 'LOC101250586', 'LOC104649028', 'SlVTE5', 'LOC101247833', 'LyesC2p089', 'TCP5', 'LOC101265790', 'LOC101247914', 'LOC101264050', 'LOC101245616', 'SQD1', 'LOC101250378', 'LeNCED1', 'LOC101259692', 'VKOR', 'LOC101255514', 'LOC101245297', 'LOC101245729', 'LOC101259221', 'LOC101260852', 'novel.1', 'LyesC2p079', 'LOC101268617', 'MTSHP', 'MKS2c', 'LOC101250520', 'LOC101252117', 'LOC101255298', 'LOC101268227', 'HDS', 'PDF1A', 'ca3', 'LOC101255076', 'LOC101258970', 'dxs2', 'PSBO', 'LOC101250287', 'LOC101252977', 'PHS1', 'LyesC2p078', 'LOC101268563', 'LOC101260274', 'VGT1', 'LyesC2p082', 'LOC101266918', 'LOC101249904', 'LyesC2p053', 'LOC101247061', 'LOC101244614', 'TMT', 'LOC101256609', 'LOC101258297', 'LOC101256529', 'Shy', 'LOC101252192', 'LOC101247770', 'GR', 'LOC101266624', 'LOC101251350', 'LOC101246521', 'LOC101257061', 'LOC101250650', 'MKS2', 'LOC101249680', 'OTC', 'LOC101261284', 'LOC101245880', 'LOC101248098', 'LOC101257676', 'LOC101248896', 'PPO-2', 'SlArf_Xyl4', 'LOC101256944', 'LOC543920', 'LOC101258337', 'novel.82', 'novel.817', 'rps16', 'LOC101245121', 'LOC101244516', 'ME1', 'Psy1', 'LOC101264609', 'LyesC2p083', 'LOC101265242', 'OEE1', 'LOC101256822', 'SlIPT3', 'novel.924', 'POR2', 'LOC101254848', 'LOC101265835', 'LOC101268560', 'LOC101266160', 'LOC101265168', 'TIL', 'LOC101247891', 'LOC101252466', 'TPS7', 'LAPA1', 'LOC101245785', 'pGlcT4', 'LOC101254712', 'LOC101264082', 'dxs', 'vis1', 'LOC101263269', 'LOC101258500', 'LOC101247687', 'LOC100736525', 'LOC543658', 'PETE', 'LOC101253219', 'LyesC2p062', 'LOC101254513', 'LOC101256077', 'pds', 'LOC101246731', 'LOC101247532', 'LOC101259494', 'LOC101260469', 'LOC101252603', 'LyesC2p063', 'LOC101261547', 'LOC101259632', 'SPA', 'LOC100191110', 'LOC101244176', 'TPx1', 'novel.866', 'CRTISO', 'LOC109120519', 'SSADH', 'THIC', 'LOC101249002', 'novel.766', 'Why3', 'LOC101245293', 'LOC101257319', 'LOC101262218', 'LOC101264255', 'MST1', 'SppS', 'Rbcs-3B', 'LOC101266963', 'LOC101253320', 'novel.1105', 'SlTIP2-2', 'MSH1', 'LOC101266265', 'LOC101246995', 'LyesC2p077', 'LOC101253996', 'LOC101252124', 'HrBP1', 'LOC101264004', 'pGlcT3', 'sfr2', 'LOC101249584', 'LOC101263817', 'LOC104649438', 'LOC101264583', 'LOC101268832', 'NAGK', 'LOC101251311', 'SlFBA4', 'PSBR', 'LOC101245704', 'LOC101261642', 'LyesC2p088', 'LOC101254806', 'LOC101257857', 'HXK4', 'rbcS1', 'LOC101244709', 'SBPase', 'LOC101259223', 'LOC101256192', 'LOC101267163', 'LOC101246143', 'LOC778326', 'LOC101246676', 'TIL_', 'DXR', 'LyesC2p084', 'SlVP2', 'LOC101243925', 'LOC101257875', 'SLTAB2', 'Sip1', 'LOC101262961', 'mdh', 'SODCP.2', 'LOC101255261', 'MTS1', 'CAB7', 'PSBP', 'LOC101261259', 'Z-ISO', 'LOC101259256'})</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>LOC101262260;LOC101252138;Psy1;LOC101261433;LOC101250405;LOC101258500;LOC101256609;LOC101265555;LOC101255298;HDS;OEE1;SODCP.2;LOC101247891;LOC101256822;LOC101265790;NDPS1;SPA;LOC101252151;LOC101263817;LOC101249002;SlArf_Xyl3;LyesC2p070;CAB9;LOC101259256;LyesC2p077;LyesC2p086;SlFBA1;SEND33;PETE;LOC101245880;LOC101245729;LOC543932;LOC101245785;LOC101266713;PSBO;LyesC2p079;TCP4;LyesC2p089;LOC101250520;LOC101246521;LOC101265217;LyesC2p081;LOC101244176;LOC101243925;LOC101254229;ELIP;LOC101249846;LyesC2p080;zds;LOC101253541;LOC101247061;LyesC2p078;LOC101263085;LyesC2p073;novel.895;HXK4;ZEP;MKS2b;LOC101263054;SlIPT1;LOC101264082;LOC101252192;LOC101256077;LOC101262783;LOC101268832;novel.924;psbS;novel.1;LyesC2p087;LOC101248511;LOC101263269;LOC101258297;LOC101255076;LOC101268227;TCP5;LOC101255525;LOC101267611;LOC101263675;LOC101268560;LOC101252202;SLTAB2;novel.766;PDF1B;mdh;LOC100736525;pGlcT3;LOC101256592;VDE;LOC101255358;SlIPT2;LOC101245704;SGR1;LOC101244516;novel.866;novel.82;LOC101247770;SlFBA4;sfr2;LOC101246676;novel.1105;SQD1;LOC101258970;LOC101255271;LOC101248098;LOC101257542;LOC101252931;LOC101264109;LOC101264255;LOC101267006;LyesC2p071;MKS2;LOC101253805;LOC101264004;LeNCED1;LOC101265931;LOC101255514;LOC100191110;LOC101256944;LOC101251350;SlFBA3;LOC101250561;LOC101264062;LyesC2p082;LOC101245293;MST2;LOC101249680;LOC101266963;Why3;LyesC2p069;LOC101259572;LOC544217;LOC101265242;LOC101249057;LOC101244466;LOC101254712;LOC101268617;MDHAR;LOC101249417;LOC101265168;LOC101251311;LOC101258337;LOC101251285;LOC101268563;LOC101252603;LOC101250287;LOC101245297;LOC101254608;TPx1;LOC101263132;LOC101252124;GGPS2;VKOR;LOC101257319;LOC101246143;PAT;SSADH;LOC101249584;MTS1;LOC101258785;Rbcs-3B;PsbQ;LOC101246554;LOC101255295;LOC101245518;LOC104649028;pGlcT4;LOC101251653;LyesC2p062;LOC101244709;dxs;LyesC2p085;LOC101266486;SlIPT4;LOC101243905;MTS2;LyesC2p083;LOC101255756;LOC101257061;LOC101256426;LOC101253219;LOC101261284;LOC101261489;TIL_;SlVP2;LOC101245421;SlFRK3;LOC101055526;LOC101247914;LOC101253342;LOC100037490;LOC101253320;LOC101248896;LOC101257676;Cel2;MTSHP;SlTIP2-2;LOC101262888;CrtR-b2;LOC101262961;LOC101247532;SlArf_Xyl4;rbcS1;LOC101247693;LOC101254281;Shy;LOC101263281;LOC101244717;ME1;sos1;LyesC2p074;LyesC2p088;PDF1A;LOC101245121;LOC101254806;LOC101259223;LOC101256427;LOC101263249;LOC101259692;LOC101266918;VGT1;Sip1;LOC101257833;LOC101255435;LOC101254513;SK;CRTISO;LOC543658;LOC101245901;LOC101253996;LOC101055519;LOC101260274;LOC101244514;CAB7;DXR;NSY;LOC104644379;LOC101253221;LOC101250586;LOC101263732;LOC101249164;AOS2;LOC101259221;LOC104649438;LyesC2p076;PPO-2;LOC101256529;SSR2;LOC101247851;novel.817;LOC101248500;SlIPT3;LOC101262221;LOC101260852;TPS24;LOC101248838;LOC101264145;LyesC2p072;LOC101247687;LOC101055609;LOC101267425;LOC100037730;LOC101258293;rps16;LOC101252977;CAB4;LOC101261259;novel.1062;LOC101257875;SlFBA2;LOC101267346;LOC101261642;PSBR;LOC101256192;LOC101254882;LOC101267163;SlALD3H1;ribA;MST1;OTC;LOC101264050;PSBP;LOC101264480;MKS2c;SppS;LOC101250650;pds;LOC101252466;LOC101255261;POR2;LOC101246731;LOC101259494;LOC101262218;LAPA1;LOC101261547;LOC778326;LOC101247293;LOC101244614;HPL;LOC101254848;SNF1;LOC101258151;HrBP1;LOC101245616;TMT;LOC101259632;LOC101251312;SBPase;GR;LOC101257857;LOC101255583;nii1;LOC543930;LOC101245370;THIC;LOC101257407;pGlcT1;LOC101262255;LOC101265835;EO;NAGK;LOC101256513;LyesC2p053;LOC101266624;ca3;TOC75-III;LOC101260607;LOC543920;LOC101260856;PPO;vis1;TPS7;LOC101247833;LOC101245112;AgpL1;LOC101266160;Z-ISO;LOC101249904;LyesC2p084;LOC101250378;LOC109120519;LOC101267959;SlHDA3;LOC101259028;LOC101255672;LOC101259357;LOC101252117;LOC101264609;LOC101250891;LyesC2p075;LOC101268200;LOC101249327;LyesC2p063;TIL;LOC101267919;TomloxC;PIIGLB1;LOC101243864;LOC101257971;LOC101260469;LOC101246995;LOC101254112;LOC101266265;MSH1;SlCOR413IM1;LOC101255915;PHS1;LOC101264583;SlVTE5;TPS3;dxs2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GO:0051119</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sugar transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2.620763877731853e-06</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0006788468118030166</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.128739817935465</v>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-2.280702114105225</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7.889541149139404</v>
+      </c>
+      <c r="J36" t="n">
+        <v>23</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101246848', 'STP12', 'LOC101263002', 'LOC101259076', 'std1', 'LOC101259239', 'pGlcT3', 'VGT1', 'SFP6', 'ht2', 'ht1', 'VGT2', 'pGlcT4', 'SFP4', 'LOC101265318', 'LOC101263500', 'st3', 'LOC101251853', 'STP18', 'STP11', 'PMT5', 'SFP11', 'SFP5'})</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>LOC101265318;VGT2;LOC101259239;SFP5;STP11;ht1;pGlcT3;SFP4;SFP6;ht2;STP12;std1;LOC101263500;pGlcT4;PMT5;LOC101251853;VGT1;st3;LOC101263002;SFP11;LOC101246848;STP18;LOC101259076</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GO:0019752</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>carboxylic acid metabolic process</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3.398270325559704e-06</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0008576711490893375</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.319457267814002</v>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-3.3058762550354</v>
+      </c>
+      <c r="I37" t="n">
+        <v>12.89604663848877</v>
+      </c>
+      <c r="J37" t="n">
+        <v>206</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH2B7d', 'novel.168', 'LOC101258525', 'LOC101256649', 'LOC101245297', 'LOC101263085', 'ME2', 'LOC101254591', 'SlGGP-LIKE', 'LEAS1', 'LOC101249193', 'LOC101267118', 'SlFBA2', 'LOC112940921', 'LOC101256592', 'LOC101254720', 'LOC101245370', 'LOC101255271', 'LOC100134915', 'AOS3', 'LOC104648641', 'LOC101258131', 'SlFBA3', 'SlFRK3', 'SlADH11A4a', 'PIIGLB1', 'PAL3', 'HXK3', 'PDH', 'ZEP', 'LOC101263879', 'SK', 'LOC101250354', 'LOC104644402', 'LOC104645573', 'MIOX', 'LOC101264480', 'HDS', 'TAO2', 'SlFBA8', 'PRO2', 'SlALDH6B2', 'LOC101250058', 'LOC101258391', 'SlDMR6-1', 'SNF1', 'LOC101264863', 'OAT', 'novel.966', 'SCOA', 'LOC101254137', 'gdh1', 'hdc', 'MKS1b', 'SSADH', 'LOC101248511', 'LOC101252977', 'LOC101259236', 'LOC101259572', 'PP2Ac1', 'THM16', 'LOC101263535', 'MKS1d', 'LOC101249057', 'AOS2', 'LOC101264873', 'LOC101257319', 'LOC101266918', 'PAL2', 'LOC101260607', 'LOC101250481', 'MKS1e', 'HPL', 'SlALDH2B7a', 'LOC101254597', 'LOC101255411', 'LOC101244614', 'LOC101256694', 'MST1', 'LysRS', 'LOC101252202', 'TomloxC', 'LOC101256529', 'LOC101267103', 'NAOD', 'LOC778303', 'LOC101254281', 'LOC101244007', 'LOC544276', 'LOC101264132', 'LOC101251091', 'LOC101254608', 'opr3', 'LOC101252192', 'PP2Ac2', 'LOC101247770', 'LOC101267184', 'LOC101252738', 'LOC101259725', 'LOC101244882', 'ACS2', 'LOC101252453', 'LOC101261578', 'LOC101266950', 'LOC104646631', 'LOC101247693', 'GS1', 'LOC101251350', 'GABA-TP2', 'LOC101259235', 'LOC101246995', 'LOC101258355', 'LOC109120859', 'SlFBA1', 'PGH1', 'LOC101250561', 'LOC101267663', 'OTC', 'PAL5', 'SlMYB21', 'LOC101245553', 'LOC101254439', 'LOC101252161', 'ACS6', 'LOC101263817', 'LOC101244092', 'THM27', 'novel.879', 'SlFBA6', 'LOC107648852', 'LOC101246116', 'LOC101245480', 'NAGK', 'LOC101251311', 'LOC101263606', 'TAO3', 'LOC543920', 'LOC101251816', 'LOC101250807', 'MST2', 'LOC101258830', 'SlADH12A1', 'LOC101261642', 'ACS4', 'ME1', 'LOC101268510', 'LOC101257857', 'HXK4', 'mMDH2', 'LOC101250891', 'LOC101258079', 'novel.92', 'LOC101055519', 'MKS1a', 'LOC101260990', 'LOC101246283', 'GME1', 'LOC101248029', 'LOC101246396', 'SIZ1', 'LOC101244469', 'LOC101254848', 'LOC101250164', 'LOC101252583', 'LOC101249935', 'LOC101267346', 'TomloxE', 'OPR1', 'LOC101250586', 'PAT', 'LOC101254332', 'LOC101255874', 'novel.105', 'LOC101266174', 'LOC101267959', 'LOC101267503', 'LOC101247833', 'DXR', 'LOC101263406', 'LOC101248052', 'LOC101262503', 'LOC101254112', 'adc1', 'ODC', 'LOC101247891', 'Slalpha-kGDH', 'LOC101247828', 'LOC101247914', 'Sip1', 'LOC101252466', 'NAOAT', 'LOC101244691', 'mdh', 'LOC101259366', 'novel.113', 'LOC101253805', 'SlFBA7', 'LOC101247047', 'mMDH1', 'LeNCED1', 'LOC101258500', 'LOC101248790', 'LOC101256513', 'novel.706', 'LOXB', 'LOC543658'})</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>LOC101258500;NAOD;HDS;LOC101247891;LOC101252161;LOC101263817;SlFBA1;LOC778303;PP2Ac2;MKS1e;LOC101244691;LOC101251816;LOC104646631;SlGGP-LIKE;MKS1d;LOC101250481;LOC101247828;LOC101258131;LOC101250807;LOC101247047;LOC101263606;LEAS1;LOC104648641;novel.92;LOC101246116;LOC101249935;LOC101263085;HXK4;ZEP;LOC101252192;adc1;GABA-TP2;PGH1;LOC101267118;LOC101250058;LOC101248511;LOC101252453;LOC101262503;HXK3;LOC101245553;SlMYB21;novel.113;LOC101252202;mdh;LOC101251091;LOC101249193;LOC104645573;LOC101256592;TAO3;LOC101261578;LOC101267503;MIOX;ODC;LOC101247770;LOC101259725;SIZ1;LOC101254591;LOC101259366;ACS6;LOC101255271;LOC112940921;TomloxE;LysRS;GME1;SlALDH2B7a;LOC101263879;LOC101253805;LeNCED1;LOC101251350;SlFBA3;LOC101250561;THM16;MST2;LOC101244007;LOC101264863;LOC101259572;ACS2;LOC101264873;LOC101249057;LOC101254439;LOC101267663;LOC101258079;LOC101251311;LOC101268510;LOC101245297;LOC101254608;LOC101256694;LOC101257319;Slalpha-kGDH;PAT;LOC101250164;SSADH;PP2Ac1;LOC101250354;SlADH11A4a;SlFBA7;LOC101266950;novel.966;LOC101259236;LOC100134915;PRO2;LOC101258355;LOC101254720;SlADH12A1;SlADH2B7d;SlFRK3;ACS4;LOC101247914;SlALDH6B2;SlFBA6;MKS1a;LOC101247693;LOC101254281;LOC101244882;ME1;LOC101260990;LOC101248029;LOC101244092;novel.879;LOC101254137;LOC101248052;mMDH1;LOC101266918;LOC101254332;LOC101254597;ME2;Sip1;PAL3;SK;LOC543658;LOC101055519;TAO2;novel.105;DXR;LOC101252583;LOC101250586;AOS2;PAL5;LOC101256529;AOS3;PAL2;LOC101259235;LOC101255411;hdc;LOC101246396;LOC107648852;LOC101266174;LOC101252977;LOC101256649;LOC101244469;SlDMR6-1;SlFBA2;LOC101267346;LOC101261642;LOC101248790;OPR1;LOXB;LOC544276;mMDH2;MST1;OTC;LOC101264132;LOC101264480;LOC101267103;LOC101252466;LOC101267184;LOC109120859;OAT;SlFBA8;LOC101244614;HPL;LOC101254848;SCOA;MKS1b;SNF1;LOC101263406;novel.168;LOC101257857;LOC101245370;LOC101258391;NAGK;LOC101256513;NAOAT;gdh1;LOC101260607;LOC543920;LOC101247833;PDH;LOC101252738;LOC101267959;THM27;novel.706;LOC101250891;LOC101245480;GS1;LOC101263535;LOC101246283;TomloxC;PIIGLB1;LOC101246995;LOC101254112;LOC104644402;LOC101258525;LOC101258830;opr3;LOC101255874</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GO:0032787</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>monocarboxylic acid metabolic process</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5.898425918072915e-06</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.001439541468441547</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.2036339086009705</v>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-3.110862016677856</v>
+      </c>
+      <c r="I38" t="n">
+        <v>13.10690784454346</v>
+      </c>
+      <c r="J38" t="n">
+        <v>127</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH2B7d', 'novel.168', 'LOC101258525', 'LOC101256649', 'LOC101245297', 'LOC101263085', 'LOC101254591', 'SlFBA2', 'LOC112940921', 'LOC101256592', 'LOC101254720', 'LOC101245370', 'LOC101255271', 'LOC100134915', 'AOS3', 'SlFBA3', 'SlFRK3', 'PIIGLB1', 'PAL3', 'HXK3', 'ZEP', 'LOC101250354', 'LOC104644402', 'LOC104645573', 'LOC101264480', 'HDS', 'TAO2', 'SlFBA8', 'LOC101250058', 'LOC101258391', 'SlDMR6-1', 'SNF1', 'LOC101254137', 'MKS1b', 'SSADH', 'LOC101248511', 'LOC101252977', 'LOC101259572', 'PP2Ac1', 'LOC101263535', 'MKS1d', 'LOC101249057', 'AOS2', 'PAL2', 'LOC101260607', 'LOC101250481', 'MKS1e', 'HPL', 'SlALDH2B7a', 'LOC101254597', 'LOC101255411', 'LOC101256694', 'LOC101252202', 'TomloxC', 'LOC101256529', 'LOC101267103', 'LOC544276', 'LOC101264132', 'opr3', 'LOC101247770', 'PP2Ac2', 'LOC101252738', 'LOC101266950', 'LOC101252453', 'LOC101261578', 'LOC104646631', 'GABA-TP2', 'LOC101246995', 'LOC101258355', 'LOC109120859', 'SlFBA1', 'PGH1', 'LOC101250561', 'PAL5', 'SlMYB21', 'LOC101252161', 'LOC101244092', 'THM27', 'novel.879', 'SlFBA6', 'LOC107648852', 'LOC101245480', 'LOC101251311', 'LOC101263606', 'TAO3', 'LOC101250807', 'ME1', 'LOC101268510', 'LOC101257857', 'HXK4', 'LOC101258079', 'novel.92', 'MKS1a', 'LOC101260990', 'LOC101246396', 'SIZ1', 'LOC101244469', 'LOC101250164', 'LOC101252583', 'LOC101267346', 'TomloxE', 'OPR1', 'LOC101250586', 'LOC101255874', 'novel.105', 'LOC101266174', 'LOC101267959', 'LOC101267503', 'LOC101247833', 'DXR', 'LOC101263406', 'LOC101262503', 'LOC101247828', 'Sip1', 'LOC101244691', 'LOC101259366', 'novel.113', 'LOC101253805', 'SlFBA7', 'LOC101247047', 'LeNCED1', 'LOC101258500', 'LOC101248790', 'LOC101256513', 'novel.706', 'LOXB', 'LOC543658'})</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>LOC101258500;HDS;LOC101252161;SlFBA1;PP2Ac2;MKS1e;LOC101244691;LOC104646631;MKS1d;LOC101250481;LOC101247828;LOC101250807;LOC101247047;LOC101263606;novel.92;LOC101263085;HXK4;ZEP;GABA-TP2;PGH1;LOC101250058;LOC101248511;LOC101252453;LOC101262503;HXK3;SlMYB21;novel.113;LOC101252202;LOC104645573;LOC101256592;TAO3;LOC101261578;LOC101267503;LOC101247770;SIZ1;LOC101254591;LOC101259366;LOC101255271;LOC112940921;TomloxE;SlALDH2B7a;LOC101253805;LeNCED1;SlFBA3;LOC101250561;LOC101259572;LOC101249057;LOC101258079;LOC101251311;LOC101268510;LOC101245297;LOC101256694;LOC101250164;SSADH;PP2Ac1;LOC101250354;SlFBA7;LOC101266950;LOC100134915;LOC101258355;LOC101254720;SlADH2B7d;SlFRK3;SlFBA6;MKS1a;ME1;LOC101260990;LOC101244092;novel.879;LOC101254137;LOC101254597;Sip1;PAL3;LOC543658;TAO2;novel.105;DXR;LOC101252583;LOC101250586;AOS2;PAL5;LOC101256529;AOS3;PAL2;LOC101255411;LOC101246396;LOC107648852;LOC101266174;LOC101252977;LOC101256649;LOC101244469;SlDMR6-1;SlFBA2;LOC101267346;LOC101248790;OPR1;LOXB;LOC544276;LOC101264132;LOC101264480;LOC101267103;LOC109120859;SlFBA8;HPL;MKS1b;SNF1;LOC101263406;novel.168;LOC101257857;LOC101245370;LOC101258391;LOC101256513;LOC101260607;LOC101247833;LOC101252738;LOC101267959;THM27;novel.706;LOC101245480;LOC101263535;TomloxC;PIIGLB1;LOC101246995;LOC104644402;LOC101258525;opr3;LOC101255874</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GO:0120251</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>hydrocarbon biosynthetic process</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5.996261323387529e-06</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.001439541468441547</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.08713029806662356</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-1.777386665344238</v>
+      </c>
+      <c r="I39" t="n">
+        <v>12.70693969726562</v>
+      </c>
+      <c r="J39" t="n">
+        <v>27</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>GO:0120252</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101244469', 'ACO1', 'LOC101267934', 'E8-6', 'ACO4-like', 'pds', 'novel.93', 'ACS6', 'ACO4', 'MKK2', 'LOC101250012', 'LOC101245697', 'zds', 'ACO3', 'novel.729', 'aco5', 'MKK4', 'TPS32', 'ODD', 'TPS33', 'ACS4', 'LeNCED1', 'Z-ISO', 'NSGT1', 'NSY', 'LOC101259689', 'ACS2'})</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>TPS32;zds;TPS33;E8-6;ACS6;LeNCED1;ACS2;ACO4;NSGT1;ACO3;ACS4;ACO1;ACO4-like;LOC101250012;MKK2;NSY;LOC101267934;LOC101259689;LOC101244469;novel.93;pds;aco5;MKK4;LOC101245697;Z-ISO;novel.729;ODD</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GO:0008610</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>lipid biosynthetic process</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>6.258800260937397e-06</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.001466794546866828</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.189007680973552</v>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-2.637407302856445</v>
+      </c>
+      <c r="I40" t="n">
+        <v>13.8261547088623</v>
+      </c>
+      <c r="J40" t="n">
+        <v>153</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101250473', 'LOC101245297', 'LOC101263085', 'LOC101254591', 'PSY2', 'LOC101245370', 'LOC100134915', 'pds', 'AOS3', 'LOC101267522', 'SlFRK3', 'PIIGLB1', 'LOC101262639', 'LOC101260469', 'LOC101257572', 'ZEP', 'LOC104649012', '3OH-2', 'LOC101255340', 'MTS2', 'LOC104645573', 'TTS2', 'LOC101260812', 'LOC101254497', 'HDS', 'LOC101244523', 'TAO2', 'TPS33', 'LOC101264777', 'CYP724B2', 'NXD1', 'SNF1', 'TPS35', 'CRTISO', '3OH-1', 'LOC101263151', 'LOC101244466', 'dxs2', 'LOC101264840', 'LOC101248511', 'PHS1', 'TPS17', 'LOC101263090', 'LOC101267934', 'LOC101264879', 'LOC101263535', 'LOC101249057', 'AOS2', 'SlGPAT6', 'LOC101250481', 'HPL', 'LOC101255411', 'LOC101244831', 'LOC101256694', 'TPS24', 'SppS', 'TPS16', 'TPS31', 'CrtR-b2', 'LOC101252202', 'TomloxC', 'SlCPTBP', 'novel.729', 'HMG2', 'MDC', 'LOC101266963', 'TPS32', 'LOC101249786', 'TPS3', 'opr3', 'LOC101247770', 'LOC101246651', 'NDPS1', 'novel.915', 'LOC101246390', 'TPS14', 'LOC101251763', 'LOC101246730', 'GA2ox2', 'LOC101250561', 'LOC101249584', 'TPS28', 'novel.93', 'LOC101252161', 'GGPS2', 'SD1', 'LOC101244092', 'LOC101258806', 'novel.879', 'LOC101256685', 'LOC101261489', 'LOC107648852', 'LOC101255353', 'LOC101251311', 'LOC101263606', 'novel.572', 'zds', 'TAO3', 'LOC101254424', 'LOC100037490', 'LOC101250807', 'LOC101254190', 'LOC101245704', 'LOC101260363', 'LOC101268510', 'Psy1', 'CYP85A1', 'novel.92', 'NSGT1', 'NSY', 'LOC101247014', 'LOC101246396', 'LOC101246264', 'LOC101246676', 'LOC101252583', 'TomloxE', 'OPR1', 'LOC101266160', 'LOC101250586', 'LOC101247110', 'novel.105', 'LOC543694', 'LOC101266174', 'LOC101267503', 'LOC101267959', 'DXR', 'THM6', 'LOC101249394', '20ox-2', 'LOC101250012', 'TPS37', 'Sip1', 'LOC101253180', 'LOC101244691', 'TPS7', 'novel.113', 'MTS1', 'dxs', 'TPS36', 'SSTLE1', 'TCTR1', 'LOC101262198', 'LeNCED1', 'LOC101258273', 'TPS39', 'LOC101248790', 'LOC101256513', 'SlscADH1', 'TPS38', 'Z-ISO', 'LOXB', 'HMGR', 'LOC543658'})</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>LOC543694;Psy1;SlGPAT6;HDS;GA2ox2;LOC101252161;SD1;NDPS1;TPS32;LOC101256685;LOC101244691;LOC101250481;LOC101244523;LOC101250807;LOC101253180;LOC101263606;LOC101258273;LOC101264840;zds;novel.92;THM6;LOC101263085;ZEP;LOC101263090;TPS33;LOC101248511;TPS37;novel.113;TPS38;LOC101252202;LOC104645573;LOC101246264;TAO3;LOC101245704;LOC101267503;3OH-1;LOC101247770;LOC101247110;LOC101246676;LOC101254591;NXD1;LOC101257572;TomloxE;LOC101244831;LOC101254497;LOC101260363;LeNCED1;LOC101250561;LOC101266963;TPS39;PSY2;LOC101249057;LOC101244466;LOC101262639;CYP724B2;LOC101251311;LOC101246390;LOC101268510;LOC101245297;LOC101256694;GGPS2;LOC101249584;MTS1;3OH-2;LOC101247014;LOC100134915;LOC101262198;NSGT1;dxs;MTS2;TPS31;LOC101249394;LOC101249786;LOC101261489;SSTLE1;SlFRK3;LOC100037490;CrtR-b2;HMG2;LOC101246651;LOC101244092;novel.879;LOC101263151;TPS35;LOC101255353;Sip1;LOC101250012;CRTISO;LOC543658;TAO2;novel.105;DXR;NSY;LOC101252583;20ox-2;LOC101260812;LOC101264777;LOC101250586;AOS2;LOC101267934;TPS14;AOS3;LOC101246730;LOC101250473;TPS24;LOC101255411;LOC101246396;LOC107648852;LOC101266174;LOC101248790;OPR1;LOXB;novel.93;novel.915;SppS;pds;HMGR;TPS36;novel.572;MDC;HPL;SNF1;SlCPTBP;LOC101264879;LOC101254190;TPS16;LOC101245370;LOC101267522;LOC104649012;LOC101256513;CYP85A1;TPS7;LOC101266160;LOC101258806;Z-ISO;TPS28;LOC101267959;TPS17;TTS2;LOC101254424;LOC101251763;novel.729;LOC101263535;TomloxC;PIIGLB1;LOC101260469;LOC101255340;SlscADH1;PHS1;TCTR1;TPS3;dxs2;opr3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GO:0019684</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>photosynthesis, light reaction</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6.713848127604297e-06</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.001481405772926062</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.2700702605583635</v>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-2.969672679901123</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6.671913146972656</v>
+      </c>
+      <c r="J41" t="n">
+        <v>37</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101263132', 'LyesC2p072', 'LOC101259223', 'LOC101250650', 'PSBO', 'OEE1', 'LOC101245729', 'LOC101262260', 'LOC101249002', 'LOC101253996', 'LOC101254513', 'LOC101250586', 'LOC101254882', 'LOC101260852', 'LyesC2p089', 'CAB9', 'LOC101257676', 'LyesC2p073', 'LOC104649438', 'LyesC2p053', 'SLTAB2', 'LOC101262961', 'CAB4', 'LOC101252117', 'LOC101256426', 'LyesC2p075', 'PSBR', 'LOC101262255', 'SPA', 'LyesC2p074', 'CAB7', 'LOC101255672', 'LOC101254806', 'LOC101259692', 'VKOR', 'LOC101251312', 'LOC101252151'})</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>LOC101262260;OEE1;SPA;LOC101252151;LOC101249002;CAB9;LOC101245729;PSBO;LyesC2p089;LyesC2p073;SLTAB2;LOC101263132;VKOR;LOC101256426;LOC101257676;LOC101262961;LyesC2p074;LOC101254806;LOC101259223;LOC101259692;LOC101254513;LOC101253996;CAB7;LOC101250586;LOC104649438;LOC101260852;LyesC2p072;CAB4;PSBR;LOC101254882;LOC101250650;LOC101251312;LOC101262255;LyesC2p053;LOC101255672;LOC101252117;LyesC2p075</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GO:1900367</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>positive regulation of defense response to insect</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>6.772656688171575e-06</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.001481405772926062</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.6615420590096579</v>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.6109678149223328</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8.475418090820312</v>
+      </c>
+      <c r="J42" t="n">
+        <v>11</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>frozenset({'sbt4b', 'sbt3', 'sbt4e', 'LOC101252733', 'sbt4c', 'sbt4d', 'LOC101055569', 'LOC101253643', 'LOC101260044', 'sbt4a', 'LOC101248896'})</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>LOC101260044;sbt3;sbt4d;sbt4b;LOC101248896;sbt4e;LOC101253643;sbt4a;LOC101055569;sbt4c;LOC101252733</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GO:0044283</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>small molecule biosynthetic process</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>8.601495816084922e-06</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.001840533115602693</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.1813629826565857</v>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-3.278107643127441</v>
+      </c>
+      <c r="I43" t="n">
+        <v>13.45409107208252</v>
+      </c>
+      <c r="J43" t="n">
+        <v>149</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101250473', 'LOC101245297', 'LOC101254591', 'SlGGP-LIKE', 'LEAS1', 'SlFBA2', 'LOC101256592', 'LOC101260852', 'LOC101245370', 'LOC100134915', 'AOS3', 'LOC104648641', 'ribA', 'SlFBA3', 'SlFRK3', 'PIIGLB1', 'PAL3', 'LOC101260469', 'ZEP', '3OH-2', 'LOC101255340', 'SK', 'LOC104644402', 'LOC104645573', 'MIOX', 'LOC101254497', 'GCH1', 'LOC101263675', 'TAO2', 'SlFBA8', 'PRO2', 'LOC101258391', 'LOC101244800', 'SNF1', 'LOC101264863', 'OAT', '3OH-1', 'dxs2', 'MKS1b', 'LOC101248511', 'THIC', 'PHS1', 'LOC101259236', 'THM16', 'LOC101263535', 'MKS1d', 'LOC101249057', 'AOS2', 'LOC101266918', 'LOC101257319', 'PAL2', 'LOC101250481', 'MKS1e', 'HPL', 'LOC101255411', 'LOC101244614', 'LOC101256694', 'TPS24', 'SppS', 'TMT', 'LOC101252202', 'TomloxC', 'SlCPTBP', 'LOC101263281', 'LOC101256529', 'NAOD', 'LOC101249786', 'LOC101254281', 'opr3', 'LOC101254608', 'LOC101252192', 'LOC101247770', 'LOC101267184', 'LOC101259725', 'NDPS1', 'GS1', 'LOC101247693', 'novel.915', 'LOC101251350', 'GABA-TP2', 'LOC101248500', 'SlFBA1', 'GA2ox2', 'LOC101250561', 'LOC101267663', 'OTC', 'PAL5', 'LOC101249584', 'LOC101254439', 'LOC101252161', 'LOC101263817', 'LOC101244092', 'novel.879', 'LOC101256685', 'SlFBA6', 'LOC107648852', 'NAGK', 'LOC101251311', 'LOC101263606', 'TAO3', 'LOC543920', 'LOC101251816', 'LOC101250807', 'LOC101260363', 'LOC101268510', 'LOC101055519', 'novel.92', 'NSY', 'MKS1a', 'LOC101246283', 'LOC101247014', 'GME1', 'LOC101246396', 'LOC101244469', 'LOC101254848', 'LOC101252583', 'TomloxE', 'OPR1', 'LOC101266160', 'LOC101250586', 'PAT', 'LOC101254332', 'novel.105', 'LOC543694', 'LOC101266174', 'LOC101267503', 'LOC101267959', 'LOC101247833', 'SlVTE5', 'LOC101254112', 'LOC101247891', '20ox-2', 'LOC101247914', 'Sip1', 'LOC101252466', 'NAOAT', 'LOC101244691', 'LOC101259366', 'novel.113', 'LOC101253805', 'dxs', 'SlFBA7', 'TCTR1', 'LOC101262198', 'LeNCED1', 'LOC101258500', 'LOC101248790', 'LOC101256513', 'LOXB'})</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>LOC543694;LOC101258500;NAOD;GA2ox2;LOC101247891;LOC101252161;NDPS1;LOC101263817;SlFBA1;LOC101256685;MKS1e;LOC101244691;LOC101251816;SlGGP-LIKE;MKS1d;LOC101250481;LOC101250807;LOC101263606;LEAS1;LOC104648641;novel.92;ZEP;LOC101252192;GABA-TP2;LOC101248511;novel.113;LOC101263675;LOC101252202;LOC104645573;LOC101256592;TAO3;LOC101267503;MIOX;3OH-1;LOC101247770;LOC101259725;LOC101254591;LOC101259366;TomloxE;GME1;LOC101254497;LOC101260363;LOC101253805;LeNCED1;LOC101251350;SlFBA3;LOC101250561;THM16;LOC101264863;LOC101249057;LOC101254439;LOC101267663;LOC101251311;LOC101268510;LOC101245297;LOC101254608;LOC101256694;LOC101257319;PAT;LOC101249584;3OH-2;SlFBA7;LOC101247014;LOC101259236;LOC100134915;LOC101262198;PRO2;dxs;LOC101249786;SlFRK3;LOC101247914;SlFBA6;MKS1a;LOC101247693;LOC101254281;LOC101263281;LOC101244092;novel.879;LOC101244800;LOC101266918;LOC101254332;Sip1;PAL3;SK;LOC101055519;TAO2;novel.105;NSY;LOC101252583;20ox-2;LOC101250586;AOS2;PAL5;LOC101256529;AOS3;LOC101248500;PAL2;LOC101260852;LOC101250473;TPS24;LOC101255411;LOC101246396;LOC107648852;LOC101266174;LOC101244469;SlFBA2;GCH1;LOC101248790;OPR1;LOXB;ribA;OTC;novel.915;SppS;LOC101252466;LOC101267184;OAT;SlFBA8;LOC101244614;HPL;LOC101254848;MKS1b;SNF1;TMT;SlCPTBP;LOC101245370;THIC;LOC101258391;NAGK;LOC101256513;NAOAT;LOC543920;LOC101247833;LOC101266160;LOC101267959;GS1;LOC101263535;LOC101246283;TomloxC;PIIGLB1;LOC101260469;LOC101255340;LOC101254112;LOC104644402;PHS1;TCTR1;SlVTE5;dxs2;opr3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GO:0016053</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>organic acid biosynthetic process</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1.306919265241283e-05</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.002737022622929775</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1944177735636406</v>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-3.452275991439819</v>
+      </c>
+      <c r="I44" t="n">
+        <v>13.48096561431885</v>
+      </c>
+      <c r="J44" t="n">
+        <v>122</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101250473', 'LOC101245297', 'LOC101254591', 'SlGGP-LIKE', 'LEAS1', 'LOC101256592', 'LOC101245370', 'LOC100134915', 'AOS3', 'LOC104648641', 'SlFRK3', 'PIIGLB1', 'PAL3', 'ZEP', '3OH-2', 'LOC101255340', 'SK', 'LOC104644402', 'LOC104645573', 'MIOX', 'LOC101254497', 'TAO2', 'PRO2', 'LOC101258391', 'SNF1', 'OAT', '3OH-1', 'MKS1b', 'LOC101248511', 'PHS1', 'LOC101259236', 'THM16', 'LOC101263535', 'MKS1d', 'LOC101249057', 'AOS2', 'LOC101266918', 'LOC101257319', 'PAL2', 'LOC101250481', 'MKS1e', 'HPL', 'LOC101255411', 'LOC101244614', 'LOC101256694', 'TPS24', 'LOC101252202', 'TomloxC', 'LOC101256529', 'NAOD', 'LOC101249786', 'LOC101254281', 'opr3', 'LOC101254608', 'LOC101252192', 'LOC101247770', 'LOC101267184', 'LOC101259725', 'GS1', 'LOC101247693', 'novel.915', 'LOC101251350', 'GABA-TP2', 'GA2ox2', 'LOC101250561', 'LOC101267663', 'OTC', 'PAL5', 'LOC101254439', 'LOC101252161', 'LOC101263817', 'LOC101244092', 'novel.879', 'LOC101256685', 'LOC107648852', 'NAGK', 'LOC101251311', 'LOC101263606', 'TAO3', 'LOC543920', 'LOC101251816', 'LOC101250807', 'LOC101260363', 'LOC101268510', 'LOC101055519', 'novel.92', 'MKS1a', 'LOC101246283', 'LOC101247014', 'GME1', 'LOC101246396', 'LOC101244469', 'LOC101254848', 'LOC101252583', 'TomloxE', 'OPR1', 'LOC101250586', 'PAT', 'LOC101254332', 'novel.105', 'LOC543694', 'LOC101266174', 'LOC101267503', 'LOC101267959', 'LOC101247833', 'LOC101254112', 'LOC101247891', '20ox-2', 'LOC101247914', 'Sip1', 'LOC101252466', 'NAOAT', 'LOC101244691', 'LOC101259366', 'novel.113', 'TCTR1', 'LOC101262198', 'LeNCED1', 'LOC101258500', 'LOC101248790', 'LOC101256513', 'LOXB'})</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>LOC543694;LOC101258500;NAOD;GA2ox2;LOC101247891;LOC101252161;LOC101263817;LOC101256685;MKS1e;LOC101244691;LOC101251816;SlGGP-LIKE;MKS1d;LOC101250481;LOC101250807;LOC101263606;LEAS1;LOC104648641;novel.92;ZEP;LOC101252192;GABA-TP2;LOC101248511;novel.113;LOC101252202;LOC104645573;LOC101256592;TAO3;LOC101267503;MIOX;3OH-1;LOC101247770;LOC101259725;LOC101254591;LOC101259366;TomloxE;GME1;LOC101254497;LOC101260363;LeNCED1;LOC101251350;LOC101250561;THM16;LOC101249057;LOC101254439;LOC101267663;LOC101251311;LOC101268510;LOC101245297;LOC101254608;LOC101256694;LOC101257319;PAT;3OH-2;LOC101247014;LOC101259236;LOC100134915;LOC101262198;PRO2;LOC101249786;SlFRK3;LOC101247914;MKS1a;LOC101247693;LOC101254281;LOC101244092;novel.879;LOC101266918;LOC101254332;Sip1;PAL3;SK;LOC101055519;TAO2;novel.105;LOC101252583;20ox-2;LOC101250586;AOS2;PAL5;LOC101256529;AOS3;PAL2;LOC101250473;TPS24;LOC101255411;LOC101246396;LOC107648852;LOC101266174;LOC101244469;LOC101248790;OPR1;LOXB;OTC;novel.915;LOC101252466;LOC101267184;OAT;LOC101244614;HPL;LOC101254848;MKS1b;SNF1;LOC101245370;LOC101258391;NAGK;LOC101256513;NAOAT;LOC543920;LOC101247833;LOC101267959;GS1;LOC101263535;LOC101246283;TomloxC;PIIGLB1;LOC101255340;LOC101254112;LOC104644402;PHS1;TCTR1;opr3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GO:0010207</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>photosystem II assembly</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1.59981672897407e-05</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.003280624179852453</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.123967153629185</v>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-3.182448387145996</v>
+      </c>
+      <c r="I45" t="n">
+        <v>6.589755058288574</v>
+      </c>
+      <c r="J45" t="n">
+        <v>12</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101263132', 'LOC101259223', 'LOC101255672', 'PSBO', 'LOC101252117', 'OEE1', 'LOC101256426', 'VKOR', 'CAB9', 'PSBR', 'LOC101253996', 'LOC101254513'})</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>OEE1;CAB9;PSBO;LOC101263132;VKOR;LOC101256426;LOC101259223;LOC101254513;LOC101253996;PSBR;LOC101255672;LOC101252117</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GO:0044281</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>small molecule metabolic process</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1.738198551269177e-05</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.00342699758667484</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.2228047215982601</v>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-3.393838167190552</v>
+      </c>
+      <c r="I46" t="n">
+        <v>12.68965625762939</v>
+      </c>
+      <c r="J46" t="n">
+        <v>314</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH2B7d', 'LOC101263085', 'LOC101254591', 'LOC101267118', 'LOC101254882', 'LOC112940921', 'LOC101256592', 'LOC101245370', 'LOC101255271', 'LOC101244906', 'SlFBA3', 'PIIGLB1', 'PAL3', 'LOC101249670', 'PDH', 'ZEP', 'GCH1', 'LOC101263675', 'LOC101244523', 'SlDMR6-1', 'LOC101264840', 'LOC101248511', 'PP2Ac1', 'LOC101252837', 'LOC101263535', 'LOC101264873', 'MKS1e', 'LOC101252202', 'TomloxC', 'SlCPTBP', 'LOC101263281', 'LOC101267103', 'NAOD', 'LOC778303', 'LOC101254281', 'nii1', 'LOC101244007', 'LOC101264132', 'opr3', 'LOC101254608', 'LOC101261928', 'PP2Ac2', 'LOC101259725', 'LOC101259689', 'NDPS1', 'LOC101266950', 'LOC104646631', 'GABA-TP2', 'LOC101259235', 'LOC101258355', 'LOC101263369', 'LOC101253541', 'GA2ox2', 'LOC101250561', 'ACS6', 'LOC101244092', 'LOC101256685', 'LOC101245480', 'LOC101250807', 'LOC101268146', 'SlADH12A1', 'LOC101262091', 'LOC101250891', 'LOC101258079', 'NSY', 'LOC101260990', 'LOC101247014', 'LOC101255254', 'LOC101262221', 'LOC101250164', 'LOC101252583', 'LOC101249935', 'PAT', 'LOC101267959', 'LOC101267503', 'LOC101263406', 'LOC101252025', 'LOC101254112', 'LOC101266713', 'LOC101244691', 'novel.113', 'LOC101253805', 'SlFBA7', 'LOC101256513', 'NDK', 'SlGGP-LIKE', 'SlFBA2', 'LOC101254720', 'LOC100134915', 'LOC104648641', 'LOC101258131', 'ribA', 'SlFRK3', 'SlADH11A4a', 'LOC101264109', 'HXK3', 'LOC101257326', '3OH-2', 'SK', 'MIOX', 'LOC101254497', 'LOC101264480', 'LOC101258391', 'LOC101244800', 'SNF1', 'LOC101264863', 'novel.966', 'gdh1', '3OH-1', 'MKS1b', 'LOC101259236', 'LOC101259572', 'THM16', 'LOC101252681', 'MKS1d', 'LOC101249057', 'AOS2', 'PAL2', 'LOC101260607', 'WRKYIId', 'HPL', 'SlALDH2B7a', 'LOC101255411', 'TPS24', 'LOC544276', 'LOC101251091', 'LOC101268347', 'LOC101244882', 'ACS2', 'LOC101247693', 'LOC101253342', 'LOC101251035', 'LOC101248500', 'novel.516', 'LOC109120859', 'SlFBA1', 'PGH1', 'LOC101267663', 'PAL5', 'LOC101245553', 'LOC101252161', 'THM27', 'LOC101246116', 'TAO3', 'LOC101251816', 'MST2', 'LOC101250791', 'LOC101055519', 'novel.92', 'LOC101260960', 'LOC101248029', 'LOC101251366', 'LOC101246396', 'SIZ1', 'LOC101244469', 'LOC101267346', 'P18', 'LOC101250586', 'LOC101255874', 'LOC101266174', 'LOC543694', 'SlVTE5', 'LOC101247833', 'ODC', '20ox-2', 'ARF1', 'LOC101247914', 'LOC101247047', 'LeNCED1', 'LOC101266485', 'SAM3', 'LOC101249663', 'LOC101258525', 'LOC101245297', 'ME2', 'LEAS1', 'LOC101249193', 'LOC101245952', 'LOC101260852', 'LOC101263879', 'ureD', 'HDS', 'PRO2', 'SlALDH6B2', 'LOC101250058', 'OAT', 'SCOA', 'LOC101254137', 'dxs2', 'LOC101250287', 'LOC101252977', 'PHS1', 'LOC101258787', 'LOC101266918', 'LOC101244614', 'SAHH', 'TMT', 'LOC101263008', 'LOC101256529', 'MDC', 'NR', 'LOC101252192', 'LOC101247770', 'GS1', 'novel.915', 'LOC101251350', 'novel.312', 'LOC101257261', 'OTC', 'LOC101254439', 'LOC107648852', 'LOC101263606', 'LOC543920', 'LOC101260363', 'ACS4', 'TAL', 'ME1', 'LOC101268510', 'MKS1a', 'LOC104648010', 'LOC101254848', 'TomloxE', 'OPR1', 'SAM1', 'LOC101266160', 'novel.105', 'adc1', 'LOC101247891', 'LOC101252466', 'NAOAT', 'LOC101259366', 'LOC101247250', 'dxs', 'mMDH1', 'TCTR1', 'LOC101262198', 'LOC101258500', 'LOC101248790', 'LOC543658', 'novel.168', 'LOC101256649', 'LOC101250473', 'LyesC2p062', 'GolS-1', 'LOC101256077', 'AOS3', 'ureF', 'LOC101260469', 'LOC101255340', 'LOC101250354', 'LOC104644402', 'LOC104645573', 'TAO2', 'SlFBA8', 'LOC101258461', 'LOC101264724', 'LOC109120519', 'hdc', 'LOC101248505', 'SSADH', 'THIC', 'LOC101259139', 'LOC101257319', 'LOC101250481', 'MKK2', 'LOC101264255', 'LOC101254597', 'LOC101256694', 'MST1', 'SppS', 'LysRS', 'HMG2', 'SDH', 'LOC101249786', 'LOC101267184', 'LOC101252738', 'LOC101261578', 'LOC101252453', 'LOC101246995', 'LOC101251763', 'LOC101264004', 'SlMYB21', 'LOC101249584', 'LOC101263817', 'novel.879', 'SlFBA6', 'NAGK', 'LOC101251311', 'LOC101258830', 'LOC101261642', 'NRT2.2', 'LOC101257857', 'HXK4', 'mMDH2', 'LOC101246283', 'LOC101265950', 'GME1', 'LOC101264576', 'LOC101249166', 'LOC778326', 'LOC101254332', 'DXR', 'LOC101248052', 'LOC101262503', 'LOC101249671', 'Slalpha-kGDH', 'LOC101249394', 'LOC101247828', 'Sip1', 'LOC101247538', 'mdh', 'novel.706', 'LOXB', 'HMGR'})</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>LOC543694;LOC101250791;LOC101265950;LOC101247250;LOC101258500;NAOD;HDS;GA2ox2;LOC101247891;LOC101252161;NDPS1;LOC101263817;SlFBA1;LOC778303;NDK;LOC101256685;PP2Ac2;MKS1e;LOC101244691;LOC101251816;LOC104646631;SlGGP-LIKE;MKS1d;LOC101250481;LOC101247828;LOC101244523;LOC101266713;LOC101258131;LOC101250807;LOC101247047;LOC101249671;LOC101263606;LOC101252025;LEAS1;LOC101264840;SAM3;LOC101258461;LOC104648641;LOC101253541;novel.92;LOC101246116;LOC101249935;LOC101263085;HXK4;ZEP;P18;LOC101252192;LOC101256077;SAM1;adc1;GABA-TP2;PGH1;LOC101267118;LOC101250058;LOC101244906;LOC101248511;LOC101252453;LOC101262503;HXK3;LOC101245553;SlMYB21;novel.113;LOC101263675;LOC101252202;mdh;LOC101251091;LOC101249193;LOC104645573;LOC101256592;TAO3;LOC101261578;LOC101267503;MIOX;ODC;3OH-1;LOC101245952;LOC101247770;LOC101259725;SIZ1;LOC101254591;LOC101259366;ACS6;LOC101255271;LOC112940921;TomloxE;LysRS;LOC101264109;LOC101264255;GME1;SlALDH2B7a;LOC101254497;LOC101260363;LOC101263879;LOC101253805;LOC101264004;LeNCED1;LOC101259139;LOC101251350;SlFBA3;LOC101250561;THM16;MST2;LOC101244007;LOC101264863;LOC101259572;ureD;ACS2;LOC101264873;LOC101249057;LOC101254439;ARF1;LOC101267663;LOC101258079;NR;LOC101251311;LOC101251366;LOC101251035;novel.516;LOC101268510;LOC101250287;LOC101245297;LOC101254608;LOC101256694;LOC101261928;LOC101257319;Slalpha-kGDH;PAT;LOC101250164;SSADH;PP2Ac1;LOC101249584;LOC101250354;SlADH11A4a;3OH-2;SlFBA7;LOC101266950;LOC101247014;LOC101257261;LOC101257326;novel.966;LOC101259236;LOC101266485;LOC100134915;LyesC2p062;LOC101262198;PRO2;dxs;LOC101258355;LOC101249394;LOC101254720;LOC101249786;SlADH12A1;SAHH;SlADH2B7d;SlFRK3;ACS4;SDH;LOC101247914;SlALDH6B2;LOC101253342;SlFBA6;LOC101249670;MKS1a;HMG2;LOC101247693;LOC101254281;LOC101244882;LOC101263281;LOC101255254;ME1;LOC101260990;LOC101248029;LOC101244092;novel.879;LOC101244800;LOC101254137;LOC101248052;LOC101263008;mMDH1;LOC101266918;LOC101254332;LOC101254597;ME2;Sip1;PAL3;SK;LOC543658;LOC101055519;LOC104648010;TAO2;novel.105;MKK2;DXR;NSY;LOC101252583;20ox-2;NRT2.2;LOC101258787;LOC101250586;AOS2;PAL5;ureF;LOC101256529;AOS3;LOC101248500;PAL2;LOC101262221;LOC101260852;LOC101250473;LOC101259235;TPS24;LOC101255411;hdc;LOC101246396;LOC107648852;LOC101266174;LOC101252977;LOC101263369;LOC101256649;LOC101249663;LOC101259689;LOC101244469;SlDMR6-1;SlFBA2;LOC101267346;LOC101261642;GCH1;LOC101248790;OPR1;LOXB;LOC101260960;LOC101268347;LOC101254882;LOC544276;LOC101247538;mMDH2;ribA;MST1;OTC;LOC101264132;novel.915;LOC101264480;LOC101267103;SppS;LOC101248505;LOC101252466;HMGR;LOC101267184;LOC109120859;MDC;LOC778326;OAT;GolS-1;SlFBA8;LOC101244614;HPL;LOC101254848;SCOA;WRKYIId;MKS1b;SNF1;LOC101263406;TMT;novel.168;SlCPTBP;LOC101257857;nii1;LOC101268146;LOC101245370;THIC;LOC101252837;LOC101258391;NAGK;LOC101256513;TAL;NAOAT;gdh1;LOC101249166;LOC101260607;LOC543920;LOC101247833;LOC101266160;PDH;LOC101252738;LOC101264724;LOC109120519;LOC101267959;LOC101262091;THM27;LOC101251763;novel.706;LOC101250891;LOC101245480;LOC101252681;GS1;LOC101263535;LOC101246283;TomloxC;PIIGLB1;novel.312;LOC101260469;LOC101255340;LOC101246995;LOC101254112;LOC104644402;LOC101258525;PHS1;LOC101264576;TCTR1;LOC101258830;SlVTE5;dxs2;opr3;LOC101255874</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GO:0035251</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UDP-glucosyltransferase activity</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1.740829821535528e-05</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.00342699758667484</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.1207889344733883</v>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-1.880221247673035</v>
+      </c>
+      <c r="I47" t="n">
+        <v>11.31186771392822</v>
+      </c>
+      <c r="J47" t="n">
+        <v>43</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101263151', 'GAME3', 'LOC101260997', 'LOC101055573', 'LOC101255510', 'LOC101260093', 'LOC101263090', 'LOC101259221', 'GAME1', 'LOC101254402', 'LOC101255377', 'LOC101251337', 'SlGGP-LIKE', 'SlUGT75C1', 'LOC101256154', 'LOC101249176', 'ert1b', 'twi1', 'LOC101268453', 'sus3', 'LOC101248661', 'LOC101252007', 'LOC100529103', 'sps', 'LOC101256157', 'LOC101246612', 'LOC101258806', 'LOC101258947', 'LOC101258117', 'LOC101244237', 'SUS4', 'LOC101251018', 'LOC101251036', 'LOC101259617', 'gtsatom', 'LOC101247047', 'LOC101268254', 'LOC101250431', 'LOC101250058', 'LOC101253864', 'novel.706', 'LOC101258702', 'novel.70'})</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>LOC101268254;LOC101251036;LOC101259617;SlGGP-LIKE;LOC101247047;LOC101055573;LOC101263090;gtsatom;LOC101250058;LOC101251337;sus3;LOC101254402;LOC101251018;LOC101248661;LOC101255510;ert1b;LOC101260997;SUS4;LOC101256157;LOC101250431;twi1;GAME1;LOC101255377;LOC101246612;LOC101253864;LOC101263151;LOC101259221;LOC101260093;LOC101244237;novel.70;LOC101258702;GAME3;LOC101252007;LOC100529103;LOC101256154;LOC101268453;LOC101258117;SlUGT75C1;LOC101258806;novel.706;LOC101258947;LOC101249176;sps</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GO:0005615</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>extracellular space</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2.585604136732031e-05</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.00499021598389282</v>
+      </c>
+      <c r="E48" t="n">
+        <v>7</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.1589160129882413</v>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.4980916380882263</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8.773968696594238</v>
+      </c>
+      <c r="J48" t="n">
+        <v>46</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>frozenset({'CHI14', 'novel.867', 'CHI3', 'novel.710', 'LOC101256306', 'LOC101260044', 'sbt4a', 'SlCKX4', 'LOC101268808', 'sbt4b', 'LOC101247374', 'sbt3', 'sbt4e', 'LOC101252733', 'SlCYP1', 'sbt4c', 'LOC101250380', 'LOC101246103', 'novel.438', 'LOC101253643', 'SlCKX2', 'novel.670', 'novel.696', 'PR1a2', 'LOC101249996', 'LOC101252653', 'LOC100191111', 'LOC101246829', 'LOC101264531', 'P4', 'p69c', 'p69F', 'LOC101245521', 'pip1', 'LOC101254190', 'LOC101267778', 'P69B', 'P69A', 'CHI17', 'sbt4d', 'LOC101260447', 'PR1b1', 'LOC109118719', 'p69d', 'LOC101260130', 'PR-1a1'})</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>P4;LOC109118719;PR1a2;LOC101260044;LOC101252653;p69c;PR1b1;LOC101268808;SlCYP1;P69B;sbt3;LOC101250380;sbt4d;LOC101245521;PR-1a1;CHI17;SlCKX4;LOC101249996;CHI14;sbt4b;novel.710;novel.696;SlCKX2;P69A;CHI3;LOC100191111;LOC101260130;novel.438;LOC101256306;sbt4e;p69d;LOC101260447;LOC101253643;LOC101254190;novel.867;LOC101267778;sbt4a;p69F;LOC101246829;LOC101246103;LOC101247374;LOC101264531;sbt4c;novel.670;pip1;LOC101252733</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GO:0016998</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>cell wall macromolecule catabolic process</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2.94212012263908e-05</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.005188955697240972</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.1219374033709468</v>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-1.835960388183594</v>
+      </c>
+      <c r="I49" t="n">
+        <v>10.09475708007812</v>
+      </c>
+      <c r="J49" t="n">
+        <v>19</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>frozenset({'SlArf_Xyl2', 'CHI14', 'XYL1', 'LOC101251335', 'novel.622', 'CHI3', 'ARF1', 'SlArf_Xyl4', 'LOC101266643', 'XTH6', 'SlArf_Xyl1', 'LOC101254239', 'LOC101263519', 'LOC101266770', 'LOC101256554', 'SlArf_Xyl3', 'CHI9', 'CHI17', 'LOC101254249'})</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>SlArf_Xyl3;CHI9;XYL1;LOC101254239;CHI17;CHI14;ARF1;LOC101263519;LOC101254249;XTH6;CHI3;LOC101256554;SlArf_Xyl4;novel.622;LOC101266770;LOC101251335;LOC101266643;SlArf_Xyl1;SlArf_Xyl2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>GO:0010360</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>negative regulation of anion channel activity</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3.110315819742124e-05</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.005188955697240972</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.0002047502047503036</v>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-2.837721586227417</v>
+      </c>
+      <c r="I50" t="n">
+        <v>8.583328247070312</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>GO:0034763,GO:0032410,GO:1903960,GO:1903792,GO:0032413,GO:0034766,GO:0043271</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101244003', 'LOC101248778', 'PHOT1', 'PP2C-2', 'PHOT2'})</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>PHOT1;PHOT2;LOC101244003;PP2C-2;LOC101248778</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GO:0016762</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>xyloglucan:xyloglucosyl transferase activity</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3.790559069808254e-05</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.006052266432695157</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.06428059200678544</v>
+      </c>
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-1.380279898643494</v>
+      </c>
+      <c r="I51" t="n">
+        <v>10.70440006256104</v>
+      </c>
+      <c r="J51" t="n">
+        <v>15</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101265927', 'XTH7', 'XTH16', 'LOC543511', 'XET4', 'XTH1', 'tXET-B2', 'XTH5', 'XTH6', 'XET2', 'XTH9', 'tXET-B1', 'LOC101261871', 'LOC101256574', 'XTH3'})</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>LOC543511;LOC101265927;XTH7;XTH5;tXET-B2;tXET-B1;XTH6;XTH3;XET2;LOC101261871;LOC101256574;XTH9;XTH16;XET4;XTH1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>GO:0097264</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>self proteolysis</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3.812257633110838e-05</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.006052266432695157</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.662396569515351</v>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.6979764103889465</v>
+      </c>
+      <c r="I52" t="n">
+        <v>8.533289909362793</v>
+      </c>
+      <c r="J52" t="n">
         <v>9</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>frozenset({'LOC112940921', 'novel.168', 'LOC101252520', 'LOC101252192', 'LOC104648550', 'LOC101261578', 'LOC101253176', 'HDS', 'LOC101260990'})</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>LOC101252520;LOC112940921;LOC101261578;LOC101253176;LOC101260990;LOC104648550;HDS;LOC101252192;novel.168</t>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>frozenset({'sbt4b', 'sbt3', 'sbt4e', 'LOC101252733', 'sbt4c', 'sbt4d', 'LOC101260044', 'sbt4a', 'LOC101253643'})</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>LOC101260044;sbt3;sbt4d;sbt4b;sbt4e;LOC101253643;sbt4a;sbt4c;LOC101252733</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>GO:0031408</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>oxylipin biosynthetic process</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3.89716678363193e-05</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.006088859150998267</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.05283720128587177</v>
+      </c>
+      <c r="G53" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-3.606182098388672</v>
+      </c>
+      <c r="I53" t="n">
+        <v>13.66263198852539</v>
+      </c>
+      <c r="J53" t="n">
+        <v>19</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>GO:0031407</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>frozenset({'MKS1b', 'LOC101246396', 'OPR1', 'TomloxE', 'LOC101250586', 'LOC101254332', 'LOC101263535', 'novel.105', 'LOC101266174', 'MKS1d', 'AOS2', 'AOS3', 'MKS1e', 'HPL', 'LOC107648852', 'TomloxC', 'opr3', 'LOXB', 'MKS1a'})</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>MKS1e;MKS1d;TomloxE;MKS1a;LOC101254332;novel.105;LOC101250586;AOS2;AOS3;LOC101246396;LOC107648852;LOC101266174;OPR1;LOXB;HPL;MKS1b;LOC101263535;TomloxC;opr3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>GO:0019253</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>reductive pentose-phosphate cycle</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4.196197487592352e-05</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.006354334133903312</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.05792837508244444</v>
+      </c>
+      <c r="G54" t="b">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-3.701955318450928</v>
+      </c>
+      <c r="I54" t="n">
+        <v>8.109868049621582</v>
+      </c>
+      <c r="J54" t="n">
+        <v>12</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>GO:0019685</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101267611', 'LOC101264004', 'LOC101253541', 'LOC101260852', 'LOC101264109', 'Rbcs-3B', 'rbcS1', 'LOC101257875', 'LOC101253805', 'SBPase', 'LOC101266713', 'LOC101264255'})</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>LOC101266713;LOC101253541;LOC101267611;LOC101264109;LOC101264255;LOC101253805;LOC101264004;Rbcs-3B;rbcS1;LOC101260852;LOC101257875;SBPase</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GO:0015293</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>symporter activity</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5.384284399975816e-05</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.008029925961963932</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.03496260277152361</v>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-2.118463754653931</v>
+      </c>
+      <c r="I55" t="n">
+        <v>8.2178955078125</v>
+      </c>
+      <c r="J55" t="n">
+        <v>32</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>frozenset({'SUT2', 'LOC101264062', 'STP12', 'PMT6', 'LOC101248631', 'LOC101256192', 'SlLAX1', 'PT2', 'ST2', 'VGT1', 'LOC101249680', 'LOC101249671', 'ht2', 'LOC101263768', 'ST4.1', 'ht1', 'PT1', 'SUT4', 'LOC101246241', 'VGT2', 'LOC101267393', 'LOC100736477', 'LOC101252766', 'LOC101250791', 'LOC101251853', 'STP18', 'STP11', 'LOC101253320', 'PMT5', 'pGlcT1', 'LOC101250213', 'ST1'})</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ST1;LOC101250791;LOC100736477;PT1;VGT2;LOC101249671;STP11;LOC101267393;ht1;ST4.1;LOC101264062;LOC101249680;ht2;STP12;PMT5;LOC101253320;PMT6;LOC101252766;LOC101251853;SUT2;VGT1;LOC101250213;LOC101256192;SUT4;LOC101263768;PT2;LOC101246241;SlLAX1;pGlcT1;LOC101248631;ST2;STP18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GO:0015977</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>carbon fixation</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5.939038481602859e-05</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.00859675820212014</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.05399910699168652</v>
+      </c>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-3.856034517288208</v>
+      </c>
+      <c r="I56" t="n">
+        <v>8.261930465698242</v>
+      </c>
+      <c r="J56" t="n">
+        <v>14</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101261166', 'LOC101267611', 'LOC101264004', 'LOC101253541', 'LOC101260852', 'LOC101264109', 'Rbcs-3B', 'ppc2', 'rbcS1', 'LOC101257875', 'LOC101253805', 'SBPase', 'LOC101266713', 'LOC101264255'})</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>ppc2;LOC101266713;LOC101253541;LOC101267611;LOC101264109;LOC101264255;LOC101253805;LOC101264004;Rbcs-3B;LOC101261166;rbcS1;LOC101260852;LOC101257875;SBPase</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GO:0010252</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>auxin homeostasis</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5.939038481602859e-05</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.00859675820212014</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.1699852669042581</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-3.334070920944214</v>
+      </c>
+      <c r="I57" t="n">
+        <v>10.52791786193848</v>
+      </c>
+      <c r="J57" t="n">
+        <v>14</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>frozenset({'PIN2', 'PIN3', 'PIN9', 'PIN10', 'LOC100527965', 'LOC101263921', 'TCP23', 'PIN5', 'PIN7', 'LOC101244469', 'PIN4', 'LOC101262636', 'PIN8', 'PIN6'})</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>PIN2;PIN10;PIN9;PIN8;PIN6;TCP23;PIN5;PIN7;PIN3;LOC100527965;LOC101263921;LOC101244469;PIN4;LOC101262636</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GO:0043171</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>peptide catabolic process</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>6.214182798504283e-05</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.008864666852996762</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.5888227066816767</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.4634996056556702</v>
+      </c>
+      <c r="I58" t="n">
+        <v>8.467042922973633</v>
+      </c>
+      <c r="J58" t="n">
+        <v>11</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>frozenset({'sbt4b', 'sbt3', 'sbt4e', 'LOC101252733', 'LOC101246397', 'sbt4c', 'sbt4d', 'LOC101259958', 'LOC101260044', 'sbt4a', 'LOC101253643'})</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>LOC101260044;sbt3;sbt4d;sbt4b;LOC101259958;sbt4e;LOC101253643;LOC101246397;sbt4a;sbt4c;LOC101252733</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>GO:2000068</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>regulation of defense response to insect</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6.361945446624543e-05</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.008867093073140413</v>
+      </c>
+      <c r="E59" t="n">
+        <v>7</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.6267074008308764</v>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-0.457997053861618</v>
+      </c>
+      <c r="I59" t="n">
+        <v>8.278215408325195</v>
+      </c>
+      <c r="J59" t="n">
+        <v>13</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>frozenset({'WRKY81', 'sbt4b', 'sbt3', 'sbt4e', 'LOC101252733', 'sbt4c', 'sbt4d', 'LOC101246681', 'LOC101055569', 'LOC101253643', 'LOC101260044', 'sbt4a', 'LOC101248896'})</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>LOC101260044;sbt3;sbt4d;sbt4b;WRKY81;LOC101248896;sbt4e;LOC101246681;LOC101253643;sbt4a;LOC101055569;sbt4c;LOC101252733</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GO:0044255</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>cellular lipid metabolic process</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>6.448960193674841e-05</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.008867093073140413</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1284239564586286</v>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-2.587142705917358</v>
+      </c>
+      <c r="I60" t="n">
+        <v>13.95909023284912</v>
+      </c>
+      <c r="J60" t="n">
+        <v>176</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH2B7d', 'LOC101258525', 'LOC101250473', 'LOC101245297', 'LOC101263085', 'LOC101254591', 'PLDb2', 'PSY2', 'LOC101254720', 'LOC101245370', 'LOC100134915', 'pds', 'AOS3', 'TPLD', 'SlFRK3', 'PIIGLB1', 'LOC101262639', 'LOC101257572', 'ZEP', 'LOC104649012', '3OH-2', 'LOC101255340', 'LOC101250354', 'MTS2', 'LOC104645573', 'TTS2', 'LOC101260812', 'LOC101254497', 'HDS', 'LOC101244523', 'TAO2', 'TPS33', 'NXD1', 'SNF1', 'TPS35', 'CRTISO', '3OH-1', 'LOC101263151', 'LOC101244466', 'dxs2', 'LOC101264840', 'LOC101248511', 'PHS1', 'LOC101259139', 'TPS17', 'LOC101263090', 'PP2Ac1', 'LOC101265793', 'LOC101263535', 'LOC101249057', 'LOC101252788', 'AOS2', 'LOC101260607', 'SlGPAT6', 'LOC101250481', 'HPL', 'LOC101246303', 'SlALDH2B7a', 'PLDa1', 'LOC101254597', 'LOC101255411', 'LOC101256694', 'TPS24', 'SppS', 'TPS16', 'TPS31', 'CrtR-b2', 'LOC101252202', 'TomloxC', 'SlCPTBP', 'PLDa2', 'HMG2', 'MDC', 'LOC101266963', 'TPS32', 'LOC101249786', 'TPS3', 'LOC101264132', 'opr3', 'LOC101247770', 'PP2Ac2', 'LOC101252738', 'NDPS1', 'PLDb1', 'LOC101266950', 'LOC101252453', 'VDE', 'novel.915', 'TPS14', 'LOC101248500', 'LOC101246995', 'LOC101258355', 'LOC109120859', 'LOC101251763', 'LOC101246730', 'GA2ox2', 'LOC101250561', 'SlMYB21', 'LOC101249584', 'TPS28', 'LOC101252161', 'GGPS2', 'LOC101244092', 'LOC101258806', 'THM27', 'novel.879', 'LOC101256685', 'LOC101261489', 'LOC107648852', 'LOC101251311', 'LOC101263606', 'novel.572', 'zds', 'TAO3', 'LOC101254424', 'LOC100037490', 'LOC101250807', 'LOC101250289', 'LOC101254190', 'LOC101245704', 'LOC101260363', 'LOC101268510', 'Psy1', 'novel.92', 'NSGT1', 'NSY', 'LOC101247014', 'LOC101255254', 'LOC101246396', 'LOC101246264', 'LOC101246676', 'LOC101250164', 'LOC101252583', 'TomloxE', 'OPR1', 'LOC101266160', 'LOC101250586', 'LOC101247110', 'LOC101255874', 'novel.105', 'LOC543694', 'LOC101266174', 'LOC101267503', 'LOC101249983', 'LOC101267959', 'DXR', 'LOC101263406', 'LOC101262503', 'LOC101252025', 'LOC101268830', 'LOC101249394', '20ox-2', 'LOC101250012', 'TPS37', 'Sip1', 'LOC101253180', 'LOC101244691', 'TPS7', 'novel.113', 'LOC101247250', 'MTS1', 'dxs', 'TPS36', 'SSTLE1', 'TCTR1', 'LOC101262198', 'LeNCED1', 'TPS39', 'LOC101248790', 'LOC101256513', 'SlscADH1', 'TPS38', 'Z-ISO', 'LOXB', 'HMGR', 'LOC543658'})</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>LOC543694;Psy1;SlGPAT6;LOC101247250;HDS;GA2ox2;LOC101252161;NDPS1;TPS32;LOC101256685;PP2Ac2;LOC101244691;LOC101250481;LOC101244523;LOC101250807;LOC101253180;LOC101263606;LOC101252025;LOC101264840;zds;novel.92;LOC101263085;LOC101268830;ZEP;LOC101263090;TPS33;LOC101248511;LOC101252453;LOC101262503;TPS37;SlMYB21;novel.113;TPS38;LOC101252202;LOC104645573;VDE;LOC101246264;TAO3;LOC101245704;LOC101267503;3OH-1;LOC101247770;LOC101247110;LOC101246676;LOC101254591;NXD1;LOC101257572;TomloxE;SlALDH2B7a;LOC101254497;LOC101260363;LeNCED1;LOC101259139;LOC101250561;LOC101266963;TPS39;PSY2;LOC101249057;LOC101244466;LOC101262639;LOC101251311;LOC101268510;LOC101245297;LOC101256694;GGPS2;LOC101250164;PP2Ac1;LOC101249584;MTS1;LOC101250354;3OH-2;LOC101266950;LOC101247014;LOC101246303;LOC100134915;LOC101262198;NSGT1;dxs;LOC101258355;MTS2;TPS31;LOC101249394;LOC101254720;LOC101249786;LOC101261489;SSTLE1;SlADH2B7d;SlFRK3;LOC100037490;LOC101252788;CrtR-b2;LOC101265793;HMG2;LOC101255254;LOC101244092;novel.879;LOC101263151;TPS35;LOC101249983;LOC101254597;Sip1;PLDa2;LOC101250012;CRTISO;LOC543658;TAO2;novel.105;DXR;NSY;LOC101252583;20ox-2;LOC101260812;LOC101250586;AOS2;TPS14;AOS3;LOC101248500;LOC101246730;LOC101250473;TPS24;LOC101255411;LOC101246396;LOC107648852;LOC101266174;TPLD;LOC101248790;OPR1;LOXB;LOC101264132;novel.915;SppS;pds;HMGR;TPS36;novel.572;LOC109120859;MDC;HPL;SNF1;LOC101263406;SlCPTBP;LOC101254190;TPS16;LOC101250289;LOC101245370;LOC104649012;LOC101256513;LOC101260607;PLDa1;TPS7;LOC101266160;LOC101258806;Z-ISO;TPS28;LOC101252738;LOC101267959;TPS17;TTS2;PLDb2;THM27;LOC101254424;LOC101251763;LOC101263535;TomloxC;PIIGLB1;PLDb1;LOC101255340;LOC101246995;SlscADH1;LOC101258525;PHS1;TCTR1;TPS3;dxs2;opr3;LOC101255874</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>GO:0002213</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>defense response to insect</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6.486139401260894e-05</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.008867093073140413</v>
+      </c>
+      <c r="E61" t="n">
+        <v>7</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.5399025550926668</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.8006539344787598</v>
+      </c>
+      <c r="I61" t="n">
+        <v>8.505128860473633</v>
+      </c>
+      <c r="J61" t="n">
+        <v>16</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>frozenset({'WRKY81', 'sbt4b', 'sbt3', 'sbt4e', 'LOC101252733', 'LOC101249884', 'sbt4c', 'sbt4d', 'LOC101263181', 'LOC101246681', 'LOC101266611', 'LOC101055569', 'LOC101253643', 'LOC101260044', 'sbt4a', 'LOC101248896'})</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>LOC101260044;sbt3;sbt4d;sbt4b;WRKY81;LOC101248896;LOC101266611;sbt4e;LOC101263181;LOC101246681;LOC101249884;LOC101253643;sbt4a;LOC101055569;sbt4c;LOC101252733</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>GO:0010229</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>inflorescence development</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>9.839756138849443e-05</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01308820536144528</v>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.03247221404864216</v>
+      </c>
+      <c r="G62" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-3.295337915420532</v>
+      </c>
+      <c r="I62" t="n">
+        <v>10.1380672454834</v>
+      </c>
+      <c r="J62" t="n">
+        <v>11</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>frozenset({'SFT', 'TCP16', 'LOC101266437', 'PIN9', 'LOC101246760', 'MPK3', 'LOC100527965', 'TCP17', 'TCP23', 'LOC101253401', 'MKK2'})</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>SFT;PIN9;LOC101246760;TCP23;LOC100527965;MKK2;TCP17;MPK3;TCP16;LOC101266437;LOC101253401</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>GO:0042447</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>hormone catabolic process</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.0001014976997274529</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01314528761075419</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.1359099353309676</v>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-2.797042608261108</v>
+      </c>
+      <c r="I63" t="n">
+        <v>10.94956684112549</v>
+      </c>
+      <c r="J63" t="n">
+        <v>7</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>frozenset({'SlCKX1', 'LOC101268833', 'SlCKX5', 'SlCKX3', 'SlCKX7', 'LOC101268251', 'SlCKX4'})</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>LOC101268833;LOC101268251;SlCKX4;SlCKX1;SlCKX5;SlCKX7;SlCKX3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>GO:0030388</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>fructose 1,6-bisphosphate metabolic process</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.0001014976997274529</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01314528761075419</v>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.1017334548941975</v>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-2.457656145095825</v>
+      </c>
+      <c r="I64" t="n">
+        <v>12.29314994812012</v>
+      </c>
+      <c r="J64" t="n">
+        <v>7</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>frozenset({'SlFBA2', 'SlFBA6', 'SlFBA1', 'SlFBA8', 'LOC101260852', 'SlFBA7', 'SlFBA3'})</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>SlFBA1;SlFBA3;SlFBA7;SlFBA6;LOC101260852;SlFBA2;SlFBA8</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>GO:1901605</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>alpha-amino acid metabolic process</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.0001124431864203293</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01437374394721171</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.1388937701868143</v>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-3.751905679702759</v>
+      </c>
+      <c r="I65" t="n">
+        <v>13.11444473266602</v>
+      </c>
+      <c r="J65" t="n">
+        <v>63</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101247693', 'LOC101251350', 'SSADH', 'LOC101259235', 'LOC101244469', 'LOC101254848', 'LOC101259236', 'LOC101249935', 'LOC101254591', 'LEAS1', 'THM16', 'PAT', 'LOC101267663', 'OTC', 'PAL5', 'LOC101254112', 'LOC101245553', 'LOC101264873', 'adc1', 'ODC', 'LOC101254439', 'LOC101247891', 'LOC101263817', 'LOC104648641', 'LOC101257319', 'Slalpha-kGDH', 'LOC101266918', 'PAL2', 'SlADH11A4a', 'LOC101247914', 'LOC101244614', 'PIIGLB1', 'MST1', 'PAL3', 'LOC101252466', 'NAGK', 'NAOAT', 'PDH', 'LOC543920', 'LOC101263879', 'LOC101256529', 'LOC101251816', 'NAOD', 'MST2', 'LOC101258830', 'LOC101254281', 'SlADH12A1', 'LOC101261642', 'PRO2', 'LOC101251091', 'LOC101254608', 'LOC101252192', 'SlALDH6B2', 'LOC101250891', 'LOC101055519', 'LOC101259725', 'LOC101264863', 'OAT', 'LOC101246283', 'novel.966', 'LOC101244882', 'gdh1', 'GS1'})</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>NAOD;LOC101247891;LOC101263817;LOC101251816;LEAS1;LOC104648641;LOC101249935;LOC101252192;adc1;LOC101245553;LOC101251091;ODC;LOC101259725;LOC101254591;LOC101263879;LOC101251350;THM16;MST2;LOC101264863;LOC101264873;LOC101254439;LOC101267663;LOC101254608;LOC101257319;Slalpha-kGDH;PAT;SSADH;SlADH11A4a;novel.966;LOC101259236;PRO2;SlADH12A1;LOC101247914;SlALDH6B2;LOC101247693;LOC101254281;LOC101244882;LOC101266918;PAL3;LOC101055519;PAL5;LOC101256529;PAL2;LOC101259235;LOC101244469;LOC101261642;MST1;OTC;LOC101252466;OAT;LOC101244614;LOC101254848;NAGK;NAOAT;gdh1;LOC543920;PDH;LOC101250891;GS1;LOC101246283;PIIGLB1;LOC101254112;LOC101258830</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>GO:0009536</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>plastid</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.0001286660377605278</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.0162366642266266</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.03475624418023084</v>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-2.800174713134766</v>
+      </c>
+      <c r="I66" t="n">
+        <v>8.161211967468262</v>
+      </c>
+      <c r="J66" t="n">
+        <v>403</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101263085', 'LOC101245421', 'LOC101262888', 'LOC101244921', 'PSY2', 'LOC101244306', 'LOC101254882', 'LOC101256592', 'SlCOR413IM1', 'LOC101244514', 'LOC101245370', 'LOC101255271', 'LOC101258293', 'LyesC2p073', 'TPLD', 'LOC101247851', 'SlFBA3', 'PIIGLB1', 'LOC101262785', 'CAB4', 'LOC101255583', 'ZEP', 'MTS2', 'LOC101251653', 'LOC101263675', 'LOC101255358', 'MDHAR', 'LOC101257833', 'LOC101255295', 'LOC101268200', 'LOC101258151', 'LOC101251312', 'LOC101267611', 'LOC101252138', 'LOC101248511', 'LOC101254229', 'LOC101247293', 'LyesC2p087', 'LOC101245112', 'LOC101268808', 'LOC101253221', 'LOC544217', 'LOC101252202', 'TomloxC', 'novel.87', 'LOC101263281', 'novel.1062', 'LyesC2p069', 'LOC101254281', 'LOC101259028', 'nii1', 'TPS3', 'LOC101254608', 'LOC101265217', 'NDPS1', 'LOC101252151', 'LOC101258785', 'LOC101264062', 'LyesC2p070', 'SlIPT2', 'LOC101253541', 'LOC101250561', 'LOC101266486', 'CAB9', 'LOC101261489', 'zds', 'LOC100037490', 'LOC101257971', 'SlADH12A1', 'SlIPT4', 'LOC101255672', 'LOC101250891', 'TOC75-III', 'NSY', 'LOC101263132', 'LyesC2p072', 'LOC101262221', 'LOC101256427', 'LOC543930', 'LOC101249935', 'PAT', 'LOC101251285', 'LOC101267959', 'LOC101254112', 'LOC101261948', 'ELIP', 'LOC101266713', 'LOC101263732', 'LOC101265555', 'LOC101255435', 'LOC100037730', 'LOC104644379', 'LOC101248300', 'LOC101253805', 'SEND33', 'LOC101249417', 'LOC101262255', 'LyesC2p081', 'LOC101252931', 'LOC101265931', 'LOC101256513', 'novel.860', 'PPO', 'LOC101257542', 'LOC101249846', 'PsbQ', 'SlFBA2', 'LyesC2p086', 'SlALD3H1', 'LOC101243864', 'SSR2', 'novel.895', 'ribA', 'SlFRK3', 'MKS2b', 'LOC101264109', 'SK', 'LOC101243905', 'LOC101262783', 'LOC101245901', 'LOC101264480', 'LyesC2p074', 'SGR1', 'SNF1', 'pGlcT1', 'LOC101260856', 'LOC101244466', 'LOC101244717', 'LOC101249164', 'LOC101245518', 'LyesC2p076', 'LOC101262260', 'LOC101259357', 'LOC101259572', 'SlIPT1', 'LyesC2p080', 'SlHDA3', 'PDF1B', 'AgpL1', 'LOC101261433', 'LOC101249057', 'AOS2', 'LOC101260607', 'LOC101249327', 'HPL', 'LyesC2p085', 'TPS24', 'LOC101267006', 'CrtR-b2', 'LyesC2p075', 'Cel2', 'LOC101255915', 'SlArf_Xyl3', 'LOC101055609', 'LOC101055526', 'LOC101248838', 'LOC101247693', 'VDE', 'LOC101246554', 'LOC101264145', 'LOC101253342', 'LOC101248500', 'LOC101267425', 'psbS', 'LOC101257407', 'SlFBA1', 'sos1', 'LOC101255756', 'GGPS2', 'TCP4', 'TAO3', 'LOC101256426', 'EO', 'LOC101267919', 'LyesC2p071', 'MST2', 'LOC543932', 'LOC101263249', 'LOC101255525', 'LOC101055519', 'novel.92', 'LOC101250405', 'LOC101263054', 'LOC101267346', 'LOC101250586', 'LOC104649028', 'SlVTE5', 'LOC101247833', 'LyesC2p089', 'TCP5', 'LOC101265790', 'LOC101247914', 'LOC101264050', 'LOC101245616', 'SQD1', 'LOC101250378', 'LeNCED1', 'LOC101259692', 'VKOR', 'LOC101255514', 'LOC101245297', 'LOC101245729', 'LOC101259221', 'LOC101244634', 'LOC101260852', 'novel.1', 'LyesC2p079', 'LOC101268617', 'MTSHP', 'MKS2c', 'ht2', 'LOC101261339', 'LOC101250520', 'LOC101252117', 'LOC101259372', 'LOC101255298', 'LOC101268227', 'HDS', 'PDF1A', 'ca3', 'LOC101255076', 'OAT', 'LOC101258970', 'dxs2', 'PSBO', 'LOC101250287', 'LOC101252977', 'PHS1', 'LyesC2p078', 'LOC101268563', 'LOC101260274', 'VGT1', 'LyesC2p082', 'LOC101266918', 'LOC101249904', 'LyesC2p053', 'LOC101247061', 'LOC101244614', 'TMT', 'LOC101256609', 'LOC101258297', 'LOC101256529', 'Shy', 'LOC101252192', 'LOC101247770', 'SKP1', 'GR', 'LOC101266624', 'LOC101251350', 'LOC101246521', 'LOC101257061', 'LOC101250650', 'MKS2', 'LOC101249680', 'OTC', 'LOC101261284', 'LOC101245880', 'LOC101248098', 'LOC101257676', 'LOC101248896', 'PPO-2', 'SlArf_Xyl4', 'LOC101256944', 'LOC543920', 'LOC101258337', 'novel.82', 'novel.817', 'rps16', 'LOC101245121', 'LOC101244516', 'ME1', 'Psy1', 'LOC101265484', 'LOC101264609', 'LyesC2p083', 'LOC101265242', 'OEE1', 'LOC101256822', 'SlIPT3', 'novel.924', 'POR2', 'LOC101254848', 'LOC101265835', 'LOC101268560', 'LOC101266160', 'LOC101265168', 'TIL', 'LOC101251571', 'LOC101247891', 'LOC101252466', 'TPS7', 'LAPA1', 'LOC101245785', 'pGlcT4', 'LOC101254712', 'LOC101264082', 'dxs', 'vis1', 'LOC101259830', 'LOC101263269', 'LOC101258500', 'LOC101247687', 'LOC100736525', 'LOC543658', 'PETE', 'LOC101253219', 'LyesC2p062', 'LOC101254513', 'LOC101256077', 'pds', 'LOC101246731', 'LOC101247532', 'LOC101259494', 'LOC101260469', 'LOC101252603', 'LyesC2p063', 'LOC101261547', 'LOC101259632', 'SPA', 'LOC100191110', 'LOC101244176', 'LOC101246763', 'TPx1', 'novel.866', 'CRTISO', 'LOC101268373', 'LOC109120519', 'SSADH', 'THIC', 'LOC101249002', 'novel.766', 'Why3', 'LOC101245293', 'LOC101257319', 'LOC101262218', 'LOC101264255', 'MST1', 'SppS', 'Rbcs-3B', 'SlArf_Xyl1', 'LOC101266963', 'SDH', 'LOC101253320', 'novel.1105', 'SlTIP2-2', 'MSH1', 'LOC101266265', 'LOC101246995', 'LyesC2p077', 'LOC101253996', 'LOC101252124', 'HrBP1', 'LOC101264004', 'pGlcT3', 'sfr2', 'LOC101249584', 'LOC101263817', 'LOC104649438', 'LOC101264583', 'LOC101268832', 'NAGK', 'novel.1033', 'SlFBA4', 'LOC101251311', 'PSBR', 'LOC101245704', 'LOC101261642', 'LyesC2p088', 'LOC101254806', 'LOC101257857', 'HXK4', 'rbcS1', 'LOC101244709', 'SBPase', 'PHOT2', 'novel.1175', 'LOC101259223', 'LOC101248631', 'LOC101256192', 'LOC101267163', 'LOC101246143', 'LOC778326', 'LOC101246676', 'TIL_', 'DXR', 'LyesC2p084', 'SlVP2', 'LOC101243925', 'LOC101257875', 'Ve2', 'SLTAB2', 'Sip1', 'LOC101262961', 'mdh', 'SODCP.2', 'LOC101255261', 'VGT2', 'MTS1', 'CAB7', 'PSBP', 'LOC101261259', 'Z-ISO', 'LOC101259256'})</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>LOC101262260;LOC101252138;Psy1;LOC101261433;LOC101250405;LOC101258500;LOC101256609;novel.1033;LOC101265555;LOC101255298;HDS;OEE1;SODCP.2;LOC101247891;LOC101256822;LOC101265790;NDPS1;SPA;LOC101252151;LOC101263817;LOC101249002;SlArf_Xyl3;LyesC2p070;CAB9;LOC101259256;VGT2;LyesC2p077;LyesC2p086;SlFBA1;SEND33;PETE;LOC101245880;LOC101245729;LOC543932;LOC101245785;LOC101266713;PSBO;LyesC2p079;TCP4;LyesC2p089;LOC101250520;LOC101246521;LOC101268808;LOC101265217;LyesC2p081;LOC101244176;LOC101243925;LOC101254229;ELIP;LOC101249846;LyesC2p080;zds;LOC101253541;novel.92;LOC101247061;LyesC2p078;LOC101249935;LOC101263085;LyesC2p073;PHOT2;novel.895;HXK4;ZEP;MKS2b;LOC101263054;SlIPT1;LOC101264082;LOC101252192;LOC101256077;LOC101262783;LOC101268832;novel.924;psbS;novel.87;novel.1;LyesC2p087;LOC101248511;LOC101263269;LOC101258297;LOC101255076;LOC101262785;LOC101259830;LOC101268227;TCP5;LOC101255525;LOC101267611;LOC101263675;LOC101268560;LOC101252202;SLTAB2;novel.766;PDF1B;mdh;LOC100736525;pGlcT3;LOC101256592;VDE;TAO3;LOC101255358;SlIPT2;LOC101245704;SGR1;LOC101244516;novel.866;novel.82;LOC101247770;SlFBA4;sfr2;LOC101246676;novel.1105;SQD1;LOC101258970;LOC101255271;LOC101248098;LOC101261948;LOC101257542;LOC101252931;LOC101264109;LOC101264255;LOC101267006;LyesC2p071;MKS2;LOC101253805;LOC101264004;LeNCED1;LOC101265931;LOC101255514;LOC100191110;LOC101256944;LOC101251350;SlFBA3;LOC101250561;LOC101264062;LyesC2p082;LOC101245293;MST2;LOC101249680;LOC101266963;ht2;Why3;LyesC2p069;LOC101259572;LOC544217;LOC101265242;PSY2;LOC101249057;LOC101244466;LOC101254712;LOC101268617;MDHAR;LOC101249417;LOC101265168;LOC101251311;LOC101258337;LOC101251285;LOC101268563;LOC101252603;LOC101250287;LOC101245297;LOC101254608;TPx1;LOC101263132;LOC101252124;GGPS2;VKOR;LOC101257319;LOC101246143;PAT;SSADH;LOC101249584;MTS1;LOC101258785;Rbcs-3B;PsbQ;LOC101246554;LOC101255295;LOC101245518;LOC104649028;pGlcT4;LOC101251653;LyesC2p062;LOC101261339;LOC101244709;dxs;LyesC2p085;LOC101266486;SlIPT4;LOC101243905;MTS2;LyesC2p083;LOC101255756;LOC101257061;SlADH12A1;LOC101265484;LOC101256426;LOC101246763;LOC101253219;LOC101261284;LOC101261489;TIL_;SlVP2;LOC101245421;SlFRK3;LOC101055526;SDH;LOC101247914;LOC101253342;LOC100037490;LOC101253320;LOC101248896;LOC101257676;Cel2;MTSHP;SlTIP2-2;LOC101262888;CrtR-b2;LOC101262961;LOC101247532;SlArf_Xyl4;rbcS1;Ve2;LOC101247693;LOC101254281;Shy;LOC101263281;LOC101244717;ME1;sos1;LyesC2p074;LyesC2p088;PDF1A;LOC101245121;LOC101254806;LOC101259223;LOC101256427;LOC101263249;LOC101259692;LOC101266918;VGT1;Sip1;LOC101257833;LOC101255435;LOC101254513;SK;LOC101268373;CRTISO;LOC543658;LOC101245901;LOC101253996;LOC101055519;LOC101260274;LOC101244514;CAB7;LOC101244306;DXR;NSY;LOC104644379;SKP1;LOC101253221;LOC101250586;LOC101263732;LOC101249164;AOS2;LOC101259221;LOC104649438;LyesC2p076;PPO-2;LOC101256529;SSR2;LOC101247851;novel.817;LOC101248300;LOC101248500;SlIPT3;LOC101262221;LOC101260852;TPS24;LOC101248838;LOC101264145;LyesC2p072;LOC101247687;LOC101055609;LOC101267425;LOC100037730;LOC101258293;novel.1175;rps16;LOC101252977;TPLD;CAB4;LOC101251571;LOC101244634;LOC101261259;novel.1062;LOC101257875;SlFBA2;LOC101267346;LOC101261642;PSBR;LOC101256192;LOC101254882;LOC101267163;LOC101244921;SlALD3H1;ribA;MST1;OTC;LOC101264050;PSBP;LOC101264480;MKS2c;SppS;LOC101250650;pds;LOC101252466;LOC101255261;POR2;LOC101246731;LOC101259494;LOC101262218;LAPA1;LOC101261547;LOC778326;OAT;LOC101247293;LOC101244614;HPL;LOC101254848;SNF1;LOC101258151;HrBP1;LOC101245616;TMT;LOC101259632;LOC101251312;SBPase;GR;LOC101259372;LOC101257857;LOC101255583;nii1;LOC543930;LOC101245370;THIC;LOC101257407;pGlcT1;LOC101262255;SlArf_Xyl1;LOC101265835;EO;NAGK;LOC101256513;LyesC2p053;LOC101248631;LOC101266624;ca3;TOC75-III;LOC101260607;LOC543920;LOC101260856;PPO;vis1;TPS7;LOC101247833;LOC101245112;AgpL1;LOC101266160;Z-ISO;LOC101249904;LyesC2p084;LOC101250378;LOC109120519;LOC101267959;SlHDA3;LOC101259028;LOC101255672;LOC101259357;LOC101252117;LOC101264609;LOC101250891;LyesC2p075;LOC101268200;LOC101249327;LyesC2p063;TIL;LOC101267919;TomloxC;novel.860;PIIGLB1;LOC101243864;LOC101257971;LOC101260469;LOC101246995;LOC101254112;LOC101266265;MSH1;SlCOR413IM1;LOC101255915;PHS1;LOC101264583;SlVTE5;TPS3;dxs2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>GO:0009308</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>amine metabolic process</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.0001353822011016942</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01686793677777184</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.124441416070814</v>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-2.773242950439453</v>
+      </c>
+      <c r="I67" t="n">
+        <v>11.28024864196777</v>
+      </c>
+      <c r="J67" t="n">
+        <v>38</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>frozenset({'spe4', 'LOC101264170', 'SPM1', 'SlIPT3', 'LOC101244469', 'spdsyn', 'novel.766', 'LOC101254402', 'SlIPT1', 'SlCKX4', 'SlCYP735A2', 'LOC101249176', 'SlIPT2', 'LOC101253022', 'TLOG1', 'adc1', 'ODC', 'LOC101263817', 'SlCKX2', 'SlCKX1', 'PIIGLB1', 'SlCKX3', 'LOC101256529', 'SlCKX7', 'LOC101268146', 'pmt', 'LOC101262778', 'SlIPT5', 'SlIPT4', 'LOC101268254', 'SAMDC', 'SlCKX5', 'LOC101256765', 'SlCYP735A1', 'LOC101254319', 'novel.966', 'LOC101246083', 'LOC101258232'})</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>SlCYP735A2;LOC101268254;LOC101263817;SlIPT1;adc1;LOC101264170;SlIPT5;novel.766;SlIPT2;ODC;TLOG1;SlCKX4;LOC101254402;SlCKX2;spe4;novel.966;SlCKX1;SlIPT4;pmt;SlCKX5;spdsyn;LOC101256765;SPM1;SlCKX7;LOC101258232;LOC101256529;SAMDC;SlIPT3;LOC101253022;LOC101244469;LOC101254319;LOC101262778;LOC101246083;SlCKX3;LOC101268146;SlCYP735A1;PIIGLB1;LOC101249176</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>GO:0015145</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>monosaccharide transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.0001512572157103402</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01861030967796099</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.09742732579331366</v>
+      </c>
+      <c r="G68" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-2.041182279586792</v>
+      </c>
+      <c r="I68" t="n">
+        <v>7.915181636810303</v>
+      </c>
+      <c r="J68" t="n">
+        <v>11</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>frozenset({'ht2', 'LOC101251853', 'pGlcT3', 'STP12', 'ht1', 'VGT1', 'STP18', 'STP11', 'VGT2', 'pGlcT4', 'PMT5'})</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>VGT2;STP11;ht1;pGlcT3;ht2;STP12;pGlcT4;PMT5;LOC101251853;VGT1;STP18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>GO:0010817</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>regulation of hormone levels</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.0001778916188380925</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.02161712597806598</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.1405403671960284</v>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-3.078390836715698</v>
+      </c>
+      <c r="I69" t="n">
+        <v>11.02310276031494</v>
+      </c>
+      <c r="J69" t="n">
+        <v>71</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101249663', 'spe4', 'LOC104645199', 'PIN10', 'LOC101247545', 'TRN1', 'SlIPT3', 'LOC101248505', 'LOC101244469', 'LOC101259437', 'PIN4', 'novel.1112', 'novel.766', 'LOC101267152', 'LOC101254402', 'LOC101249609', 'SlIPT1', 'SlCKX4', 'SlCYP735A2', 'LOC101249176', 'SlIPT2', 'LOC101249771', 'PIN3', 'LOC101256077', 'LOC101254657', 'CYP734A8', 'SlVP2', 'LOC101267522', 'LOC101249671', 'LOC101263817', 'PIN8', 'LOC101268251', 'SlCKX2', 'LOC101247828', 'SlCKX1', 'LOC101244831', 'LOC101247843', 'LOC101255353', 'PIN9', 'LOC101258514', 'TAO3', 'PIN7', 'LOC101251445', 'LOC101253401', 'SlCKX3', 'LOC101256529', 'SlCKX7', 'LOC101258354', 'LOC104644402', 'PIN6', 'LOC101257674', 'PIN2', 'SlIPT5', 'SlIPT4', 'TAO2', 'LOC101268254', 'LOC101268833', 'LOC101262778', 'mek1', 'CYP724B2', 'LOC100527965', 'SlCKX5', 'LOC101252303', 'CYP85A1', 'novel.92', 'LOC101256765', 'MDR1', 'SlCYP735A1', 'PIN5', 'TLOG1', 'LOC101246083'})</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>SlCYP735A2;LOC101268833;mek1;LOC104645199;LOC101268254;LOC101263817;LOC101257674;PIN2;LOC101247828;PIN10;LOC101267152;LOC101249671;novel.1112;novel.92;PIN9;SlIPT1;LOC101256077;PIN8;PIN6;SlIPT5;novel.766;TAO3;SlIPT2;LOC101268251;TLOG1;LOC101244831;CYP734A8;PIN5;PIN7;LOC101247843;SlCKX4;LOC101251445;LOC101254402;CYP724B2;SlCKX2;spe4;LOC101254657;SlCKX1;SlIPT4;LOC101249771;LOC101258514;SlVP2;SlCKX5;TRN1;PIN3;LOC101247545;LOC100527965;LOC101255353;LOC101252303;LOC101256765;TAO2;SlCKX7;LOC101256529;SlIPT3;LOC101249663;LOC101244469;LOC101262778;LOC101246083;LOC101248505;LOC101259437;SlCKX3;LOC101267522;PIN4;LOC101249609;CYP85A1;MDR1;SlCYP735A1;LOC101258354;LOC101253401;LOC104644402;LOC101249176</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>GO:0043450</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>alkene biosynthetic process</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.0001877661138684855</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.02174331598597062</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.1498674405585827</v>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-1.84816837310791</v>
+      </c>
+      <c r="I70" t="n">
+        <v>12.3635835647583</v>
+      </c>
+      <c r="J70" t="n">
+        <v>15</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>GO:0043449,GO:0009693,GO:0009692,GO:1900674,GO:1900673</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>frozenset({'ODD', 'ACS4', 'LOC101245697', 'ACO4-like', 'LOC101244469', 'ACO3', 'ACO1', 'ACS6', 'aco5', 'LOC101259689', 'ACO4', 'MKK2', 'E8-6', 'MKK4', 'ACS2'})</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>E8-6;ACS6;ACS2;ACO4;ACO3;ACS4;ACO1;ACO4-like;MKK2;LOC101259689;LOC101244469;aco5;MKK4;LOC101245697;ODD</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>GO:0034754</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>cellular hormone metabolic process</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.0001981992531314305</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.0226845959136357</v>
+      </c>
+      <c r="E71" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.1570957183722891</v>
+      </c>
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-2.663940191268921</v>
+      </c>
+      <c r="I71" t="n">
+        <v>11.06133937835693</v>
+      </c>
+      <c r="J71" t="n">
+        <v>26</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>frozenset({'SlIPT3', 'LOC101244469', 'novel.766', 'LOC101249609', 'LOC101254402', 'SlIPT1', 'SlCKX4', 'SlCYP735A2', 'LOC101249176', 'SlIPT2', 'SlCKX2', 'LOC101247828', 'SlCKX1', 'SlCKX3', 'LOC101256529', 'SlCKX7', 'LOC104644402', 'LOC101262778', 'SlIPT5', 'SlIPT4', 'LOC101268254', 'SlCKX5', 'LOC101256765', 'SlCYP735A1', 'TLOG1', 'LOC101246083'})</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>SlCYP735A2;LOC101268254;LOC101247828;SlIPT1;SlIPT5;novel.766;SlIPT2;TLOG1;SlCKX4;LOC101254402;SlCKX2;SlCKX1;SlIPT4;SlCKX5;LOC101256765;SlCKX7;LOC101256529;SlIPT3;LOC101244469;LOC101262778;LOC101246083;SlCKX3;LOC101249609;SlCYP735A1;LOC104644402;LOC101249176</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GO:0015301</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="n">
+        <v>0.0002159257929783004</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.02442453600993616</v>
+      </c>
+      <c r="E72" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.2064900992544451</v>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-2.291130781173706</v>
+      </c>
+      <c r="I72" t="n">
+        <v>8.623876571655273</v>
+      </c>
+      <c r="J72" t="n">
+        <v>9</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>frozenset({'ST2', 'ST4.1', 'LOC101264062', 'LOC101256192', 'LOC101253320', 'LOC101246241', 'LOC101260863', 'LOC101250213', 'ST1'})</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>ST1;ST4.1;LOC101264062;LOC101253320;LOC101250213;LOC101256192;LOC101246241;ST2;LOC101260863</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>GO:0016829</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>lyase activity</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.0002183642353829505</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.02442453600993616</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.06590859131719694</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-2.166448593139648</v>
+      </c>
+      <c r="I73" t="n">
+        <v>14.59787845611572</v>
+      </c>
+      <c r="J73" t="n">
+        <v>87</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101249663', 'ME2', 'LOC101249193', 'LOC101244298', 'SlFBA2', 'LOC101255271', 'AOS3', 'LOC101258131', 'ribA', 'SlFBA3', 'PAL3', 'MTS2', 'ca3', 'TPS33', 'SlFBA8', 'LOC101259958', 'TPS35', 'hdc', 'LOC101263652', 'LOC101248505', 'LOC101260911', 'THIC', 'PHS1', 'TPS17', 'LOC101267934', 'AOS2', 'PAL2', 'HPL', 'LOC101244614', 'TPS24', 'TPS16', 'TPS31', 'LOC101263281', 'novel.729', 'LOC101256529', 'MDC', 'TPS32', 'LOC544276', 'TPS3', 'LOC101264132', 'ACS2', 'LOC101247693', 'LOC101251350', 'TPS14', 'LOC101259235', 'LOC101263344', 'novel.516', 'LOC101260268', 'SlFBA1', 'PGH1', 'PAL5', 'TPS28', 'novel.93', 'ACS6', 'LOC101263817', 'SlFBA6', 'LOC101263458', 'novel.572', 'LOC101264531', 'ACS4', 'ME1', 'LOC101250891', 'LOC101246283', 'SlPL', 'LOC101248029', 'LOC101245200', 'LOC101246676', 'LOC101250752', 'LOC101255874', 'LOC101261166', 'LOC101247833', 'adc1', 'ODC', 'LOC101267191', 'TPS37', 'LOC101246397', 'TPS7', 'ppc2', 'MTS1', 'SlFBA7', 'TPS36', 'SSTLE1', 'SAMDC', 'TPS39', 'LOC101258500', 'LOC101248790', 'TPS38'})</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>LOC101258500;LOC101263652;ppc2;TPS32;LOC101263817;SlFBA1;LOC101258131;LOC101260268;TPS33;adc1;PGH1;TPS37;TPS38;LOC101249193;LOC101263344;ODC;LOC101245200;LOC101246676;ACS6;LOC101255271;LOC101251350;SlFBA3;SlPL;LOC101267191;TPS39;ACS2;novel.516;MTS1;SlFBA7;LOC101260911;MTS2;TPS31;SSTLE1;ACS4;SlFBA6;LOC101261166;LOC101247693;LOC101263281;ME1;LOC101248029;LOC101259958;LOC101250752;TPS35;ME2;PAL3;AOS2;PAL5;LOC101267934;LOC101256529;SAMDC;TPS14;AOS3;PAL2;LOC101259235;TPS24;hdc;LOC101249663;SlFBA2;LOC101248790;LOC101263458;LOC544276;novel.93;ribA;LOC101264132;LOC101248505;TPS36;novel.572;MDC;SlFBA8;LOC101244614;HPL;LOC101246397;TPS16;THIC;ca3;TPS7;LOC101247833;LOC101244298;TPS28;TPS17;LOC101264531;LOC101250891;novel.729;LOC101246283;PHS1;TPS3;LOC101255874</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>GO:0008194</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UDP-glycosyltransferase activity</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.0002279574123885212</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.02467361935609792</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.100057555667046</v>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-1.817341923713684</v>
+      </c>
+      <c r="I74" t="n">
+        <v>11.23381614685059</v>
+      </c>
+      <c r="J74" t="n">
+        <v>71</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101260603', 'LOC101263151', 'GAME3', 'LOC101260997', 'LOC101247584', 'LOC101263085', 'LOC101259457', 'LOC101055573', 'LOC101255510', 'LOC101260093', 'LOC101263090', 'LOC101259221', 'GAME1', 'LOC101254402', 'LOC101255377', 'LOC101251337', 'SlGGP-LIKE', 'LOC112941789', 'LOC101247095', 'LOC101264204', 'LOC101256154', 'LOC101263892', 'GolS-1', 'SlUGT75C1', 'ert1b', 'twi1', 'LOC101249176', 'LOC104647664', 'LOC101268453', 'LOC101254109', 'sus3', 'LOC101257246', 'LOC101248661', 'LOC101252007', 'LOC100529103', 'pglcat8', 'sps', 'LOC101256157', 'LOC101246612', 'LOC101258806', 'LOC101244316', 'LOC101257330', 'LOC101258947', 'LOC101263884', 'LOC101248863', 'LOC101263008', 'LOC101249320', 'LOC101258117', 'LOC101252830', 'LOC101244237', 'LOC101244199', 'SUS4', 'LOC101251018', 'LOC101251036', 'LOC101247047', 'gtsatom', 'LOC101259617', 'novel.277', 'LOC101268254', 'LOC101256691', 'LOC101250431', 'LOC101250058', 'LOC101253864', 'LOC101256765', 'NSGT1', 'LOC101258702', 'novel.706', 'LOC101249599', 'novel.70', 'SlUGT73C4', 'LOC101245628'})</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>LOC101268254;LOC101251036;LOC101259457;LOC101259617;SlGGP-LIKE;LOC101257330;LOC101248863;LOC101247047;LOC101263085;LOC101055573;LOC101260603;LOC101263090;gtsatom;LOC101250058;LOC101251337;LOC101256691;SlUGT73C4;LOC101249320;sus3;LOC101254402;LOC101251018;LOC101252830;LOC101248661;LOC101255510;ert1b;LOC101260997;LOC101254109;SUS4;LOC101256157;LOC101250431;NSGT1;novel.277;twi1;LOC112941789;GAME1;LOC101255377;LOC101246612;LOC101253864;LOC101263151;LOC101263008;LOC101249599;LOC101256765;LOC104647664;LOC101259221;LOC101260093;LOC101244237;novel.70;LOC101247095;LOC101258702;LOC101244199;GAME3;LOC101247584;LOC101252007;LOC101264204;LOC100529103;LOC101263884;LOC101256154;LOC101263892;GolS-1;pglcat8;LOC101268453;LOC101258117;SlUGT75C1;LOC101257246;LOC101258806;LOC101245628;novel.706;LOC101258947;LOC101249176;LOC101244316;sps</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>GO:0009044</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>xylan 1,4-beta-xylosidase activity</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.000230988658657188</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.02467361935609792</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.1259723994679001</v>
+      </c>
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-1.867815971374512</v>
+      </c>
+      <c r="I75" t="n">
+        <v>9.756415367126465</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>GO:0046556</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>frozenset({'SlArf_Xyl2', 'ARF1', 'XYL1', 'LOC101256554', 'SlArf_Xyl3', 'SlArf_Xyl4', 'LOC101266643', 'SlArf_Xyl1', 'LOC101254239', 'LOC101263519'})</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>SlArf_Xyl3;XYL1;LOC101254239;ARF1;LOC101263519;LOC101256554;SlArf_Xyl4;LOC101266643;SlArf_Xyl1;SlArf_Xyl2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>GO:1902066</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>regulation of cell wall pectin metabolic process</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.000230988658657188</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.02467361935609792</v>
+      </c>
+      <c r="E76" t="n">
+        <v>7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.624997108809009</v>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-0.4156293272972107</v>
+      </c>
+      <c r="I76" t="n">
+        <v>8.24033260345459</v>
+      </c>
+      <c r="J76" t="n">
+        <v>10</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>frozenset({'sbt4b', 'sbt3', 'sbt4e', 'LOC101252733', 'sbt4c', 'sbt4d', 'LOC101253643', 'LOC101260044', 'sbt4a', 'LOC101252737'})</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>LOC101260044;sbt3;sbt4d;sbt4b;LOC101252737;sbt4e;LOC101253643;sbt4a;sbt4c;LOC101252733</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>GO:0004332</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>fructose-bisphosphate aldolase activity</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.0002331247180856554</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.02467361935609792</v>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.1034904980149902</v>
+      </c>
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-2.535168886184692</v>
+      </c>
+      <c r="I77" t="n">
+        <v>12.38844680786133</v>
+      </c>
+      <c r="J77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>frozenset({'SlFBA2', 'SlFBA6', 'SlFBA1', 'SlFBA8', 'SlFBA7', 'SlFBA3'})</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>SlFBA1;SlFBA3;SlFBA7;SlFBA6;SlFBA2;SlFBA8</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>GO:0019139</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>cytokinin dehydrogenase activity</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.0002331247180856554</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.02467361935609792</v>
+      </c>
+      <c r="E78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.148901613490645</v>
+      </c>
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-2.892389535903931</v>
+      </c>
+      <c r="I78" t="n">
+        <v>11.08386039733887</v>
+      </c>
+      <c r="J78" t="n">
+        <v>6</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>frozenset({'SlCKX1', 'SlCKX5', 'SlCKX3', 'SlCKX7', 'SlCKX2', 'SlCKX4'})</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>SlCKX4;SlCKX2;SlCKX1;SlCKX5;SlCKX7;SlCKX3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>GO:0043177</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>organic acid binding</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.0002426045668428799</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.02540379522802624</v>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.1621975462779687</v>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-2.092712640762329</v>
+      </c>
+      <c r="I79" t="n">
+        <v>12.50596714019775</v>
+      </c>
+      <c r="J79" t="n">
+        <v>31</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC544002', 'LOC101246666', 'LOC112941968', 'TSI-1', 'ACO1', 'LOC101244962', 'LOC101266885', 'E8-6', 'LOC101250715', 'OTC', 'ACO4-like', 'LOC101254439', 'NAGK', 'LOC101245697', 'LOC101250944', 'F3H', 'LOC101260836', 'ACO3', 'GID1', 'LOC101250354', 'aco5', 'LOC101258963', 'SlFBA7', 'LOC101256856', 'ODD', 'LOC101259244', 'LOC101245998', 'LOC101263741', 'LOC101259725', 'LOC101249699', 'ACO4'})</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>F3H;LOC101256856;E8-6;LOC101263741;LOC101259725;LOC101266885;LOC544002;LOC101250944;LOC101254439;LOC112941968;ACO4;LOC101250354;SlFBA7;LOC101258963;TSI-1;ACO3;ACO1;ACO4-like;LOC101259244;LOC101249699;LOC101245998;LOC101250715;LOC101244962;OTC;GID1;aco5;NAGK;LOC101245697;LOC101260836;LOC101246666;ODD</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>GO:0031406</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>carboxylic acid binding</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.00025383997630963</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.02630049354542829</v>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.1755160442589865</v>
+      </c>
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-2.200138568878174</v>
+      </c>
+      <c r="I80" t="n">
+        <v>12.688889503479</v>
+      </c>
+      <c r="J80" t="n">
+        <v>32</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC544002', 'LOC101246666', 'XSP10', 'LOC112941968', 'TSI-1', 'ACO1', 'LOC101244962', 'LOC101250715', 'E8-6', 'LOC104648550', 'ACO4-like', 'LOC101254439', 'NAGK', 'LOC101252520', 'LOC101245697', 'LOC101250944', 'F3H', 'LOC101260836', 'ACO3', 'LOC101250354', 'aco5', 'LOC101258963', 'SlFBA7', 'LOC101256856', 'ODD', 'LOC101253176', 'LOC101259244', 'LOC101245998', 'LOC101263741', 'LOC101259725', 'LOC101249699', 'ACO4'})</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>F3H;XSP10;LOC101256856;LOC101253176;E8-6;LOC101263741;LOC101259725;LOC544002;LOC101250944;LOC101254439;LOC112941968;ACO4;LOC101250354;SlFBA7;LOC101258963;TSI-1;ACO3;ACO1;ACO4-like;LOC104648550;LOC101252520;LOC101259244;LOC101249699;LOC101245998;LOC101250715;LOC101244962;aco5;NAGK;LOC101245697;LOC101260836;LOC101246666;ODD</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>GO:0008271</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>secondary active sulfate transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.0003082182829905213</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.03160200582787188</v>
+      </c>
+      <c r="E81" t="n">
+        <v>8</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.2060155994582224</v>
+      </c>
+      <c r="G81" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-2.207755565643311</v>
+      </c>
+      <c r="I81" t="n">
+        <v>8.57338809967041</v>
+      </c>
+      <c r="J81" t="n">
+        <v>8</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>frozenset({'ST2', 'ST4.1', 'LOC101264062', 'LOC101256192', 'LOC101253320', 'LOC101246241', 'LOC101250213', 'ST1'})</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>ST1;ST4.1;LOC101264062;LOC101253320;LOC101250213;LOC101256192;LOC101246241;ST2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>GO:0006536</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>glutamate metabolic process</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.0003489496419812139</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.03460735191666931</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.06973860957441727</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-4.003378391265869</v>
+      </c>
+      <c r="I82" t="n">
+        <v>12.52302169799805</v>
+      </c>
+      <c r="J82" t="n">
+        <v>9</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101254281', 'SlADH12A1', 'LOC101261642', 'SSADH', 'LOC101259235', 'PDH', 'LOC101264873', 'OAT', 'gdh1'})</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>LOC101264873;SSADH;SlADH12A1;LOC101254281;LOC101259235;LOC101261642;OAT;gdh1;PDH</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>GO:1901615</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>organic hydroxy compound metabolic process</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0.0003813549717432494</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.03716511868186935</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.01601558499748429</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-2.670889377593994</v>
+      </c>
+      <c r="I83" t="n">
+        <v>13.36603832244873</v>
+      </c>
+      <c r="J83" t="n">
+        <v>84</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>frozenset({'novel.168', 'LOC101249663', 'LOC101254591', 'LOC112940921', 'LOC101256592', 'LOC101254720', 'LOC101255271', 'AOS3', 'LOC101267522', 'LOC101263783', 'LOC101260469', 'ZEP', 'LOC104649012', 'LOC101260468', 'LOC104645573', 'MIOX', 'GCH1', 'TAO2', 'LOC101264777', 'CYP724B2', 'LOC101250058', 'SlDMR6-1', 'LOC101264863', 'LOC101254137', 'LOC101263151', 'dxs2', 'LOC101264840', 'LOC101248505', 'MKS1b', 'THIC', 'LOC101259139', 'LOC101259572', 'LOC101267934', 'MKS1d', 'AOS2', 'MKS1e', 'HPL', 'LOC101244831', 'TMT', 'MYB12', 'SlCPTBP', 'novel.729', 'HMG2', 'MDC', 'SDH', 'LOC101261928', 'NDPS1', 'LOC101261578', 'LOC101248500', 'LOC101259437', 'novel.1112', 'LOC101251763', 'LOC101249584', 'novel.93', 'SD1', 'LOC101246612', 'LOC101255353', 'TAO3', 'LOC101268146', 'CYP85A1', 'novel.92', 'MKS1a', 'LOC101260990', 'LOC101255254', 'SIZ1', 'LOC101266160', 'SlVTE5', 'LOC101247833', 'LOC101263406', 'LOC101252025', 'CYP734A8', 'LOC101249394', 'LOC101247828', 'LOC101250012', 'LOC101259366', 'LOC101247250', 'dxs', 'LOC101247047', 'LeNCED1', 'LOC101258273', 'LOC101258500', 'LOC101266485', 'novel.706', 'HMGR'})</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>LOC101247250;LOC101258500;SD1;NDPS1;MKS1e;MKS1d;LOC101247828;LOC101247047;novel.1112;LOC101252025;LOC101258273;LOC101264840;novel.92;ZEP;LOC101250058;LOC104645573;LOC101256592;TAO3;LOC101261578;MIOX;SIZ1;LOC101254591;LOC101259366;LOC101255271;MYB12;LOC112940921;LOC101244831;LeNCED1;CYP734A8;LOC101259139;LOC101264863;LOC101259572;LOC101260468;CYP724B2;LOC101263783;LOC101261928;LOC101249584;LOC101266485;dxs;LOC101249394;LOC101254720;SDH;MKS1a;HMG2;LOC101255254;LOC101260990;LOC101246612;LOC101263151;LOC101254137;LOC101255353;LOC101250012;TAO2;LOC101264777;AOS2;LOC101267934;AOS3;LOC101248500;LOC101249663;SlDMR6-1;GCH1;novel.93;LOC101248505;HMGR;LOC101259437;MDC;HPL;MKS1b;LOC101263406;TMT;novel.168;SlCPTBP;LOC101268146;THIC;LOC101267522;LOC104649012;CYP85A1;LOC101247833;LOC101266160;LOC101251763;novel.706;novel.729;LOC101260469;SlVTE5;dxs2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>GO:0016903</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>oxidoreductase activity, acting on the aldehyde or oxo group of donors</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0.0003862508305921623</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.03727320515214366</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.07539563309063252</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-3.774429798126221</v>
+      </c>
+      <c r="I84" t="n">
+        <v>12.25089931488037</v>
+      </c>
+      <c r="J84" t="n">
+        <v>24</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH2B7d', 'SSADH', 'LOC101252977', 'SlADH10A9', 'LOC101250164', 'LOC109120859', 'LOC101267118', 'LOC101264004', 'LOC101253541', 'SlALD3H1', 'SlALDH11A3a', 'SlALDH2B7a', 'LOC101266713', 'LOC101255461', 'LOC101260469', 'TAO3', 'LOC778303', 'SlADH12A1', 'TAO2', 'LOC101244007', 'PRO2', 'SlALDH6B2', 'novel.92', 'SlADH3F1a'})</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>LOC778303;LOC101266713;LOC101253541;novel.92;LOC101267118;TAO3;SlALDH2B7a;LOC101264004;LOC101244007;LOC101250164;SSADH;PRO2;SlADH12A1;SlADH2B7d;SlALDH6B2;TAO2;SlADH10A9;LOC101252977;SlALD3H1;LOC109120859;LOC101255461;SlALDH11A3a;SlADH3F1a;LOC101260469</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>GO:0016705</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0.0004047876801671812</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.03868276830956859</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.006443889791397029</v>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-2.036205768585205</v>
+      </c>
+      <c r="I85" t="n">
+        <v>13.32213973999023</v>
+      </c>
+      <c r="J85" t="n">
+        <v>93</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>frozenset({'novel.394', 'LOC101245261', 'SlCYP735A2', 'LOC101254720', 'LOC101252232', 'LOC101245370', 'LOC100134915', 'AOS3', 'LOC101268276', 'LOC101256104', 'LOC101263783', 'LOC101257572', 'ZEP', 'LOC104649012', '3OH-2', 'LOC101260468', 'LOC101255340', 'LOC101251883', 'LOC101254497', 'LOC112940024', 'LOC101264777', 'CYP724B2', 'SlDMR6-1', 'SlCYP735A1', '3OH-1', 'LOC101250559', 'LOC101258968', 'LOC101267934', 'LOC101247777', 'ACO4-like', 'AOS2', 'LOC101245978', 'LOC101250481', 'LOC104648171', 'HPL', 'LOC101264644', 'LOC101245697', 'LOC101252202', 'LOC101261750', 'LOC101268013', 'ACO3', 'novel.729', 'aco5', 'novel.1062', 'LOC101266963', 'LOC101249786', 'ODD', 'LOC101244196', 'LOC101261488', 'novel.915', 'LOC101246390', 'LOC544002', 'ACO1', 'LOC101244962', 'GA2ox2', 'LOC101250561', 'novel.93', 'SD1', 'novel.1159', 'LOC101256685', 'LOC101253283', 'LOC101256720', 'zds', 'LOC101257532', 'LOC101260363', 'LOC101267987', 'LOC101262964', 'LOC101249256', 'CYP85A1', 'LOC101249699', 'NSY', 'LOC101263405', 'LOC101246558', 'LOC104649220', 'CYP77A19', 'E8-6', 'LOC101250586', 'LOC101264047', 'LOC101264988', 'LOC101264773', 'LOC101263406', 'CYP734A8', '20ox-2', 'LOC101250012', 'F3H', 'LOC101258933', 'LOC101246950', 'LOC101257397', 'LOC101254669', 'LOC101255011', 'LOC101247804', 'LOC101252777', 'ACO4'})</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>SlCYP735A2;LOC101246950;LOC101244196;GA2ox2;SD1;LOC101256685;LOC101250481;F3H;LOC101252777;LOC101257532;zds;LOC101255011;LOC101252232;ZEP;E8-6;LOC101256104;LOC104649220;LOC101252202;LOC101267987;3OH-1;LOC101245261;LOC101254669;LOC101257572;LOC101254497;novel.394;LOC101260363;CYP734A8;LOC112940024;LOC101258968;LOC544002;LOC101250561;LOC101266963;LOC101264047;LOC101245978;LOC101253283;LOC101262964;LOC101260468;CYP724B2;LOC101246390;LOC101263783;LOC101250559;ACO4;3OH-2;LOC101249256;LOC100134915;LOC101254720;LOC101249786;LOC101261750;ACO3;ACO1;LOC101268276;ACO4-like;LOC101247777;LOC101268013;LOC101250012;NSY;20ox-2;LOC101264777;LOC101250586;AOS2;LOC101264644;LOC101258933;LOC101267934;AOS3;novel.1159;LOC101247804;LOC101249699;LOC101256720;LOC101246558;CYP77A19;LOC101263405;novel.1062;SlDMR6-1;LOC101244962;LOC101264988;LOC101264773;novel.93;novel.915;HPL;aco5;LOC101263406;LOC101257397;LOC101245370;LOC104648171;LOC104649012;LOC101245697;CYP85A1;LOC101251883;LOC101261488;SlCYP735A1;novel.729;LOC101255340;ODD</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>GO:0009065</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>glutamine family amino acid catabolic process</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0.000419331213981224</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.03968728018478065</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.06228695395025166</v>
+      </c>
+      <c r="G86" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-4.079685211181641</v>
+      </c>
+      <c r="I86" t="n">
+        <v>12.34844779968262</v>
+      </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH12A1', 'SSADH', 'LOC101259235', 'PDH', 'adc1', 'OAT', 'gdh1'})</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>adc1;SSADH;SlADH12A1;LOC101259235;OAT;gdh1;PDH</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>GO:0006091</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>generation of precursor metabolites and energy</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0.000429992838732379</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.04030875725374101</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.1756515946929121</v>
+      </c>
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-3.196823835372925</v>
+      </c>
+      <c r="I87" t="n">
+        <v>6.829547882080078</v>
+      </c>
+      <c r="J87" t="n">
+        <v>71</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101263132', 'LOC104646631', 'LyesC2p072', 'LOC101259223', 'LOC101256649', 'PSBO', 'LOC101250650', 'LOC101258822', 'OEE1', 'LOC101245729', 'LOC101252977', 'LOC101262260', 'LyesC2p062', 'LOC101249002', 'LOC101253996', 'LOC101254513', 'LOC101250586', 'LOC101261166', 'SlFBA2', 'LOC101254882', 'SlFBA1', 'PGH1', 'LOC101260852', 'LyesC2p089', 'AgpL1', 'CAB9', 'LOC101257676', 'LyesC2p073', 'Slalpha-kGDH', 'LOC104649438', 'LOC101264255', 'SlFBA3', 'LyesC2p053', 'SLTAB2', 'SlFBA6', 'LOC101262961', 'LOC101245480', 'LOC101264109', 'HXK3', 'CAB4', 'LOC101252117', 'ppc2', 'LOC101256426', 'LyesC2p075', 'PSBR', 'LOC101253805', 'LOC101267103', 'LOC101259372', 'SlFBA7', 'LOC101262255', 'SPA', 'LOC101264480', 'mMDH1', 'LyesC2p074', 'CAB7', 'LOC544276', 'SlFBA8', 'LOC101254806', 'TAL', 'LOC101257857', 'LOC101255672', 'HXK4', 'LOC101259692', 'mMDH2', 'LOC101245159', 'LOC101258079', 'VKOR', 'LOC101258151', 'LOC101251312', 'LOC101252151', 'SCOA'})</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>LOC101262260;OEE1;ppc2;SPA;LOC101252151;LOC101249002;CAB9;SlFBA1;LOC104646631;LOC101245729;PSBO;LyesC2p089;LyesC2p073;HXK4;PGH1;HXK3;SLTAB2;LOC101264109;LOC101264255;LOC101253805;SlFBA3;LOC101258079;LOC101263132;VKOR;Slalpha-kGDH;SlFBA7;LyesC2p062;LOC101245159;LOC101256426;SlFBA6;LOC101261166;LOC101257676;LOC101262961;LyesC2p074;LOC101254806;LOC101259223;LOC101259692;mMDH1;LOC101254513;LOC101253996;CAB7;LOC101250586;LOC104649438;LOC101260852;LyesC2p072;LOC101252977;CAB4;LOC101256649;SlFBA2;PSBR;LOC101254882;LOC544276;mMDH2;LOC101264480;LOC101267103;LOC101250650;SlFBA8;SCOA;LOC101258151;LOC101251312;LOC101259372;LOC101257857;LOC101262255;TAL;LyesC2p053;LOC101258822;AgpL1;LOC101255672;LOC101252117;LOC101245480;LyesC2p075</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>GO:0016620</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>oxidoreductase activity, acting on the aldehyde or oxo group of donors, NAD or NADP as acceptor</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0.0004437640093461664</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.04120725607541808</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.05977447622291739</v>
+      </c>
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-3.918130397796631</v>
+      </c>
+      <c r="I88" t="n">
+        <v>12.41931343078613</v>
+      </c>
+      <c r="J88" t="n">
+        <v>17</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>frozenset({'SlADH2B7d', 'SlADH12A1', 'LOC101264004', 'LOC101253541', 'PRO2', 'LOC101260469', 'SlALD3H1', 'SlALDH6B2', 'SSADH', 'SlADH10A9', 'LOC101250164', 'SlALDH11A3a', 'LOC101266713', 'LOC109120859', 'SlALDH2B7a', 'SlADH3F1a', 'LOC101255461'})</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>LOC101266713;LOC101253541;SlALDH2B7a;LOC101264004;LOC101250164;SSADH;PRO2;SlADH12A1;SlADH2B7d;SlALDH6B2;SlADH10A9;SlALD3H1;LOC109120859;LOC101255461;SlALDH11A3a;SlADH3F1a;LOC101260469</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>GO:0071949</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>FAD binding</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0.0004741562147649562</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.04361794039188284</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.07215059182852394</v>
+      </c>
+      <c r="G89" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-3.155155897140503</v>
+      </c>
+      <c r="I89" t="n">
+        <v>11.33630180358887</v>
+      </c>
+      <c r="J89" t="n">
+        <v>21</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101245200', 'LOC101266160', 'SlCKX4', 'LOC101247497', 'SlCKX2', 'SlCKX1', 'LOC101244831', 'novel.972', 'LOC101249763', 'ZEP', 'SlSSR1', 'TAO3', 'PDH', 'SlCKX3', 'SlCKX7', 'NR', 'LOC101260928', 'TAO2', 'novel.973', 'SlCKX5', 'novel.92'})</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>SlSSR1;LOC101247497;novel.92;ZEP;LOC101249763;TAO3;LOC101245200;LOC101244831;novel.972;SlCKX4;NR;SlCKX2;SlCKX1;SlCKX5;TAO2;SlCKX7;LOC101260928;SlCKX3;novel.973;LOC101266160;PDH</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>GO:0004565</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>beta-galactosidase activity</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0.0005203908552555368</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.0448517035334829</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.02606967113641438</v>
+      </c>
+      <c r="G90" t="b">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-1.445988178253174</v>
+      </c>
+      <c r="I90" t="n">
+        <v>10.19391250610352</v>
+      </c>
+      <c r="J90" t="n">
+        <v>10</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>frozenset({'TBG7', 'LOC104645427', 'LOC112941971', 'sfr2', 'TBG5', 'TBG1', 'tEG3', 'TBG3', 'TBG2', 'TBG6'})</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>tEG3;LOC112941971;TBG6;sfr2;TBG3;TBG5;TBG2;TBG7;LOC104645427;TBG1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GO:0031222</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>arabinan catabolic process</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0.0005206775839532471</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.0448517035334829</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.0989404102054617</v>
+      </c>
+      <c r="G91" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-1.69416868686676</v>
+      </c>
+      <c r="I91" t="n">
+        <v>9.65678596496582</v>
+      </c>
+      <c r="J91" t="n">
+        <v>6</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>GO:0031221</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>frozenset({'SlArf_Xyl2', 'SlArf_Xyl3', 'SlArf_Xyl4', 'SlArf_Xyl1', 'LOC101254239', 'LOC101263519'})</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>SlArf_Xyl3;LOC101254239;LOC101263519;SlArf_Xyl4;SlArf_Xyl1;SlArf_Xyl2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>GO:0098719</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>sodium ion import across plasma membrane</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.0005240217318247012</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.0448517035334829</v>
+      </c>
+      <c r="E92" t="n">
+        <v>4</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.0009419698962181977</v>
+      </c>
+      <c r="G92" t="b">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-3.127319574356079</v>
+      </c>
+      <c r="I92" t="n">
+        <v>7.919384479522705</v>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>GO:0015385,GO:0035725</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>frozenset({'nhx3', 'NHX1', 'sos1', 'NHX2', 'nhx4'})</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>nhx3;nhx4;NHX2;NHX1;sos1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>GO:0042549</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>photosystem II stabilization</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0.0005240217318247012</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.0448517035334829</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.0621340249451488</v>
+      </c>
+      <c r="G93" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-3.024905443191528</v>
+      </c>
+      <c r="I93" t="n">
+        <v>6.320738315582275</v>
+      </c>
+      <c r="J93" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>frozenset({'LyesC2p072', 'PSBO', 'LOC101259692', 'OEE1', 'LOC101257676'})</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>OEE1;PSBO;LOC101257676;LOC101259692;LyesC2p072</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>GO:0046394</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>carboxylic acid biosynthetic process</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.0005421750247677385</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.04600542042059354</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.2577419206279003</v>
+      </c>
+      <c r="G94" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-3.64018702507019</v>
+      </c>
+      <c r="I94" t="n">
+        <v>13.43782997131348</v>
+      </c>
+      <c r="J94" t="n">
+        <v>105</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101245297', 'LOC101254591', 'SlGGP-LIKE', 'LEAS1', 'LOC101256592', 'LOC101245370', 'LOC100134915', 'AOS3', 'LOC104648641', 'SlFRK3', 'PIIGLB1', 'PAL3', 'ZEP', 'SK', 'LOC104644402', 'LOC104645573', 'MIOX', 'TAO2', 'PRO2', 'LOC101258391', 'SNF1', 'OAT', 'MKS1b', 'LOC101248511', 'LOC101259236', 'THM16', 'LOC101263535', 'MKS1d', 'LOC101249057', 'AOS2', 'LOC101266918', 'PAL2', 'LOC101257319', 'LOC101250481', 'MKS1e', 'HPL', 'LOC101255411', 'LOC101244614', 'LOC101256694', 'LOC101252202', 'TomloxC', 'LOC101256529', 'NAOD', 'LOC101254281', 'opr3', 'LOC101254608', 'LOC101252192', 'LOC101247770', 'LOC101267184', 'LOC101259725', 'GS1', 'LOC101247693', 'LOC101251350', 'GABA-TP2', 'LOC101250561', 'LOC101267663', 'OTC', 'PAL5', 'LOC101254439', 'LOC101252161', 'LOC101263817', 'LOC101244092', 'novel.879', 'LOC107648852', 'NAGK', 'LOC101251311', 'LOC101263606', 'TAO3', 'LOC543920', 'LOC101251816', 'LOC101250807', 'LOC101268510', 'LOC101055519', 'novel.92', 'MKS1a', 'LOC101246283', 'GME1', 'LOC101246396', 'LOC101244469', 'LOC101254848', 'LOC101252583', 'TomloxE', 'OPR1', 'LOC101250586', 'PAT', 'LOC101254332', 'novel.105', 'LOC101266174', 'LOC101267959', 'LOC101267503', 'LOC101247833', 'LOC101254112', 'LOC101247891', 'LOC101247914', 'Sip1', 'LOC101252466', 'NAOAT', 'LOC101244691', 'LOC101259366', 'novel.113', 'LeNCED1', 'LOC101258500', 'LOC101248790', 'LOC101256513', 'LOXB'})</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>LOC101258500;NAOD;LOC101247891;LOC101252161;LOC101263817;MKS1e;LOC101244691;LOC101251816;SlGGP-LIKE;MKS1d;LOC101250481;LOC101250807;LOC101263606;LEAS1;LOC104648641;novel.92;ZEP;LOC101252192;GABA-TP2;LOC101248511;novel.113;LOC101252202;LOC104645573;LOC101256592;TAO3;LOC101267503;MIOX;LOC101247770;LOC101259725;LOC101254591;LOC101259366;TomloxE;GME1;LeNCED1;LOC101251350;LOC101250561;THM16;LOC101249057;LOC101254439;LOC101267663;LOC101251311;LOC101268510;LOC101245297;LOC101254608;LOC101256694;LOC101257319;PAT;LOC101259236;LOC100134915;PRO2;SlFRK3;LOC101247914;MKS1a;LOC101247693;LOC101254281;LOC101244092;novel.879;LOC101266918;LOC101254332;Sip1;PAL3;SK;LOC101055519;TAO2;novel.105;LOC101252583;LOC101250586;AOS2;PAL5;LOC101256529;AOS3;PAL2;LOC101255411;LOC101246396;LOC107648852;LOC101266174;LOC101244469;LOC101248790;OPR1;LOXB;OTC;LOC101252466;LOC101267184;OAT;LOC101244614;HPL;LOC101254848;MKS1b;SNF1;LOC101245370;LOC101258391;NAGK;LOC101256513;NAOAT;LOC543920;LOC101247833;LOC101267959;GS1;LOC101263535;LOC101246283;TomloxC;PIIGLB1;LOC101254112;LOC104644402;opr3</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>GO:0009522</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>photosystem I</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.0005476830303258937</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.04607559032049377</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.1128450055546188</v>
+      </c>
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-2.63505220413208</v>
+      </c>
+      <c r="I95" t="n">
+        <v>6.55372953414917</v>
+      </c>
+      <c r="J95" t="n">
+        <v>15</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>frozenset({'LyesC2p069', 'LOC101265555', 'CAB7', 'LOC101245121', 'LOC101254806', 'CAB4', 'LOC101245729', 'LOC101264609', 'LOC101262260', 'CAB9', 'LOC101249002', 'LOC101245421', 'LOC101252151', 'LOC101263732', 'LyesC2p070'})</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>LOC101262260;LOC101265555;LOC101252151;LOC101249002;LyesC2p070;CAB9;LOC101245729;LyesC2p069;LOC101245421;LOC101245121;LOC101254806;CAB7;LOC101263732;CAB4;LOC101264609</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>GO:0009686</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>gibberellin biosynthetic process</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0.000555186987740927</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.04631106373164359</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.1748603617117705</v>
+      </c>
+      <c r="G96" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-1.932996511459351</v>
+      </c>
+      <c r="I96" t="n">
+        <v>14.29818534851074</v>
+      </c>
+      <c r="J96" t="n">
+        <v>17</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>frozenset({'LOC101247014', 'LOC101249786', 'LOC101256685', 'LOC101260363', '20ox-2', 'LOC543694', 'TPS24', 'novel.915', 'GA2ox2', 'LOC101262198', 'TCTR1', 'LOC101250473', '3OH-2', 'PHS1', 'LOC101255340', 'LOC101254497', '3OH-1'})</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>LOC543694;GA2ox2;LOC101256685;3OH-1;LOC101254497;LOC101260363;3OH-2;LOC101247014;LOC101262198;LOC101249786;20ox-2;LOC101250473;TPS24;novel.915;LOC101255340;PHS1;TCTR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>GO:0005975</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>carbohydrate metabolic process</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0.0005656268817766557</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.0467854235069548</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.0964081760923821</v>
+      </c>
+      <c r="G97" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-1.360816836357117</v>
+      </c>
+      <c r="I97" t="n">
+        <v>10.114914894104</v>
+      </c>
+      <c r="J97" t="n">
+        <v>202</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>frozenset({'XTH16', 'XYL1', 'SUT2', 'LOC101256649', 'tXET-B2', 'XTH5', 'LOC101055573', 'TAPG5', 'LOC101259221', 'LOC101255377', 'LOC101260044', 'SlGGP-LIKE', 'PGcat', 'LOC101256154', 'GolS-1', 'LOC101244298', 'sbt4b', 'SlFBA2', 'PME2.1', 'sbt4e', 'LOC101260852', 'sus3', 'LOC101249633', 'PE1', 'sbt4c', 'LOC101248661', 'LOC100529103', 'LOC101247646', 'SIP', 'SlFBA3', 'SlFRK3', 'novel.1002', 'LOC101266973', 'LIN8', 'LOC543511', 'LOC101264109', 'HXK3', 'LOC101266643', 'LOC101257783', 'LOC101247340', 'SUS4', 'MIOX', 'PMEU1', 'LOC101264480', 'LOC101250431', 'SlFBA8', 'LOC101244370', 'CHI9', 'cellulase', 'sbt4d', 'SNF1', 'LOC101254249', 'LOC101258461', 'lin5', 'LOC101258151', 'LOC101264724', 'TBG3', 'LOC101256574', 'LOC101253643', 'LOC101263151', 'SlArf_Xyl2', 'LOC101261426', 'LOC101267611', 'LOC101264840', 'LOC101252138', 'LOC101260911', 'LOC101255510', 'LOC101252977', 'LOC101251335', 'LOC101259139', 'CHI3', 'COBRA-like', 'XTH9', 'sbt4a', 'TAPG1', 'LOC101265793', 'LOC101252837', 'sbt3', 'LOC101258787', 'AgpL1', 'Wiv-1', 'LOC101252007', 'PS-2', 'sps', 'LOC101264255', 'LOC101247359', 'LOC100736472', 'LOC101256106', 'Rbcs-3B', 'LOC101263008', 'SUT4', 'XTH6', 'GID1', 'SlArf_Xyl1', 'LOC101254239', 'TPG6', 'LOC101267103', 'SDH', 'Cel2', 'XTH7', 'PG2', 'LOC104645427', 'SlArf_Xyl3', 'LOC544276', 'LOC101261928', 'LOC101263475', 'LOC101267184', 'tEG3', 'LOC101267699', 'LOC101252737', 'LOC101260603', 'LOC101248047', 'LOC104646631', 'LOC101260997', 'LOC101263563', 'LOC101251035', 'LOC101249056', 'novel.516', 'LOC543987', 'LOC101263369', 'LOC101251763', 'LOC101254849', 'LOC101264004', 'SlFBA1', 'LOC101253541', 'PGH1', 'LOC101268453', 'TAPG2', 'sfr2', 'LOC101245594', 'pglcat8', 'TAPG4', 'LOC101246713', 'SlFBA6', 'LOC101245480', 'bmy3', 'SlArf_Xyl4', 'LOC101263458', 'LOC101251018', 'LOC101266770', 'LOC101256554', 'TAL', 'LOC101257857', 'HXK4', 'CHI17', 'LOC101258079', 'rbcS1', 'LOC101253853', 'LOC101248575', 'SBPase', 'LOC101268410', 'TBG6', 'LOC112941971', 'LOC101255254', 'GME1', 'CHI14', 'SlPL', 'TBG7', 'LOC101247584', 'novel.622', 'LOC101249166', 'LOC101247095', 'LOC101265509', 'LOC101265927', 'LOC101250752', 'LOC101264974', 'LOC101252733', 'LOC101250187', 'SlVP2', 'LOC101252025', 'XET2', 'LOC101257875', 'tXET-B1', 'novel.670', 'LOC101245007', 'LOC101266713', 'LOC101261871', 'LOC101267191', 'LOC101252840', 'LOC100191116', 'ARF1', 'AI', 'Sip1', 'XTH1', 'AGAL', 'LOC101261650', 'LOC101247250', 'LOC101253805', 'TBG1', 'SlFBA7', 'LOC101260647', 'TBG2', 'XET4', 'LOC101263519', 'XTH3', 'LOC101251735', 'LOC101265800', 'LOC101266485', 'XOPG1', 'TBG5', 'TPS1', 'LOC101247546'})</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>AI;LOC101252138;LOC101247250;LOC543511;tEG3;LOC101267699;LOC101260044;LOC101266973;SlArf_Xyl3;SlFBA1;LOC104646631;SlGGP-LIKE;LOC101247646;LOC101266713;LOC101265927;LOC101252025;LOC101264840;CHI9;LOC101258461;XTH7;LOC101253541;LOC112941971;XTH5;tXET-B2;LOC101055573;LOC101260603;XYL1;LOC101257783;HXK4;sbt3;LOC101265800;PGH1;LOC101261650;LOC543987;HXK3;LOC101267611;TBG6;LOC100736472;LOC101261426;TAPG2;MIOX;sbt4d;PGcat;LOC101246713;sfr2;LOC100191116;LOC101254239;LOC101247340;TBG3;LOC101264109;LOC101264255;GME1;LOC101256106;LOC101253805;LOC101264004;LOC101247546;LOC101259139;TPG6;CHI17;tXET-B1;sus3;LOC101248575;SlFBA3;LOC101250187;lin5;SlPL;CHI14;sbt4b;LOC101245007;LOC101267191;ARF1;LOC101251018;LOC101258079;bmy3;LOC101251035;novel.516;LOC101248661;LOC101263519;LOC101254249;LOC101261928;LOC101255510;TBG5;LOC101260997;Rbcs-3B;Wiv-1;SUS4;LOC101251735;LOC101263475;SlFBA7;TBG2;LOC101260911;LOC101266485;cellulase;LOC101250431;XTH6;AGAL;XTH3;SlVP2;LOC101268410;SlFRK3;CHI3;LOC101263563;TBG7;SDH;SlFBA6;Cel2;LOC101256554;SIP;LOC101265793;SlArf_Xyl4;LOC101245594;rbcS1;novel.1002;LOC101255254;novel.622;LOC101255377;TAPG1;XET2;LOC101263151;LOC101250752;LOC101263008;SUT2;LOC101266770;PG2;Sip1;LOC101261871;LOC101252737;LOC101258787;LOC101259221;LOC101264974;LOC101256574;LOC101260852;PMEU1;PS-2;LOC101247095;XTH9;sbt4e;LOC101252977;LOC101263369;LOC101256649;LOC101252840;LOC101257875;SlFBA2;LOC101263458;LOC544276;LOC101251335;LOC101247584;XTH16;LOC101252007;LOC101264480;LOC101267103;LOC104645427;TPS1;XOPG1;LOC100529103;COBRA-like;GID1;TAPG5;LOC101267184;LOC101256154;SUT4;LOC101266643;GolS-1;LOC101260647;SlFBA8;XET4;SNF1;LOC101258151;LOC101253643;SBPase;LOC101257857;pglcat8;LOC101252837;LOC101268453;sbt4a;SlArf_Xyl1;LOC101249633;LOC101254849;TAL;PE1;LOC101249166;LOC101247359;LOC101253853;XTH1;LOC101244298;AgpL1;SlArf_Xyl2;LOC101248047;PME2.1;LOC101264724;LIN8;LOC101251763;LOC101244370;sbt4c;novel.670;LOC101245480;LOC101249056;TBG1;TAPG4;LOC101265509;sps;LOC101252733</t>
         </is>
       </c>
     </row>
@@ -1171,7 +5065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1201,13 +5095,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3428470804024799</v>
+        <v>0.2905888254136732</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01576085758768142</v>
+        <v>0.01136047591633986</v>
       </c>
     </row>
     <row r="3">
@@ -1215,13 +5109,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1928494363313539</v>
+        <v>0.2109254111433364</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01171811996673682</v>
+        <v>0.01669861655132145</v>
       </c>
     </row>
     <row r="4">
@@ -1229,13 +5123,97 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1287391496450954</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.01673136149523291</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.00202020202020202</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.01334946618210171</v>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.341802894639797</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.009996744586288846</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1107692755821404</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00840353606839863</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1437946124327869</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01644660297839671</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1146384560150103</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01254768638808992</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5578026014793229</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.009113765792127079</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.09639742131209708</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01120540620526394</v>
       </c>
     </row>
   </sheetData>
@@ -1272,7 +5250,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'p_cutoff': 0.05, 'min_genes': 3, 'logp_median_ratio': True, 'keep_top_n': 15, 'final_count': 15}</t>
+          <t>{'p_cutoff': 0.05, 'min_genes': 3, 'logp_median_ratio': True, 'keep_top_n': 15, 'final_count': 119}</t>
         </is>
       </c>
     </row>
@@ -1284,7 +5262,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'n_merged_groups': 1}</t>
+          <t>{'n_merged_groups': 12}</t>
         </is>
       </c>
     </row>
@@ -1296,7 +5274,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'metric': 'jaccard', 'n_terms': 14}</t>
+          <t>{'metric': 'jaccard', 'n_terms': 96}</t>
         </is>
       </c>
     </row>
@@ -1320,7 +5298,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'method': 'meanshift', 'n_clusters': 3}</t>
+          <t>{'method': 'meanshift', 'n_clusters': 9}</t>
         </is>
       </c>
     </row>
@@ -1332,7 +5310,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'silhouette_score': 0.07097193371613884}</t>
+          <t>{'silhouette_score': 0.16208985023588215}</t>
         </is>
       </c>
     </row>
@@ -1347,7 +5325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,17 +5348,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>GO:0031976</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GO:0009534</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>plastid thylakoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GO:0009535</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GO:0055035</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>chloroplast thylakoid membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GO:0010329</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GO:0080161</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>auxin efflux transmembrane transporter activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GO:0010333</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GO:0016838</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>terpene synthase activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GO:0120251</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GO:0120252</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>hydrocarbon biosynthetic process</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GO:0010360</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GO:0034763,GO:0032410,GO:1903960,GO:1903792,GO:0032413,GO:0034766,GO:0043271</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>negative regulation of anion channel activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GO:0031408</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GO:0031407</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>oxylipin biosynthetic process</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>GO:0019253</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>GO:0019685</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>reductive pentose-phosphate cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GO:0043450</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GO:0043449,GO:0009693,GO:0009692,GO:1900674,GO:1900673</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>alkene biosynthetic process</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GO:0009044</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GO:0046556</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>xylan 1,4-beta-xylosidase activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GO:0031222</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GO:0031221</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>arabinan catabolic process</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GO:0098719</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GO:0015385,GO:0035725</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sodium ion import across plasma membrane</t>
         </is>
       </c>
     </row>
